--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -14,9 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suivi &amp; Évolution" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traçabilité" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journal d'anomalies" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journal d'exécution" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cas de test'!$A$1:$N$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cas de test'!$A$1:$O$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -172,6 +173,12 @@
       <color rgb="000F172A"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -202,17 +209,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0064748B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D97706"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0064748B"/>
       </patternFill>
     </fill>
   </fills>
@@ -242,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -295,15 +302,6 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -316,13 +314,13 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -356,6 +354,16 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -747,7 +755,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Avancement de la campagne (burn-up)</a:t>
+              <a:t>Avancement de la campagne (cible vs réel)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -779,12 +787,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Suivi &amp; Évolution'!$A$5:$A$20</f>
+              <f>'Suivi &amp; Évolution'!$A$5:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Suivi &amp; Évolution'!$B$5:$B$20</f>
+              <f>'Suivi &amp; Évolution'!$B$5:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -811,12 +819,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Suivi &amp; Évolution'!$A$5:$A$20</f>
+              <f>'Suivi &amp; Évolution'!$A$5:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Suivi &amp; Évolution'!$C$5:$C$20</f>
+              <f>'Suivi &amp; Évolution'!$C$5:$C$19</f>
             </numRef>
           </val>
         </ser>
@@ -843,12 +851,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Suivi &amp; Évolution'!$A$5:$A$20</f>
+              <f>'Suivi &amp; Évolution'!$A$5:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Suivi &amp; Évolution'!$D$5:$D$20</f>
+              <f>'Suivi &amp; Évolution'!$D$5:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -897,7 +905,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Cas (cumulés)</a:t>
+                  <a:t>Cas de test (cumulés)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -943,6 +951,38 @@
           <order val="0"/>
           <tx>
             <strRef>
+              <f>'Suivi &amp; Évolution'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Suivi &amp; Évolution'!$A$5:$A$19</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Suivi &amp; Évolution'!$E$5:$E$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
               <f>'Suivi &amp; Évolution'!F4</f>
             </strRef>
           </tx>
@@ -961,44 +1001,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Suivi &amp; Évolution'!$A$5:$A$20</f>
+              <f>'Suivi &amp; Évolution'!$A$5:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Suivi &amp; Évolution'!$F$5:$F$20</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Suivi &amp; Évolution'!G4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Suivi &amp; Évolution'!$A$5:$A$20</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Suivi &amp; Évolution'!$G$5:$G$20</f>
+              <f>'Suivi &amp; Évolution'!$F$5:$F$19</f>
             </numRef>
           </val>
         </ser>
@@ -1166,7 +1174,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6840000" cy="3420000"/>
@@ -1188,7 +1196,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6840000" cy="3420000"/>
@@ -1907,7 +1915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:O122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1922,8 +1930,9 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1997,6 +2006,11 @@
           <t>Exigence</t>
         </is>
       </c>
+      <c r="O1" s="12" t="inlineStr">
+        <is>
+          <t>Évidence / Observé</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -2052,7 +2066,7 @@
       </c>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="L2" s="15" t="inlineStr">
@@ -2062,12 +2076,17 @@
       </c>
       <c r="M2" s="13" t="inlineStr">
         <is>
-          <t>A. Benali</t>
+          <t>QA-Auto (Playwright)</t>
         </is>
       </c>
       <c r="N2" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
+        </is>
+      </c>
+      <c r="O2" s="13" t="inlineStr">
+        <is>
+          <t>TC-PDCA-001_liste.png — 6 lignes, 1 appel API, 0 scintillement</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2154,17 @@
       </c>
       <c r="M3" s="16" t="inlineStr">
         <is>
-          <t>S. Diallo</t>
+          <t>QA-Auto (Playwright)</t>
         </is>
       </c>
       <c r="N3" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
+        </is>
+      </c>
+      <c r="O3" s="16" t="inlineStr">
+        <is>
+          <t>TC-PDCA-002_filtre.png — filtre PLAN -&gt; 1 ligne</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2233,17 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>M. Fontaine</t>
+          <t>QA-Auto (Playwright)</t>
         </is>
       </c>
       <c r="N4" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
+        </is>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
+        <is>
+          <t>TC-PDCA-003b_apres.png — cycle créé (6 -&gt; 7)</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2300,7 @@
       </c>
       <c r="K5" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="L5" s="15" t="inlineStr">
@@ -2281,12 +2310,17 @@
       </c>
       <c r="M5" s="16" t="inlineStr">
         <is>
-          <t>L. Tremblay</t>
+          <t>QA-Auto (Playwright)</t>
         </is>
       </c>
       <c r="N5" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
+        </is>
+      </c>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>TC-PDCA-004_detail.png — détail chargé, pas de 'Chargement…'</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2388,17 @@
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>R. Costa</t>
+          <t>QA-Auto (Playwright)</t>
         </is>
       </c>
       <c r="N6" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
+        </is>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
+        <is>
+          <t>TC-PDCA-005_apres.png — avancement DO-&gt;CHECK, PATCH 200</t>
         </is>
       </c>
     </row>
@@ -2420,21 +2459,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L7" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M7" s="16" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L7" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr"/>
       <c r="N7" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
         </is>
       </c>
+      <c r="O7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -2490,24 +2526,21 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="L8" s="19" t="inlineStr">
         <is>
-          <t>Échoué</t>
-        </is>
-      </c>
-      <c r="M8" s="13" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="inlineStr"/>
       <c r="N8" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
+      <c r="O8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -2565,21 +2598,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L9" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L9" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr"/>
       <c r="N9" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
+      <c r="O9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2637,7 +2667,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L10" s="21" t="inlineStr">
+      <c r="L10" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -2648,6 +2678,7 @@
           <t>CLAUDE §11.1</t>
         </is>
       </c>
+      <c r="O10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -2702,10 +2733,10 @@
       </c>
       <c r="K11" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L11" s="21" t="inlineStr">
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L11" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -2716,6 +2747,7 @@
           <t>CLAUDE §3.2</t>
         </is>
       </c>
+      <c r="O11" s="16" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -2774,21 +2806,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L12" s="22" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-      <c r="M12" s="13" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr"/>
       <c r="N12" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
+      <c r="O12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -2848,21 +2877,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L13" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M13" s="16" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+      <c r="L13" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="inlineStr"/>
       <c r="N13" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
+      <c r="O13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -2918,24 +2944,21 @@
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M14" s="13" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M14" s="13" t="inlineStr"/>
       <c r="N14" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
+      <c r="O14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -2993,21 +3016,18 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L15" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L15" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="inlineStr"/>
       <c r="N15" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
+      <c r="O15" s="16" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -3066,21 +3086,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L16" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M16" s="13" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+      <c r="L16" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M16" s="13" t="inlineStr"/>
       <c r="N16" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §11.3</t>
         </is>
       </c>
+      <c r="O16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -3135,24 +3152,21 @@
       </c>
       <c r="K17" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L17" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M17" s="16" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L17" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M17" s="16" t="inlineStr"/>
       <c r="N17" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
+      <c r="O17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -3211,21 +3225,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L18" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M18" s="13" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+      <c r="L18" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M18" s="13" t="inlineStr"/>
       <c r="N18" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
+      <c r="O18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -3286,19 +3297,16 @@
       </c>
       <c r="L19" s="19" t="inlineStr">
         <is>
-          <t>Échoué</t>
-        </is>
-      </c>
-      <c r="M19" s="16" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M19" s="16" t="inlineStr"/>
       <c r="N19" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
+      <c r="O19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -3357,21 +3365,18 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L20" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
-        </is>
-      </c>
-      <c r="M20" s="13" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L20" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M20" s="13" t="inlineStr"/>
       <c r="N20" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
+      <c r="O20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -3399,7 +3404,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -3430,7 +3435,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L21" s="21" t="inlineStr">
+      <c r="L21" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -3441,6 +3446,7 @@
           <t>CLAUDE §3.5</t>
         </is>
       </c>
+      <c r="O21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -3498,7 +3504,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L22" s="21" t="inlineStr">
+      <c r="L22" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -3509,6 +3515,7 @@
           <t>CLAUDE §3.4</t>
         </is>
       </c>
+      <c r="O22" s="13" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -3564,24 +3571,21 @@
       </c>
       <c r="K23" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L23" s="22" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-      <c r="M23" s="16" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L23" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M23" s="16" t="inlineStr"/>
       <c r="N23" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
+      <c r="O23" s="16" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -3640,21 +3644,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L24" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M24" s="13" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L24" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M24" s="13" t="inlineStr"/>
       <c r="N24" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
+      <c r="O24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -3713,21 +3714,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L25" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M25" s="16" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L25" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M25" s="16" t="inlineStr"/>
       <c r="N25" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
+      <c r="O25" s="16" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -3782,24 +3780,21 @@
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L26" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M26" s="13" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L26" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M26" s="13" t="inlineStr"/>
       <c r="N26" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
+      <c r="O26" s="13" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -3858,21 +3853,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L27" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M27" s="16" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L27" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="inlineStr"/>
       <c r="N27" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
+      <c r="O27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -3931,21 +3923,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L28" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M28" s="13" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+      <c r="L28" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="inlineStr"/>
       <c r="N28" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
+      <c r="O28" s="13" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -3973,7 +3962,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -4001,24 +3990,21 @@
       </c>
       <c r="K29" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L29" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M29" s="16" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L29" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="inlineStr"/>
       <c r="N29" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
+      <c r="O29" s="16" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -4078,19 +4064,16 @@
       </c>
       <c r="L30" s="19" t="inlineStr">
         <is>
-          <t>Échoué</t>
-        </is>
-      </c>
-      <c r="M30" s="13" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M30" s="13" t="inlineStr"/>
       <c r="N30" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
+      <c r="O30" s="13" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -4150,21 +4133,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L31" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
-        </is>
-      </c>
-      <c r="M31" s="16" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+      <c r="L31" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="inlineStr"/>
       <c r="N31" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
+      <c r="O31" s="16" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -4220,10 +4200,10 @@
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L32" s="21" t="inlineStr">
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L32" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -4234,6 +4214,7 @@
           <t>CLAUDE §12.1</t>
         </is>
       </c>
+      <c r="O32" s="13" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -4292,7 +4273,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L33" s="21" t="inlineStr">
+      <c r="L33" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -4303,6 +4284,7 @@
           <t>CLAUDE §1.4</t>
         </is>
       </c>
+      <c r="O33" s="16" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
@@ -4361,21 +4343,18 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L34" s="22" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-      <c r="M34" s="13" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L34" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M34" s="13" t="inlineStr"/>
       <c r="N34" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
+      <c r="O34" s="13" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -4430,24 +4409,21 @@
       </c>
       <c r="K35" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L35" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M35" s="16" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L35" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M35" s="16" t="inlineStr"/>
       <c r="N35" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
+      <c r="O35" s="16" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
@@ -4506,21 +4482,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L36" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M36" s="13" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+      <c r="L36" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M36" s="13" t="inlineStr"/>
       <c r="N36" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
+      <c r="O36" s="13" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -4579,21 +4552,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L37" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M37" s="16" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L37" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M37" s="16" t="inlineStr"/>
       <c r="N37" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
+      <c r="O37" s="16" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
@@ -4648,24 +4618,21 @@
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L38" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M38" s="13" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L38" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M38" s="13" t="inlineStr"/>
       <c r="N38" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
+      <c r="O38" s="13" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
@@ -4723,21 +4690,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L39" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M39" s="16" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L39" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M39" s="16" t="inlineStr"/>
       <c r="N39" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
+      <c r="O39" s="16" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
@@ -4796,21 +4760,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L40" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M40" s="13" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L40" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M40" s="13" t="inlineStr"/>
       <c r="N40" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
+      <c r="O40" s="13" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -4866,24 +4827,21 @@
       </c>
       <c r="K41" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="L41" s="19" t="inlineStr">
         <is>
-          <t>Échoué</t>
-        </is>
-      </c>
-      <c r="M41" s="16" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M41" s="16" t="inlineStr"/>
       <c r="N41" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
+      <c r="O41" s="16" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
@@ -4941,21 +4899,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L42" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
-        </is>
-      </c>
-      <c r="M42" s="13" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L42" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M42" s="13" t="inlineStr"/>
       <c r="N42" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="O42" s="13" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -5013,7 +4968,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L43" s="21" t="inlineStr">
+      <c r="L43" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -5024,6 +4979,7 @@
           <t>CLAUDE §4.1</t>
         </is>
       </c>
+      <c r="O43" s="16" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
@@ -5080,10 +5036,10 @@
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L44" s="21" t="inlineStr">
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L44" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -5094,6 +5050,7 @@
           <t>CLAUDE §4.1</t>
         </is>
       </c>
+      <c r="O44" s="13" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -5152,21 +5109,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L45" s="22" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-      <c r="M45" s="16" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L45" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M45" s="16" t="inlineStr"/>
       <c r="N45" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
+      <c r="O45" s="16" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
@@ -5225,21 +5179,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L46" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M46" s="13" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+      <c r="L46" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M46" s="13" t="inlineStr"/>
       <c r="N46" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
+      <c r="O46" s="13" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -5295,24 +5246,21 @@
       </c>
       <c r="K47" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L47" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M47" s="16" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L47" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M47" s="16" t="inlineStr"/>
       <c r="N47" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
+      <c r="O47" s="16" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
@@ -5371,21 +5319,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L48" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M48" s="13" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+      <c r="L48" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M48" s="13" t="inlineStr"/>
       <c r="N48" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
+      <c r="O48" s="13" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -5444,21 +5389,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L49" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M49" s="16" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L49" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M49" s="16" t="inlineStr"/>
       <c r="N49" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
+      <c r="O49" s="16" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
@@ -5486,7 +5428,7 @@
           <t>Intégration</t>
         </is>
       </c>
-      <c r="F50" s="23" t="inlineStr">
+      <c r="F50" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -5517,21 +5459,18 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L50" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M50" s="13" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L50" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M50" s="13" t="inlineStr"/>
       <c r="N50" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
+      <c r="O50" s="13" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -5589,21 +5528,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L51" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M51" s="16" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+      <c r="L51" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M51" s="16" t="inlineStr"/>
       <c r="N51" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
+      <c r="O51" s="16" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
@@ -5664,19 +5600,16 @@
       </c>
       <c r="L52" s="19" t="inlineStr">
         <is>
-          <t>Échoué</t>
-        </is>
-      </c>
-      <c r="M52" s="13" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M52" s="13" t="inlineStr"/>
       <c r="N52" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
+      <c r="O52" s="13" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -5731,24 +5664,21 @@
       </c>
       <c r="K53" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L53" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
-        </is>
-      </c>
-      <c r="M53" s="16" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L53" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M53" s="16" t="inlineStr"/>
       <c r="N53" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
+      <c r="O53" s="16" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
@@ -5807,7 +5737,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L54" s="21" t="inlineStr">
+      <c r="L54" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -5818,6 +5748,7 @@
           <t>CLAUDE §8.4</t>
         </is>
       </c>
+      <c r="O54" s="13" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -5875,7 +5806,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L55" s="21" t="inlineStr">
+      <c r="L55" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -5886,6 +5817,7 @@
           <t>CLAUDE §8.7</t>
         </is>
       </c>
+      <c r="O55" s="16" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
@@ -5940,24 +5872,21 @@
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L56" s="22" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-      <c r="M56" s="13" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L56" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M56" s="13" t="inlineStr"/>
       <c r="N56" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
+      <c r="O56" s="13" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
@@ -6017,21 +5946,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L57" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M57" s="16" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L57" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M57" s="16" t="inlineStr"/>
       <c r="N57" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
+      <c r="O57" s="16" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
@@ -6089,21 +6015,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L58" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M58" s="13" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+      <c r="L58" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M58" s="13" t="inlineStr"/>
       <c r="N58" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
+      <c r="O58" s="13" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -6159,24 +6082,21 @@
       </c>
       <c r="K59" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L59" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M59" s="16" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L59" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M59" s="16" t="inlineStr"/>
       <c r="N59" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
+      <c r="O59" s="16" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
@@ -6234,21 +6154,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L60" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M60" s="13" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L60" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M60" s="13" t="inlineStr"/>
       <c r="N60" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="O60" s="13" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -6307,21 +6224,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L61" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M61" s="16" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+      <c r="L61" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M61" s="16" t="inlineStr"/>
       <c r="N61" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
+      <c r="O61" s="16" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
@@ -6376,24 +6290,21 @@
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L62" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M62" s="13" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L62" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M62" s="13" t="inlineStr"/>
       <c r="N62" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
+      <c r="O62" s="13" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -6454,19 +6365,16 @@
       </c>
       <c r="L63" s="19" t="inlineStr">
         <is>
-          <t>Échoué</t>
-        </is>
-      </c>
-      <c r="M63" s="16" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M63" s="16" t="inlineStr"/>
       <c r="N63" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
+      <c r="O63" s="16" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
@@ -6525,21 +6433,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L64" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
-        </is>
-      </c>
-      <c r="M64" s="13" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L64" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M64" s="13" t="inlineStr"/>
       <c r="N64" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
+      <c r="O64" s="13" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
@@ -6595,10 +6500,10 @@
       </c>
       <c r="K65" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L65" s="21" t="inlineStr">
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L65" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -6609,6 +6514,7 @@
           <t>CLAUDE §8.11</t>
         </is>
       </c>
+      <c r="O65" s="16" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
@@ -6666,7 +6572,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L66" s="21" t="inlineStr">
+      <c r="L66" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -6677,6 +6583,7 @@
           <t>CLAUDE §7.1</t>
         </is>
       </c>
+      <c r="O66" s="13" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
@@ -6734,21 +6641,18 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L67" s="22" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-      <c r="M67" s="16" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L67" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M67" s="16" t="inlineStr"/>
       <c r="N67" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
+      <c r="O67" s="16" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
@@ -6804,24 +6708,21 @@
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L68" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M68" s="13" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L68" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M68" s="13" t="inlineStr"/>
       <c r="N68" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
+      <c r="O68" s="13" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
@@ -6880,21 +6781,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L69" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M69" s="16" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L69" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M69" s="16" t="inlineStr"/>
       <c r="N69" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
+      <c r="O69" s="16" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
@@ -6952,21 +6850,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L70" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M70" s="13" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L70" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M70" s="13" t="inlineStr"/>
       <c r="N70" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
+      <c r="O70" s="13" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
@@ -7021,24 +6916,21 @@
       </c>
       <c r="K71" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L71" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M71" s="16" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L71" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M71" s="16" t="inlineStr"/>
       <c r="N71" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
+      <c r="O71" s="16" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
@@ -7066,7 +6958,7 @@
           <t>IHM/UX</t>
         </is>
       </c>
-      <c r="F72" s="23" t="inlineStr">
+      <c r="F72" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -7097,21 +6989,18 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L72" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M72" s="13" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L72" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M72" s="13" t="inlineStr"/>
       <c r="N72" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
+      <c r="O72" s="13" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
@@ -7169,21 +7058,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L73" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M73" s="16" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+      <c r="L73" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M73" s="16" t="inlineStr"/>
       <c r="N73" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
+      <c r="O73" s="16" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
@@ -7239,24 +7125,21 @@
       </c>
       <c r="K74" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="L74" s="19" t="inlineStr">
         <is>
-          <t>Échoué</t>
-        </is>
-      </c>
-      <c r="M74" s="13" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M74" s="13" t="inlineStr"/>
       <c r="N74" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
+      <c r="O74" s="13" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
@@ -7315,21 +7198,18 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L75" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
-        </is>
-      </c>
-      <c r="M75" s="16" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L75" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M75" s="16" t="inlineStr"/>
       <c r="N75" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
+      <c r="O75" s="16" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
@@ -7387,7 +7267,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L76" s="21" t="inlineStr">
+      <c r="L76" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -7398,6 +7278,7 @@
           <t>CLAUDE §11.2</t>
         </is>
       </c>
+      <c r="O76" s="13" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
@@ -7453,10 +7334,10 @@
       </c>
       <c r="K77" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L77" s="21" t="inlineStr">
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L77" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -7467,6 +7348,7 @@
           <t>CLAUDE §3.4</t>
         </is>
       </c>
+      <c r="O77" s="16" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
@@ -7525,21 +7407,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L78" s="22" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-      <c r="M78" s="13" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+      <c r="L78" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M78" s="13" t="inlineStr"/>
       <c r="N78" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §12.3</t>
         </is>
       </c>
+      <c r="O78" s="13" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
@@ -7598,21 +7477,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L79" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M79" s="16" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L79" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M79" s="16" t="inlineStr"/>
       <c r="N79" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
+      <c r="O79" s="16" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
@@ -7668,24 +7544,21 @@
       </c>
       <c r="K80" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L80" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M80" s="13" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L80" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M80" s="13" t="inlineStr"/>
       <c r="N80" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.9</t>
         </is>
       </c>
+      <c r="O80" s="13" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -7713,7 +7586,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F81" s="23" t="inlineStr">
+      <c r="F81" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -7744,21 +7617,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L81" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M81" s="16" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+      <c r="L81" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M81" s="16" t="inlineStr"/>
       <c r="N81" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
+      <c r="O81" s="16" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
@@ -7816,21 +7686,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L82" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M82" s="13" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L82" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M82" s="13" t="inlineStr"/>
       <c r="N82" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
+      <c r="O82" s="13" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
@@ -7889,21 +7756,18 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L83" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M83" s="16" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+      <c r="L83" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M83" s="16" t="inlineStr"/>
       <c r="N83" s="16" t="inlineStr">
         <is>
           <t>ADR 0014</t>
         </is>
       </c>
+      <c r="O83" s="16" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
@@ -7961,21 +7825,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L84" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M84" s="13" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L84" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M84" s="13" t="inlineStr"/>
       <c r="N84" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
+      <c r="O84" s="13" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
@@ -8037,19 +7898,16 @@
       </c>
       <c r="L85" s="19" t="inlineStr">
         <is>
-          <t>Échoué</t>
-        </is>
-      </c>
-      <c r="M85" s="16" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M85" s="16" t="inlineStr"/>
       <c r="N85" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
+      <c r="O85" s="16" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
@@ -8077,7 +7935,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F86" s="23" t="inlineStr">
+      <c r="F86" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -8104,24 +7962,21 @@
       </c>
       <c r="K86" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L86" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
-        </is>
-      </c>
-      <c r="M86" s="13" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L86" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M86" s="13" t="inlineStr"/>
       <c r="N86" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
+      <c r="O86" s="13" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
@@ -8180,7 +8035,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L87" s="21" t="inlineStr">
+      <c r="L87" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -8191,6 +8046,7 @@
           <t>CLAUDE §19.3</t>
         </is>
       </c>
+      <c r="O87" s="16" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
@@ -8248,7 +8104,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L88" s="21" t="inlineStr">
+      <c r="L88" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -8259,6 +8115,7 @@
           <t>CLAUDE §11.3</t>
         </is>
       </c>
+      <c r="O88" s="13" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
@@ -8286,7 +8143,7 @@
           <t>Intégration</t>
         </is>
       </c>
-      <c r="F89" s="23" t="inlineStr">
+      <c r="F89" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -8316,21 +8173,18 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L89" s="22" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-      <c r="M89" s="16" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L89" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M89" s="16" t="inlineStr"/>
       <c r="N89" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
+      <c r="O89" s="16" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
@@ -8388,21 +8242,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L90" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M90" s="13" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L90" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M90" s="13" t="inlineStr"/>
       <c r="N90" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.7</t>
         </is>
       </c>
+      <c r="O90" s="13" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="16" t="inlineStr">
@@ -8460,21 +8311,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L91" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M91" s="16" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+      <c r="L91" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M91" s="16" t="inlineStr"/>
       <c r="N91" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
+      <c r="O91" s="16" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
@@ -8531,24 +8379,21 @@
       </c>
       <c r="K92" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L92" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M92" s="13" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L92" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M92" s="13" t="inlineStr"/>
       <c r="N92" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
+      <c r="O92" s="13" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="16" t="inlineStr">
@@ -8607,21 +8452,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L93" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M93" s="16" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+      <c r="L93" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M93" s="16" t="inlineStr"/>
       <c r="N93" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
+      <c r="O93" s="16" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
@@ -8679,21 +8521,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L94" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M94" s="13" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L94" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M94" s="13" t="inlineStr"/>
       <c r="N94" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="O94" s="13" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="16" t="inlineStr">
@@ -8749,24 +8588,21 @@
       </c>
       <c r="K95" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L95" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M95" s="16" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L95" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M95" s="16" t="inlineStr"/>
       <c r="N95" s="16" t="inlineStr">
         <is>
           <t>RGPD §30</t>
         </is>
       </c>
+      <c r="O95" s="16" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
@@ -8826,19 +8662,16 @@
       </c>
       <c r="L96" s="19" t="inlineStr">
         <is>
-          <t>Échoué</t>
-        </is>
-      </c>
-      <c r="M96" s="13" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M96" s="13" t="inlineStr"/>
       <c r="N96" s="13" t="inlineStr">
         <is>
           <t>RGPD</t>
         </is>
       </c>
+      <c r="O96" s="13" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="16" t="inlineStr">
@@ -8897,21 +8730,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L97" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
-        </is>
-      </c>
-      <c r="M97" s="16" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L97" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M97" s="16" t="inlineStr"/>
       <c r="N97" s="16" t="inlineStr">
         <is>
           <t>RGPD §15-22</t>
         </is>
       </c>
+      <c r="O97" s="16" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
@@ -8967,10 +8797,10 @@
       </c>
       <c r="K98" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L98" s="21" t="inlineStr">
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L98" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -8981,6 +8811,7 @@
           <t>RGPD §35</t>
         </is>
       </c>
+      <c r="O98" s="13" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="16" t="inlineStr">
@@ -9039,7 +8870,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L99" s="21" t="inlineStr">
+      <c r="L99" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -9050,6 +8881,7 @@
           <t>RGPD §33</t>
         </is>
       </c>
+      <c r="O99" s="16" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
@@ -9107,21 +8939,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L100" s="22" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-      <c r="M100" s="13" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L100" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M100" s="13" t="inlineStr"/>
       <c r="N100" s="13" t="inlineStr">
         <is>
           <t>RGPD §28/44</t>
         </is>
       </c>
+      <c r="O100" s="13" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
@@ -9177,24 +9006,21 @@
       </c>
       <c r="K101" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L101" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M101" s="16" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L101" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M101" s="16" t="inlineStr"/>
       <c r="N101" s="16" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
+      <c r="O101" s="16" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
@@ -9252,21 +9078,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L102" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M102" s="13" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L102" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M102" s="13" t="inlineStr"/>
       <c r="N102" s="13" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
+      <c r="O102" s="13" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
@@ -9324,21 +9147,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L103" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M103" s="16" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+      <c r="L103" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M103" s="16" t="inlineStr"/>
       <c r="N103" s="16" t="inlineStr">
         <is>
           <t>NIS 2</t>
         </is>
       </c>
+      <c r="O103" s="16" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
@@ -9394,24 +9214,21 @@
       </c>
       <c r="K104" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L104" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M104" s="13" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L104" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M104" s="13" t="inlineStr"/>
       <c r="N104" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §10.2</t>
         </is>
       </c>
+      <c r="O104" s="13" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
@@ -9470,21 +9287,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L105" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M105" s="16" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L105" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M105" s="16" t="inlineStr"/>
       <c r="N105" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="O105" s="16" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
@@ -9543,21 +9357,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L106" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M106" s="13" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+      <c r="L106" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M106" s="13" t="inlineStr"/>
       <c r="N106" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="O106" s="13" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="16" t="inlineStr">
@@ -9612,24 +9423,21 @@
       </c>
       <c r="K107" s="16" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="L107" s="19" t="inlineStr">
         <is>
-          <t>Échoué</t>
-        </is>
-      </c>
-      <c r="M107" s="16" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M107" s="16" t="inlineStr"/>
       <c r="N107" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §16</t>
         </is>
       </c>
+      <c r="O107" s="16" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
@@ -9687,21 +9495,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L108" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
-        </is>
-      </c>
-      <c r="M108" s="13" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+      <c r="L108" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M108" s="13" t="inlineStr"/>
       <c r="N108" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
+      <c r="O108" s="13" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="16" t="inlineStr">
@@ -9759,7 +9564,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L109" s="21" t="inlineStr">
+      <c r="L109" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -9770,6 +9575,7 @@
           <t>CLAUDE §11.1</t>
         </is>
       </c>
+      <c r="O109" s="16" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
@@ -9824,10 +9630,10 @@
       </c>
       <c r="K110" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L110" s="21" t="inlineStr">
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L110" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -9838,6 +9644,7 @@
           <t>CLAUDE §14.2</t>
         </is>
       </c>
+      <c r="O110" s="13" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="16" t="inlineStr">
@@ -9895,21 +9702,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L111" s="22" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-      <c r="M111" s="16" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+      <c r="L111" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M111" s="16" t="inlineStr"/>
       <c r="N111" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §11.4</t>
         </is>
       </c>
+      <c r="O111" s="16" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
@@ -9967,21 +9771,18 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L112" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M112" s="13" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L112" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M112" s="13" t="inlineStr"/>
       <c r="N112" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
+      <c r="O112" s="13" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="16" t="inlineStr">
@@ -10040,21 +9841,18 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L113" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M113" s="16" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+      <c r="L113" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M113" s="16" t="inlineStr"/>
       <c r="N113" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
+      <c r="O113" s="16" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
@@ -10115,21 +9913,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L114" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M114" s="13" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L114" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M114" s="13" t="inlineStr"/>
       <c r="N114" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
+      <c r="O114" s="13" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="16" t="inlineStr">
@@ -10187,21 +9982,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L115" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M115" s="16" t="inlineStr">
-        <is>
-          <t>L. Tremblay</t>
-        </is>
-      </c>
+      <c r="L115" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M115" s="16" t="inlineStr"/>
       <c r="N115" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
+      <c r="O115" s="16" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
@@ -10256,24 +10048,21 @@
       </c>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L116" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M116" s="13" t="inlineStr">
-        <is>
-          <t>R. Costa</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L116" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M116" s="13" t="inlineStr"/>
       <c r="N116" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
+      <c r="O116" s="13" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="16" t="inlineStr">
@@ -10331,21 +10120,18 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L117" s="15" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="M117" s="16" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+      <c r="L117" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M117" s="16" t="inlineStr"/>
       <c r="N117" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="O117" s="16" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
@@ -10406,19 +10192,16 @@
       </c>
       <c r="L118" s="19" t="inlineStr">
         <is>
-          <t>Échoué</t>
-        </is>
-      </c>
-      <c r="M118" s="13" t="inlineStr">
-        <is>
-          <t>S. Diallo</t>
-        </is>
-      </c>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M118" s="13" t="inlineStr"/>
       <c r="N118" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
+      <c r="O118" s="13" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="16" t="inlineStr">
@@ -10476,21 +10259,18 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L119" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
-        </is>
-      </c>
-      <c r="M119" s="16" t="inlineStr">
-        <is>
-          <t>M. Fontaine</t>
-        </is>
-      </c>
+      <c r="L119" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M119" s="16" t="inlineStr"/>
       <c r="N119" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §9.4</t>
         </is>
       </c>
+      <c r="O119" s="16" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
@@ -10549,7 +10329,7 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L120" s="21" t="inlineStr">
+      <c r="L120" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -10560,6 +10340,7 @@
           <t>CLAUDE §9.5</t>
         </is>
       </c>
+      <c r="O120" s="13" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="16" t="inlineStr">
@@ -10617,7 +10398,7 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L121" s="21" t="inlineStr">
+      <c r="L121" s="19" t="inlineStr">
         <is>
           <t>Non exécuté</t>
         </is>
@@ -10628,6 +10409,7 @@
           <t>CLAUDE §9.9</t>
         </is>
       </c>
+      <c r="O121" s="16" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
@@ -10682,27 +10464,24 @@
       </c>
       <c r="K122" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L122" s="22" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-      <c r="M122" s="13" t="inlineStr">
-        <is>
-          <t>A. Benali</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L122" s="19" t="inlineStr">
+        <is>
+          <t>Non exécuté</t>
+        </is>
+      </c>
+      <c r="M122" s="13" t="inlineStr"/>
       <c r="N122" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §9.8</t>
         </is>
       </c>
+      <c r="O122" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N122"/>
+  <autoFilter ref="A1:O122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10747,75 +10526,75 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Cas de test</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Exécutés</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>Taux d'exécution</t>
         </is>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t>Passés</t>
         </is>
       </c>
-      <c r="I4" s="26" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>Taux de réussite</t>
         </is>
       </c>
-      <c r="K4" s="27" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>Échoués</t>
         </is>
       </c>
-      <c r="M4" s="28" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Bloqués</t>
         </is>
       </c>
-      <c r="O4" s="29" t="inlineStr">
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t>Non exécutés</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="n">
+      <c r="A5" s="27" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="31" t="n">
-        <v>88</v>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="G5" s="32" t="n">
-        <v>66</v>
-      </c>
-      <c r="I5" s="32" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="K5" s="33" t="n">
-        <v>11</v>
-      </c>
-      <c r="M5" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="O5" s="35" t="n">
-        <v>22</v>
+      <c r="C5" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="29" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="32" t="n">
+        <v>116</v>
       </c>
     </row>
     <row r="6"/>
@@ -10837,32 +10616,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="E9" s="36" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="G9" s="36" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="H9" s="36" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -10875,7 +10654,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -10901,7 +10680,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -10927,7 +10706,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10953,7 +10732,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10979,7 +10758,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -11048,12 +10827,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="36" t="inlineStr">
+      <c r="G23" s="33" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="H23" s="36" t="inlineStr">
+      <c r="H23" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -11301,7 +11080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11338,433 +11117,309 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Planifiés (cumul)</t>
+          <t>Cible exécutés (objectif)</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Exécutés (cumul)</t>
+          <t>Réel exécutés (cumul)</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Passés (cumul)</t>
+          <t>Réel passés (cumul)</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Échoués (cumul)</t>
+          <t>Anomalies ouvertes (cumul)</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>Anomalies ouvertes (cumul)</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
           <t>Anomalies résolues (cumul)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
-        <is>
-          <t>06/06</t>
-        </is>
-      </c>
-      <c r="B5" s="37" t="n">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>J01 (23/06)</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>J02 (24/06)</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>J03 (25/06)</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>J04 (26/06)</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>J05 (27/06)</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="n">
+        <v>40</v>
+      </c>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>J06 (28/06)</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="n">
+        <v>48</v>
+      </c>
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>J07 (29/06)</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="n">
+        <v>56</v>
+      </c>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>J08 (30/06)</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="n">
+        <v>65</v>
+      </c>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>J09 (01/07)</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="n">
+        <v>73</v>
+      </c>
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>J10 (02/07)</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="n">
+        <v>81</v>
+      </c>
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>J11 (03/07)</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="n">
+        <v>89</v>
+      </c>
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>J12 (04/07)</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="n">
+        <v>97</v>
+      </c>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>J13 (05/07)</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="n">
+        <v>105</v>
+      </c>
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="34" t="n"/>
+      <c r="E17" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>J14 (06/07)</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="n">
+        <v>113</v>
+      </c>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>J15 (07/07)</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="37" t="inlineStr">
-        <is>
-          <t>07/06</t>
-        </is>
-      </c>
-      <c r="B6" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C6" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="37" t="inlineStr">
-        <is>
-          <t>08/06</t>
-        </is>
-      </c>
-      <c r="B7" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C7" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="37" t="inlineStr">
-        <is>
-          <t>09/06</t>
-        </is>
-      </c>
-      <c r="B8" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C8" s="37" t="n">
-        <v>9</v>
-      </c>
-      <c r="D8" s="37" t="n">
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="34" t="n"/>
+      <c r="E19" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" s="37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="37" t="inlineStr">
-        <is>
-          <t>10/06</t>
-        </is>
-      </c>
-      <c r="B9" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C9" s="37" t="n">
-        <v>15</v>
-      </c>
-      <c r="D9" s="37" t="n">
-        <v>11</v>
-      </c>
-      <c r="E9" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="37" t="n">
+      <c r="F19" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="37" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="37" t="inlineStr">
-        <is>
-          <t>11/06</t>
-        </is>
-      </c>
-      <c r="B10" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C10" s="37" t="n">
-        <v>22</v>
-      </c>
-      <c r="D10" s="37" t="n">
-        <v>16</v>
-      </c>
-      <c r="E10" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="37" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" s="37" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="37" t="inlineStr">
-        <is>
-          <t>12/06</t>
-        </is>
-      </c>
-      <c r="B11" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C11" s="37" t="n">
-        <v>30</v>
-      </c>
-      <c r="D11" s="37" t="n">
-        <v>23</v>
-      </c>
-      <c r="E11" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="37" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="37" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>13/06</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C12" s="37" t="n">
-        <v>39</v>
-      </c>
-      <c r="D12" s="37" t="n">
-        <v>29</v>
-      </c>
-      <c r="E12" s="37" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="37" t="n">
-        <v>13</v>
-      </c>
-      <c r="G12" s="37" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="37" t="inlineStr">
-        <is>
-          <t>14/06</t>
-        </is>
-      </c>
-      <c r="B13" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C13" s="37" t="n">
-        <v>49</v>
-      </c>
-      <c r="D13" s="37" t="n">
-        <v>37</v>
-      </c>
-      <c r="E13" s="37" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="37" t="n">
-        <v>15</v>
-      </c>
-      <c r="G13" s="37" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="37" t="inlineStr">
-        <is>
-          <t>15/06</t>
-        </is>
-      </c>
-      <c r="B14" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C14" s="37" t="n">
-        <v>58</v>
-      </c>
-      <c r="D14" s="37" t="n">
-        <v>43</v>
-      </c>
-      <c r="E14" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="37" t="n">
-        <v>18</v>
-      </c>
-      <c r="G14" s="37" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="37" t="inlineStr">
-        <is>
-          <t>16/06</t>
-        </is>
-      </c>
-      <c r="B15" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C15" s="37" t="n">
-        <v>66</v>
-      </c>
-      <c r="D15" s="37" t="n">
-        <v>50</v>
-      </c>
-      <c r="E15" s="37" t="n">
-        <v>8</v>
-      </c>
-      <c r="F15" s="37" t="n">
-        <v>20</v>
-      </c>
-      <c r="G15" s="37" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="37" t="inlineStr">
-        <is>
-          <t>17/06</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C16" s="37" t="n">
-        <v>73</v>
-      </c>
-      <c r="D16" s="37" t="n">
-        <v>55</v>
-      </c>
-      <c r="E16" s="37" t="n">
-        <v>9</v>
-      </c>
-      <c r="F16" s="37" t="n">
-        <v>22</v>
-      </c>
-      <c r="G16" s="37" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="37" t="inlineStr">
-        <is>
-          <t>18/06</t>
-        </is>
-      </c>
-      <c r="B17" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C17" s="37" t="n">
-        <v>79</v>
-      </c>
-      <c r="D17" s="37" t="n">
-        <v>60</v>
-      </c>
-      <c r="E17" s="37" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="37" t="n">
-        <v>24</v>
-      </c>
-      <c r="G17" s="37" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>19/06</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C18" s="37" t="n">
-        <v>84</v>
-      </c>
-      <c r="D18" s="37" t="n">
-        <v>63</v>
-      </c>
-      <c r="E18" s="37" t="n">
-        <v>10</v>
-      </c>
-      <c r="F18" s="37" t="n">
-        <v>26</v>
-      </c>
-      <c r="G18" s="37" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="37" t="inlineStr">
-        <is>
-          <t>20/06</t>
-        </is>
-      </c>
-      <c r="B19" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C19" s="37" t="n">
-        <v>87</v>
-      </c>
-      <c r="D19" s="37" t="n">
-        <v>65</v>
-      </c>
-      <c r="E19" s="37" t="n">
-        <v>11</v>
-      </c>
-      <c r="F19" s="37" t="n">
-        <v>27</v>
-      </c>
-      <c r="G19" s="37" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>21/06</t>
-        </is>
-      </c>
-      <c r="B20" s="37" t="n">
-        <v>121</v>
-      </c>
-      <c r="C20" s="37" t="n">
-        <v>88</v>
-      </c>
-      <c r="D20" s="37" t="n">
-        <v>66</v>
-      </c>
-      <c r="E20" s="37" t="n">
-        <v>11</v>
-      </c>
-      <c r="F20" s="37" t="n">
-        <v>28</v>
-      </c>
-      <c r="G20" s="37" t="n">
-        <v>25</v>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Lecture : la « cible » est la trajectoire planifiée (100% à J15). Le « réel » est renseigné au fil de l'exécution (Lot 1 = 5 cas PDCA, tous Passés). Les 6 anomalies de stabilisation pré-recette sont toutes résolues (0 ouverte).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -11823,870 +11478,870 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>ADR 0014</t>
         </is>
       </c>
-      <c r="B5" s="39" t="n">
+      <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>TC-AI-010</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
-      <c r="B6" s="39" t="n">
+      <c r="B6" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-008, TC-GRC-009</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="B7" s="39" t="n">
+      <c r="B7" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>TC-NC-004, TC-AUD-003, TC-WF-003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §10.2</t>
         </is>
       </c>
-      <c r="B8" s="39" t="n">
+      <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
-      <c r="B9" s="39" t="n">
+      <c r="B9" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-009, TC-STD-006, TC-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
-      <c r="B10" s="39" t="n">
+      <c r="B10" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="40" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>TC-AI-002, TC-AI-003, TC-AI-009</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.3</t>
         </is>
       </c>
-      <c r="B11" s="39" t="n">
+      <c r="B11" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="40" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>TC-5S-006, TC-ACAD-005</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.4</t>
         </is>
       </c>
-      <c r="B12" s="39" t="n">
+      <c r="B12" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-008</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="B13" s="39" t="n">
+      <c r="B13" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-003, TC-NC-003, TC-CAPA-003</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §12.3</t>
         </is>
       </c>
-      <c r="B14" s="39" t="n">
+      <c r="B14" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="40" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>TC-AI-005</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
-      <c r="B15" s="39" t="n">
+      <c r="B15" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="40" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-005</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §14.2</t>
         </is>
       </c>
-      <c r="B16" s="39" t="n">
+      <c r="B16" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="40" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-007</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
-      <c r="B17" s="39" t="n">
+      <c r="B17" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>TC-XCUT-004, TC-XCUT-007</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
-      <c r="B18" s="39" t="n">
+      <c r="B18" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="40" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>TC-XCUT-001, TC-XCUT-002</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
-      <c r="B19" s="39" t="n">
+      <c r="B19" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>TC-5S-003, TC-XCUT-003, TC-XCUT-005</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §16</t>
         </is>
       </c>
-      <c r="B20" s="39" t="n">
+      <c r="B20" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="40" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-004</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
-      <c r="B21" s="39" t="n">
+      <c r="B21" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="40" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-008, TC-DOCGEN-002, TC-SEC-005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
-      <c r="B22" s="39" t="n">
+      <c r="B22" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="40" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>TC-ACAD-001, TC-ACAD-002, TC-ACAD-003, TC-ACAD-004, TC-ACAD-006</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
         </is>
       </c>
-      <c r="B23" s="39" t="n">
+      <c r="B23" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="40" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-001, TC-PDCA-002, TC-PDCA-003, TC-PDCA-004, TC-PDCA-005, TC-PDCA-006</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="B24" s="39" t="n">
+      <c r="B24" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="40" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>TC-5S-001, TC-5S-002, TC-5S-004, TC-5S-005</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="B25" s="39" t="n">
+      <c r="B25" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="40" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>TC-CERCLE-001, TC-CERCLE-002, TC-CERCLE-003, TC-CERCLE-004</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="38" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="B26" s="39" t="n">
+      <c r="B26" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="40" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>TC-DMAIC-001, TC-DMAIC-002, TC-DMAIC-003, TC-DMAIC-004, TC-AI-004</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="B27" s="39" t="n">
+      <c r="B27" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="40" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-001, TC-ISHI-002, TC-ISHI-005</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="B28" s="39" t="n">
+      <c r="B28" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="40" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-004, TC-NC-005</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="B29" s="39" t="n">
+      <c r="B29" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="40" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>TC-DOC-001, TC-DOC-002, TC-DOC-003</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
-      <c r="B30" s="39" t="n">
+      <c r="B30" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="40" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-004</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="38" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="B31" s="39" t="n">
+      <c r="B31" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="40" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
         <is>
           <t>TC-CAPA-001, TC-CAPA-002</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="B32" s="39" t="n">
+      <c r="B32" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="40" t="inlineStr">
+      <c r="C32" s="37" t="inlineStr">
         <is>
           <t>TC-NC-001, TC-NC-002</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="inlineStr">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="B33" s="39" t="n">
+      <c r="B33" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="40" t="inlineStr">
+      <c r="C33" s="37" t="inlineStr">
         <is>
           <t>TC-AUD-001, TC-AUD-002</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="38" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
-      <c r="B34" s="39" t="n">
+      <c r="B34" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="40" t="inlineStr">
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-002</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="38" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
-      <c r="B35" s="39" t="n">
+      <c r="B35" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="40" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-001</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="38" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.7</t>
         </is>
       </c>
-      <c r="B36" s="39" t="n">
+      <c r="B36" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="40" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>TC-ACAD-007</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="38" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
-      <c r="B37" s="39" t="n">
+      <c r="B37" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="40" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-003</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="38" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.9</t>
         </is>
       </c>
-      <c r="B38" s="39" t="n">
+      <c r="B38" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="40" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>TC-AI-007</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="38" t="inlineStr">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
-      <c r="B39" s="39" t="n">
+      <c r="B39" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="40" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>TC-MKT-001</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="38" t="inlineStr">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
-      <c r="B40" s="39" t="n">
+      <c r="B40" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="40" t="inlineStr">
+      <c r="C40" s="37" t="inlineStr">
         <is>
           <t>TC-WF-001, TC-WF-002</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="38" t="inlineStr">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
-      <c r="B41" s="39" t="n">
+      <c r="B41" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="40" t="inlineStr">
+      <c r="C41" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-007, TC-AI-006</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="38" t="inlineStr">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="B42" s="39" t="n">
+      <c r="B42" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="40" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
         <is>
           <t>TC-CAPA-004, TC-DASH-008</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="38" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.1</t>
         </is>
       </c>
-      <c r="B43" s="39" t="n">
+      <c r="B43" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="40" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-001</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="38" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="B44" s="39" t="n">
+      <c r="B44" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="40" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-002, TC-DASH-003, TC-DASH-004, TC-DASH-007, TC-AI-001</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="38" t="inlineStr">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="B45" s="39" t="n">
+      <c r="B45" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="40" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-005, TC-DASH-006, TC-AI-008</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="38" t="inlineStr">
+      <c r="A46" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="B46" s="39" t="n">
+      <c r="B46" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="40" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
         <is>
           <t>TC-MKT-002, TC-MKT-003, TC-MKT-004, TC-MKT-005</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="38" t="inlineStr">
+      <c r="A47" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
-      <c r="B47" s="39" t="n">
+      <c r="B47" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="40" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
         <is>
           <t>TC-STD-001</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="38" t="inlineStr">
+      <c r="A48" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="B48" s="39" t="n">
+      <c r="B48" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="40" t="inlineStr">
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>TC-STD-002, TC-STD-004</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="38" t="inlineStr">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="B49" s="39" t="n">
+      <c r="B49" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="40" t="inlineStr">
+      <c r="C49" s="37" t="inlineStr">
         <is>
           <t>TC-STD-003, TC-STD-005</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="38" t="inlineStr">
+      <c r="A50" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="B50" s="39" t="n">
+      <c r="B50" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="40" t="inlineStr">
+      <c r="C50" s="37" t="inlineStr">
         <is>
           <t>TC-DOCGEN-001, TC-DOCGEN-003</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="38" t="inlineStr">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.4</t>
         </is>
       </c>
-      <c r="B51" s="39" t="n">
+      <c r="B51" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="40" t="inlineStr">
+      <c r="C51" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-001</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="38" t="inlineStr">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.5</t>
         </is>
       </c>
-      <c r="B52" s="39" t="n">
+      <c r="B52" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="40" t="inlineStr">
+      <c r="C52" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-002</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="38" t="inlineStr">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.8</t>
         </is>
       </c>
-      <c r="B53" s="39" t="n">
+      <c r="B53" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="40" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-004</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="38" t="inlineStr">
+      <c r="A54" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.9</t>
         </is>
       </c>
-      <c r="B54" s="39" t="n">
+      <c r="B54" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="40" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-003</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="38" t="inlineStr">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>NIS 2</t>
         </is>
       </c>
-      <c r="B55" s="39" t="n">
+      <c r="B55" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="40" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-010</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="38" t="inlineStr">
+      <c r="A56" s="35" t="inlineStr">
         <is>
           <t>RGPD</t>
         </is>
       </c>
-      <c r="B56" s="39" t="n">
+      <c r="B56" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="40" t="inlineStr">
+      <c r="C56" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-003</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="38" t="inlineStr">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>RGPD §15-22</t>
         </is>
       </c>
-      <c r="B57" s="39" t="n">
+      <c r="B57" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="40" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-004</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="38" t="inlineStr">
+      <c r="A58" s="35" t="inlineStr">
         <is>
           <t>RGPD §28/44</t>
         </is>
       </c>
-      <c r="B58" s="39" t="n">
+      <c r="B58" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="40" t="inlineStr">
+      <c r="C58" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-007</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="38" t="inlineStr">
+      <c r="A59" s="35" t="inlineStr">
         <is>
           <t>RGPD §30</t>
         </is>
       </c>
-      <c r="B59" s="39" t="n">
+      <c r="B59" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="40" t="inlineStr">
+      <c r="C59" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-002</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="38" t="inlineStr">
+      <c r="A60" s="35" t="inlineStr">
         <is>
           <t>RGPD §33</t>
         </is>
       </c>
-      <c r="B60" s="39" t="n">
+      <c r="B60" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="40" t="inlineStr">
+      <c r="C60" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-006</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="38" t="inlineStr">
+      <c r="A61" s="35" t="inlineStr">
         <is>
           <t>RGPD §35</t>
         </is>
       </c>
-      <c r="B61" s="39" t="n">
+      <c r="B61" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="40" t="inlineStr">
+      <c r="C61" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-005</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="38" t="inlineStr">
+      <c r="A62" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B62" s="39" t="n">
+      <c r="B62" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="40" t="inlineStr">
+      <c r="C62" s="37" t="inlineStr">
         <is>
           <t>TC-AUD-004, TC-DOCGEN-004, TC-GRC-001, TC-SEC-002, TC-SEC-003, TC-XCUT-006</t>
         </is>
@@ -12798,7 +12453,7 @@
           <t>IA / NLQ</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12845,7 +12500,7 @@
           <t>Méthodes/Transverse</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="39" t="inlineStr">
         <is>
           <t>Critique</t>
         </is>
@@ -12892,7 +12547,7 @@
           <t>PDCA/5S/NC…</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="39" t="inlineStr">
         <is>
           <t>Critique</t>
         </is>
@@ -12939,7 +12594,7 @@
           <t>Auth</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12986,7 +12641,7 @@
           <t>CI/Sécurité</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="40" t="inlineStr">
         <is>
           <t>Mineure</t>
         </is>
@@ -13033,7 +12688,7 @@
           <t>Front/Infra</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="40" t="inlineStr">
         <is>
           <t>Mineure</t>
         </is>
@@ -13061,6 +12716,245 @@
       <c r="I10" s="16" t="inlineStr">
         <is>
           <t>22/06</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Journal d'exécution</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Trace horodatée des cas exécutés (au fil de l'eau)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Cas de test</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Résultat</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Observé</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Évidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Lot 1</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>TC-PDCA-001</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Liste affichée : 6 cycles, 1 seul appel API GET, spinner 0/14, 0 toggle (non-régression ANO-002).</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>TC-PDCA-001_liste.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Lot 1</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>TC-PDCA-002</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Filtre statut 'PLAN' appliqué : 1 ligne (≤ 6). Liste correctement filtrée.</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>TC-PDCA-002_filtre.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Lot 1</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>TC-PDCA-003</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>Création d'un cycle (titre + description) : liste passée de 6 à 7, cycle visible.</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>TC-PDCA-003b_apres.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Lot 1</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>TC-PDCA-004</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Détail ouvert : titre + actions affichés, pas de 'Chargement…' figé (non-régression ANO-003).</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>TC-PDCA-004_detail.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Lot 1</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>TC-PDCA-005</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>Avancement de phase via l'UI : DO -&gt; CHECK, PATCH /cycles/{id}/advance = 200. Faux négatif initial du script corrigé (cycle terminal + sélecteur de badge).</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>TC-PDCA-005_apres.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>
       </c>
     </row>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -214,12 +214,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
+        <fgColor rgb="00D97706"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D97706"/>
+        <fgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
   </fills>
@@ -302,6 +302,9 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -314,10 +317,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -355,9 +358,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2736,18 +2736,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L11" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="inlineStr"/>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N11" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="O11" s="16" t="inlineStr"/>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-001_liste.png — 4 audits, 1 appel API, 0 scintillement</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -2806,18 +2814,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M12" s="13" t="inlineStr"/>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="O12" s="13" t="inlineStr"/>
+      <c r="O12" s="13" t="inlineStr">
+        <is>
+          <t>TC-5S-002b_apres.png — création zone+date (4 -&gt; 5). Récurrence absente du dialog (écart mineur).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -2877,18 +2893,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L13" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M13" s="16" t="inlineStr"/>
+      <c r="L13" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N13" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
-      <c r="O13" s="16" t="inlineStr"/>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-003_offline.png — /offline-queue accessible (vérif partielle PWA).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -2947,18 +2971,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M14" s="13" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="M14" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="O14" s="13" t="inlineStr"/>
+      <c r="O14" s="13" t="inlineStr">
+        <is>
+          <t>Vision YOLOv8 non câblée dans l'UI 5S + service ai-vision absent (dépendance/env).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -3016,18 +3048,26 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr"/>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N15" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="O15" s="16" t="inlineStr"/>
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>Pas de heatmap par zone dans l'UI 5S (écart vs CLAUDE §3.2) — voir ANO-007.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -3404,7 +3444,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -3962,7 +4002,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -5428,7 +5468,7 @@
           <t>Intégration</t>
         </is>
       </c>
-      <c r="F50" s="20" t="inlineStr">
+      <c r="F50" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -6958,7 +6998,7 @@
           <t>IHM/UX</t>
         </is>
       </c>
-      <c r="F72" s="20" t="inlineStr">
+      <c r="F72" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -7586,7 +7626,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F81" s="20" t="inlineStr">
+      <c r="F81" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -7935,7 +7975,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F86" s="20" t="inlineStr">
+      <c r="F86" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -8143,7 +8183,7 @@
           <t>Intégration</t>
         </is>
       </c>
-      <c r="F89" s="20" t="inlineStr">
+      <c r="F89" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -10526,75 +10566,75 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Cas de test</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Exécutés</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Taux d'exécution</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>Passés</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Taux de réussite</t>
         </is>
       </c>
-      <c r="K4" s="24" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>Échoués</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t>Bloqués</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
+      <c r="O4" s="27" t="inlineStr">
         <is>
           <t>Non exécutés</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
+      <c r="A5" s="28" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" s="29" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="K5" s="30" t="n">
+      <c r="C5" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="30" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>116</v>
+      <c r="M5" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="33" t="n">
+        <v>111</v>
       </c>
     </row>
     <row r="6"/>
@@ -10616,32 +10656,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="G9" s="33" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
+      <c r="H9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -10654,7 +10694,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -10706,7 +10746,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10758,7 +10798,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -10827,12 +10867,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="33" t="inlineStr">
+      <c r="G23" s="34" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="H23" s="33" t="inlineStr">
+      <c r="H23" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -11142,276 +11182,276 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>J01 (23/06)</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="34" t="n">
+      <c r="C5" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="34" t="n">
+      <c r="F5" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>J02 (24/06)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="34" t="n">
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>J03 (25/06)</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="34" t="n"/>
-      <c r="D7" s="34" t="n"/>
-      <c r="E7" s="34" t="n">
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>J04 (26/06)</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n">
+      <c r="B8" s="35" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="34" t="n"/>
-      <c r="D8" s="34" t="n"/>
-      <c r="E8" s="34" t="n">
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>J05 (27/06)</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="35" t="n">
         <v>40</v>
       </c>
-      <c r="C9" s="34" t="n"/>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="34" t="n">
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F9" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>J06 (28/06)</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n">
+      <c r="B10" s="35" t="n">
         <v>48</v>
       </c>
-      <c r="C10" s="34" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="34" t="n">
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="34" t="n">
+      <c r="F10" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>J07 (29/06)</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="35" t="n">
         <v>56</v>
       </c>
-      <c r="C11" s="34" t="n"/>
-      <c r="D11" s="34" t="n"/>
-      <c r="E11" s="34" t="n">
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F11" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>J08 (30/06)</t>
         </is>
       </c>
-      <c r="B12" s="34" t="n">
+      <c r="B12" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="C12" s="34" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="34" t="n">
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F12" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>J09 (01/07)</t>
         </is>
       </c>
-      <c r="B13" s="34" t="n">
+      <c r="B13" s="35" t="n">
         <v>73</v>
       </c>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="34" t="n"/>
-      <c r="E13" s="34" t="n">
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F13" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>J10 (02/07)</t>
         </is>
       </c>
-      <c r="B14" s="34" t="n">
+      <c r="B14" s="35" t="n">
         <v>81</v>
       </c>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n"/>
-      <c r="E14" s="34" t="n">
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="34" t="n">
+      <c r="F14" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>J11 (03/07)</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n">
+      <c r="B15" s="35" t="n">
         <v>89</v>
       </c>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="34" t="n"/>
-      <c r="E15" s="34" t="n">
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="34" t="n">
+      <c r="F15" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>J12 (04/07)</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n">
+      <c r="B16" s="35" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="34" t="n"/>
-      <c r="E16" s="34" t="n">
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F16" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>J13 (05/07)</t>
         </is>
       </c>
-      <c r="B17" s="34" t="n">
+      <c r="B17" s="35" t="n">
         <v>105</v>
       </c>
-      <c r="C17" s="34" t="n"/>
-      <c r="D17" s="34" t="n"/>
-      <c r="E17" s="34" t="n">
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="34" t="n">
+      <c r="F17" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>J14 (06/07)</t>
         </is>
       </c>
-      <c r="B18" s="34" t="n">
+      <c r="B18" s="35" t="n">
         <v>113</v>
       </c>
-      <c r="C18" s="34" t="n"/>
-      <c r="D18" s="34" t="n"/>
-      <c r="E18" s="34" t="n">
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F18" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>J15 (07/07)</t>
         </is>
       </c>
-      <c r="B19" s="34" t="n">
+      <c r="B19" s="35" t="n">
         <v>121</v>
       </c>
-      <c r="C19" s="34" t="n"/>
-      <c r="D19" s="34" t="n"/>
-      <c r="E19" s="34" t="n">
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="34" t="n">
+      <c r="F19" s="35" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11478,870 +11518,870 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>ADR 0014</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n">
+      <c r="B5" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>TC-AI-010</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-008, TC-GRC-009</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>TC-NC-004, TC-AUD-003, TC-WF-003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §10.2</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B8" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-009, TC-STD-006, TC-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n">
+      <c r="B10" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>TC-AI-002, TC-AI-003, TC-AI-009</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.3</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
+      <c r="B11" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>TC-5S-006, TC-ACAD-005</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.4</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
+      <c r="B12" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-008</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n">
+      <c r="B13" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-003, TC-NC-003, TC-CAPA-003</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §12.3</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n">
+      <c r="B14" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>TC-AI-005</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
-      <c r="B15" s="36" t="n">
+      <c r="B15" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-005</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §14.2</t>
         </is>
       </c>
-      <c r="B16" s="36" t="n">
+      <c r="B16" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="37" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-007</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
-      <c r="B17" s="36" t="n">
+      <c r="B17" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="37" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>TC-XCUT-004, TC-XCUT-007</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
-      <c r="B18" s="36" t="n">
+      <c r="B18" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="37" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>TC-XCUT-001, TC-XCUT-002</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n">
+      <c r="B19" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>TC-5S-003, TC-XCUT-003, TC-XCUT-005</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §16</t>
         </is>
       </c>
-      <c r="B20" s="36" t="n">
+      <c r="B20" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="37" t="inlineStr">
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-004</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
-      <c r="B21" s="36" t="n">
+      <c r="B21" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="37" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-008, TC-DOCGEN-002, TC-SEC-005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
-      <c r="B22" s="36" t="n">
+      <c r="B22" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="37" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>TC-ACAD-001, TC-ACAD-002, TC-ACAD-003, TC-ACAD-004, TC-ACAD-006</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
         </is>
       </c>
-      <c r="B23" s="36" t="n">
+      <c r="B23" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="37" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-001, TC-PDCA-002, TC-PDCA-003, TC-PDCA-004, TC-PDCA-005, TC-PDCA-006</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="B24" s="36" t="n">
+      <c r="B24" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="37" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>TC-5S-001, TC-5S-002, TC-5S-004, TC-5S-005</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="B25" s="36" t="n">
+      <c r="B25" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="37" t="inlineStr">
+      <c r="C25" s="38" t="inlineStr">
         <is>
           <t>TC-CERCLE-001, TC-CERCLE-002, TC-CERCLE-003, TC-CERCLE-004</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="B26" s="36" t="n">
+      <c r="B26" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="37" t="inlineStr">
+      <c r="C26" s="38" t="inlineStr">
         <is>
           <t>TC-DMAIC-001, TC-DMAIC-002, TC-DMAIC-003, TC-DMAIC-004, TC-AI-004</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="B27" s="36" t="n">
+      <c r="B27" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="37" t="inlineStr">
+      <c r="C27" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-001, TC-ISHI-002, TC-ISHI-005</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="B28" s="36" t="n">
+      <c r="B28" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="37" t="inlineStr">
+      <c r="C28" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-004, TC-NC-005</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="B29" s="36" t="n">
+      <c r="B29" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="38" t="inlineStr">
         <is>
           <t>TC-DOC-001, TC-DOC-002, TC-DOC-003</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
-      <c r="B30" s="36" t="n">
+      <c r="B30" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="37" t="inlineStr">
+      <c r="C30" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-004</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="B31" s="36" t="n">
+      <c r="B31" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="37" t="inlineStr">
+      <c r="C31" s="38" t="inlineStr">
         <is>
           <t>TC-CAPA-001, TC-CAPA-002</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="B32" s="36" t="n">
+      <c r="B32" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="37" t="inlineStr">
+      <c r="C32" s="38" t="inlineStr">
         <is>
           <t>TC-NC-001, TC-NC-002</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="35" t="inlineStr">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="B33" s="36" t="n">
+      <c r="B33" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="37" t="inlineStr">
+      <c r="C33" s="38" t="inlineStr">
         <is>
           <t>TC-AUD-001, TC-AUD-002</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
-      <c r="B34" s="36" t="n">
+      <c r="B34" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="37" t="inlineStr">
+      <c r="C34" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-002</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="35" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
-      <c r="B35" s="36" t="n">
+      <c r="B35" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="37" t="inlineStr">
+      <c r="C35" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-001</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.7</t>
         </is>
       </c>
-      <c r="B36" s="36" t="n">
+      <c r="B36" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="37" t="inlineStr">
+      <c r="C36" s="38" t="inlineStr">
         <is>
           <t>TC-ACAD-007</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="35" t="inlineStr">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
-      <c r="B37" s="36" t="n">
+      <c r="B37" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="37" t="inlineStr">
+      <c r="C37" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-003</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.9</t>
         </is>
       </c>
-      <c r="B38" s="36" t="n">
+      <c r="B38" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="37" t="inlineStr">
+      <c r="C38" s="38" t="inlineStr">
         <is>
           <t>TC-AI-007</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="35" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
-      <c r="B39" s="36" t="n">
+      <c r="B39" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="37" t="inlineStr">
+      <c r="C39" s="38" t="inlineStr">
         <is>
           <t>TC-MKT-001</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="35" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
-      <c r="B40" s="36" t="n">
+      <c r="B40" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="37" t="inlineStr">
+      <c r="C40" s="38" t="inlineStr">
         <is>
           <t>TC-WF-001, TC-WF-002</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="35" t="inlineStr">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
-      <c r="B41" s="36" t="n">
+      <c r="B41" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="37" t="inlineStr">
+      <c r="C41" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-007, TC-AI-006</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="35" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="B42" s="36" t="n">
+      <c r="B42" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="37" t="inlineStr">
+      <c r="C42" s="38" t="inlineStr">
         <is>
           <t>TC-CAPA-004, TC-DASH-008</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="35" t="inlineStr">
+      <c r="A43" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.1</t>
         </is>
       </c>
-      <c r="B43" s="36" t="n">
+      <c r="B43" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="37" t="inlineStr">
+      <c r="C43" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-001</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="35" t="inlineStr">
+      <c r="A44" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="B44" s="36" t="n">
+      <c r="B44" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="37" t="inlineStr">
+      <c r="C44" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-002, TC-DASH-003, TC-DASH-004, TC-DASH-007, TC-AI-001</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="35" t="inlineStr">
+      <c r="A45" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="B45" s="36" t="n">
+      <c r="B45" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="37" t="inlineStr">
+      <c r="C45" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-005, TC-DASH-006, TC-AI-008</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="35" t="inlineStr">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="B46" s="36" t="n">
+      <c r="B46" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="37" t="inlineStr">
+      <c r="C46" s="38" t="inlineStr">
         <is>
           <t>TC-MKT-002, TC-MKT-003, TC-MKT-004, TC-MKT-005</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="35" t="inlineStr">
+      <c r="A47" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
-      <c r="B47" s="36" t="n">
+      <c r="B47" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="37" t="inlineStr">
+      <c r="C47" s="38" t="inlineStr">
         <is>
           <t>TC-STD-001</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="35" t="inlineStr">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="B48" s="36" t="n">
+      <c r="B48" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="37" t="inlineStr">
+      <c r="C48" s="38" t="inlineStr">
         <is>
           <t>TC-STD-002, TC-STD-004</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="35" t="inlineStr">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="B49" s="36" t="n">
+      <c r="B49" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="37" t="inlineStr">
+      <c r="C49" s="38" t="inlineStr">
         <is>
           <t>TC-STD-003, TC-STD-005</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="35" t="inlineStr">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="B50" s="36" t="n">
+      <c r="B50" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="37" t="inlineStr">
+      <c r="C50" s="38" t="inlineStr">
         <is>
           <t>TC-DOCGEN-001, TC-DOCGEN-003</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="35" t="inlineStr">
+      <c r="A51" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.4</t>
         </is>
       </c>
-      <c r="B51" s="36" t="n">
+      <c r="B51" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="37" t="inlineStr">
+      <c r="C51" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-001</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="35" t="inlineStr">
+      <c r="A52" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.5</t>
         </is>
       </c>
-      <c r="B52" s="36" t="n">
+      <c r="B52" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="37" t="inlineStr">
+      <c r="C52" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-002</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="35" t="inlineStr">
+      <c r="A53" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.8</t>
         </is>
       </c>
-      <c r="B53" s="36" t="n">
+      <c r="B53" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="37" t="inlineStr">
+      <c r="C53" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-004</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="35" t="inlineStr">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.9</t>
         </is>
       </c>
-      <c r="B54" s="36" t="n">
+      <c r="B54" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="37" t="inlineStr">
+      <c r="C54" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-003</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="35" t="inlineStr">
+      <c r="A55" s="36" t="inlineStr">
         <is>
           <t>NIS 2</t>
         </is>
       </c>
-      <c r="B55" s="36" t="n">
+      <c r="B55" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="37" t="inlineStr">
+      <c r="C55" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-010</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="35" t="inlineStr">
+      <c r="A56" s="36" t="inlineStr">
         <is>
           <t>RGPD</t>
         </is>
       </c>
-      <c r="B56" s="36" t="n">
+      <c r="B56" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="37" t="inlineStr">
+      <c r="C56" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-003</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="35" t="inlineStr">
+      <c r="A57" s="36" t="inlineStr">
         <is>
           <t>RGPD §15-22</t>
         </is>
       </c>
-      <c r="B57" s="36" t="n">
+      <c r="B57" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="37" t="inlineStr">
+      <c r="C57" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-004</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="35" t="inlineStr">
+      <c r="A58" s="36" t="inlineStr">
         <is>
           <t>RGPD §28/44</t>
         </is>
       </c>
-      <c r="B58" s="36" t="n">
+      <c r="B58" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="37" t="inlineStr">
+      <c r="C58" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-007</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="35" t="inlineStr">
+      <c r="A59" s="36" t="inlineStr">
         <is>
           <t>RGPD §30</t>
         </is>
       </c>
-      <c r="B59" s="36" t="n">
+      <c r="B59" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="37" t="inlineStr">
+      <c r="C59" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-002</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="35" t="inlineStr">
+      <c r="A60" s="36" t="inlineStr">
         <is>
           <t>RGPD §33</t>
         </is>
       </c>
-      <c r="B60" s="36" t="n">
+      <c r="B60" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="37" t="inlineStr">
+      <c r="C60" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-006</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="35" t="inlineStr">
+      <c r="A61" s="36" t="inlineStr">
         <is>
           <t>RGPD §35</t>
         </is>
       </c>
-      <c r="B61" s="36" t="n">
+      <c r="B61" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="37" t="inlineStr">
+      <c r="C61" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-005</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="35" t="inlineStr">
+      <c r="A62" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B62" s="36" t="n">
+      <c r="B62" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="37" t="inlineStr">
+      <c r="C62" s="38" t="inlineStr">
         <is>
           <t>TC-AUD-004, TC-DOCGEN-004, TC-GRC-001, TC-SEC-002, TC-SEC-003, TC-XCUT-006</t>
         </is>
@@ -12362,7 +12402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12453,7 +12493,7 @@
           <t>IA / NLQ</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12594,7 +12634,7 @@
           <t>Auth</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12716,6 +12756,53 @@
       <c r="I10" s="16" t="inlineStr">
         <is>
           <t>22/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>ANO-007</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Heatmap 5S par zone absente de l'UI</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>5S</t>
+        </is>
+      </c>
+      <c r="D11" s="40" t="inlineStr">
+        <is>
+          <t>Mineure</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>Ouvert</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-005</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>CLAUDE §3.2 prévoit une heatmap de score 5S par zone ; l'UI 5S n'affiche qu'une table. Vision/CV 5S également non câblée (TC-5S-004).</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>À implémenter (feature) — backlog, hors correctif rapide.</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>23/06</t>
         </is>
       </c>
     </row>
@@ -12734,7 +12821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12951,8 +13038,168 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Lot 2</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-001</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>Liste des audits 5S : 4 audits, 1 appel API, 0 scintillement (non-régression).</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-001_liste.png</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="41" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Lot 2</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-002</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Création d'un audit (zone + date) : 4 -&gt; 5. Le dialog n'a pas de champ 'récurrence' (écart mineur vs scénario).</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-002b_apres.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Lot 2</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-003</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>Page /offline-queue accessible. Vérif partielle : l'E2E complet de synchro PWA (service worker) reste un test manuel dédié.</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-003_offline.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Lot 2</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-004</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>Vision YOLOv8 non câblée dans l'UI 5S (détail = textarea simple) et service ai-vision non déployé (ports 8086/8087 down). Non testable en l'état.</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Lot 2</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-005</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>Pas de heatmap par zone dans la feature 5S (table seule). Écart vs CLAUDE §3.2 — consigné en ANO-007.</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -214,12 +214,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D97706"/>
+        <fgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
+        <fgColor rgb="00D97706"/>
       </patternFill>
     </fill>
   </fills>
@@ -302,9 +302,6 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -317,10 +314,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -358,6 +355,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2971,9 +2971,9 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="M14" s="13" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="O14" s="13" t="inlineStr">
         <is>
-          <t>Vision YOLOv8 non câblée dans l'UI 5S + service ai-vision absent (dépendance/env).</t>
+          <t>TC-5S-004_vision-ui.png — Vision CV câblée sur l'audit 5S (UI détail + endpoint backend POST /fives/audits/{id}/vision, 20+9 tests). Service ai-vision absent en test → 503 propre géré par l'UI.</t>
         </is>
       </c>
     </row>
@@ -3048,9 +3048,9 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L15" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
+      <c r="L15" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="M15" s="16" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O15" s="16" t="inlineStr">
         <is>
-          <t>Pas de heatmap par zone dans l'UI 5S (écart vs CLAUDE §3.2) — voir ANO-007.</t>
+          <t>TC-5S-005_heatmap.png — Heatmap zone × mois implémentée (qos-echart, agrégation score moyen).</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -4002,7 +4002,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -5468,7 +5468,7 @@
           <t>Intégration</t>
         </is>
       </c>
-      <c r="F50" s="21" t="inlineStr">
+      <c r="F50" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -6998,7 +6998,7 @@
           <t>IHM/UX</t>
         </is>
       </c>
-      <c r="F72" s="21" t="inlineStr">
+      <c r="F72" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -7626,7 +7626,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F81" s="21" t="inlineStr">
+      <c r="F81" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -7975,7 +7975,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F86" s="21" t="inlineStr">
+      <c r="F86" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -8183,7 +8183,7 @@
           <t>Intégration</t>
         </is>
       </c>
-      <c r="F89" s="21" t="inlineStr">
+      <c r="F89" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -10566,74 +10566,74 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Cas de test</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Exécutés</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>Taux d'exécution</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t>Passés</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>Taux de réussite</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>Échoués</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Bloqués</t>
         </is>
       </c>
-      <c r="O4" s="27" t="inlineStr">
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t>Non exécutés</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="27" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>8.3%</t>
         </is>
       </c>
-      <c r="G5" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="I5" s="30" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="K5" s="31" t="n">
+      <c r="G5" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="29" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="K5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" s="33" t="n">
+      <c r="M5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="32" t="n">
         <v>111</v>
       </c>
     </row>
@@ -10656,32 +10656,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="G9" s="34" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="H9" s="34" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -10694,7 +10694,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10867,12 +10867,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="34" t="inlineStr">
+      <c r="G23" s="33" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="H23" s="34" t="inlineStr">
+      <c r="H23" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -11182,276 +11182,276 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>J01 (23/06)</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" s="35" t="n">
+      <c r="D5" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>J02 (24/06)</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="35" t="n">
+      <c r="F6" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>J03 (25/06)</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>J04 (26/06)</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="34" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="35" t="n">
+      <c r="F8" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>J05 (27/06)</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="34" t="n">
         <v>40</v>
       </c>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n">
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="35" t="n">
+      <c r="F9" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>J06 (28/06)</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n">
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="35" t="n">
+      <c r="F10" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>J07 (29/06)</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="34" t="n">
         <v>56</v>
       </c>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n">
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="35" t="n">
+      <c r="F11" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>J08 (30/06)</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n">
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>J09 (01/07)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="34" t="n">
         <v>73</v>
       </c>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n">
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>J10 (02/07)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="34" t="n">
         <v>81</v>
       </c>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n">
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>J11 (03/07)</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="34" t="n">
         <v>89</v>
       </c>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n">
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>J12 (04/07)</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="34" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>J13 (05/07)</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="34" t="n">
         <v>105</v>
       </c>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="34" t="n"/>
+      <c r="E17" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>J14 (06/07)</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="34" t="n">
         <v>113</v>
       </c>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="35" t="n">
+      <c r="F18" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>J15 (07/07)</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="34" t="n">
         <v>121</v>
       </c>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n">
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="34" t="n"/>
+      <c r="E19" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11518,870 +11518,870 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>ADR 0014</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>TC-AI-010</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-008, TC-GRC-009</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>TC-NC-004, TC-AUD-003, TC-WF-003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §10.2</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-009, TC-STD-006, TC-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>TC-AI-002, TC-AI-003, TC-AI-009</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.3</t>
         </is>
       </c>
-      <c r="B11" s="37" t="n">
+      <c r="B11" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>TC-5S-006, TC-ACAD-005</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.4</t>
         </is>
       </c>
-      <c r="B12" s="37" t="n">
+      <c r="B12" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-008</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="B13" s="37" t="n">
+      <c r="B13" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-003, TC-NC-003, TC-CAPA-003</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §12.3</t>
         </is>
       </c>
-      <c r="B14" s="37" t="n">
+      <c r="B14" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>TC-AI-005</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
-      <c r="B15" s="37" t="n">
+      <c r="B15" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-005</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §14.2</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-007</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
-      <c r="B17" s="37" t="n">
+      <c r="B17" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>TC-XCUT-004, TC-XCUT-007</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
-      <c r="B18" s="37" t="n">
+      <c r="B18" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>TC-XCUT-001, TC-XCUT-002</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>TC-5S-003, TC-XCUT-003, TC-XCUT-005</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §16</t>
         </is>
       </c>
-      <c r="B20" s="37" t="n">
+      <c r="B20" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="38" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-004</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
-      <c r="B21" s="37" t="n">
+      <c r="B21" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-008, TC-DOCGEN-002, TC-SEC-005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="38" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>TC-ACAD-001, TC-ACAD-002, TC-ACAD-003, TC-ACAD-004, TC-ACAD-006</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
         </is>
       </c>
-      <c r="B23" s="37" t="n">
+      <c r="B23" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="38" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-001, TC-PDCA-002, TC-PDCA-003, TC-PDCA-004, TC-PDCA-005, TC-PDCA-006</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="B24" s="37" t="n">
+      <c r="B24" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="38" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>TC-5S-001, TC-5S-002, TC-5S-004, TC-5S-005</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="36" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="B25" s="37" t="n">
+      <c r="B25" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="38" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>TC-CERCLE-001, TC-CERCLE-002, TC-CERCLE-003, TC-CERCLE-004</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="B26" s="37" t="n">
+      <c r="B26" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="38" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>TC-DMAIC-001, TC-DMAIC-002, TC-DMAIC-003, TC-DMAIC-004, TC-AI-004</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="36" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="B27" s="37" t="n">
+      <c r="B27" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="38" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-001, TC-ISHI-002, TC-ISHI-005</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="36" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="B28" s="37" t="n">
+      <c r="B28" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="38" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-004, TC-NC-005</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="B29" s="37" t="n">
+      <c r="B29" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="38" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>TC-DOC-001, TC-DOC-002, TC-DOC-003</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="36" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
-      <c r="B30" s="37" t="n">
+      <c r="B30" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="38" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-004</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="36" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="B31" s="37" t="n">
+      <c r="B31" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="38" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
         <is>
           <t>TC-CAPA-001, TC-CAPA-002</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="B32" s="37" t="n">
+      <c r="B32" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="38" t="inlineStr">
+      <c r="C32" s="37" t="inlineStr">
         <is>
           <t>TC-NC-001, TC-NC-002</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="36" t="inlineStr">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="B33" s="37" t="n">
+      <c r="B33" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="38" t="inlineStr">
+      <c r="C33" s="37" t="inlineStr">
         <is>
           <t>TC-AUD-001, TC-AUD-002</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="36" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
-      <c r="B34" s="37" t="n">
+      <c r="B34" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="38" t="inlineStr">
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-002</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="36" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
-      <c r="B35" s="37" t="n">
+      <c r="B35" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="38" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-001</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="36" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.7</t>
         </is>
       </c>
-      <c r="B36" s="37" t="n">
+      <c r="B36" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="38" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>TC-ACAD-007</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="36" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
-      <c r="B37" s="37" t="n">
+      <c r="B37" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="38" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-003</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="36" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.9</t>
         </is>
       </c>
-      <c r="B38" s="37" t="n">
+      <c r="B38" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="38" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>TC-AI-007</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="36" t="inlineStr">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
-      <c r="B39" s="37" t="n">
+      <c r="B39" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="38" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>TC-MKT-001</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
-      <c r="B40" s="37" t="n">
+      <c r="B40" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="38" t="inlineStr">
+      <c r="C40" s="37" t="inlineStr">
         <is>
           <t>TC-WF-001, TC-WF-002</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="36" t="inlineStr">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
-      <c r="B41" s="37" t="n">
+      <c r="B41" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="38" t="inlineStr">
+      <c r="C41" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-007, TC-AI-006</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="36" t="inlineStr">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="B42" s="37" t="n">
+      <c r="B42" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="38" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
         <is>
           <t>TC-CAPA-004, TC-DASH-008</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.1</t>
         </is>
       </c>
-      <c r="B43" s="37" t="n">
+      <c r="B43" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="38" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-001</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="B44" s="37" t="n">
+      <c r="B44" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="38" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-002, TC-DASH-003, TC-DASH-004, TC-DASH-007, TC-AI-001</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="36" t="inlineStr">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="B45" s="37" t="n">
+      <c r="B45" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="38" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-005, TC-DASH-006, TC-AI-008</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="36" t="inlineStr">
+      <c r="A46" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="B46" s="37" t="n">
+      <c r="B46" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="38" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
         <is>
           <t>TC-MKT-002, TC-MKT-003, TC-MKT-004, TC-MKT-005</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="36" t="inlineStr">
+      <c r="A47" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
-      <c r="B47" s="37" t="n">
+      <c r="B47" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="38" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
         <is>
           <t>TC-STD-001</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="36" t="inlineStr">
+      <c r="A48" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="B48" s="37" t="n">
+      <c r="B48" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="38" t="inlineStr">
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>TC-STD-002, TC-STD-004</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="36" t="inlineStr">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="B49" s="37" t="n">
+      <c r="B49" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="38" t="inlineStr">
+      <c r="C49" s="37" t="inlineStr">
         <is>
           <t>TC-STD-003, TC-STD-005</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="36" t="inlineStr">
+      <c r="A50" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="B50" s="37" t="n">
+      <c r="B50" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="38" t="inlineStr">
+      <c r="C50" s="37" t="inlineStr">
         <is>
           <t>TC-DOCGEN-001, TC-DOCGEN-003</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="36" t="inlineStr">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.4</t>
         </is>
       </c>
-      <c r="B51" s="37" t="n">
+      <c r="B51" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="38" t="inlineStr">
+      <c r="C51" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-001</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="36" t="inlineStr">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.5</t>
         </is>
       </c>
-      <c r="B52" s="37" t="n">
+      <c r="B52" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="38" t="inlineStr">
+      <c r="C52" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-002</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="36" t="inlineStr">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.8</t>
         </is>
       </c>
-      <c r="B53" s="37" t="n">
+      <c r="B53" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="38" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-004</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="36" t="inlineStr">
+      <c r="A54" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.9</t>
         </is>
       </c>
-      <c r="B54" s="37" t="n">
+      <c r="B54" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="38" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-003</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="36" t="inlineStr">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>NIS 2</t>
         </is>
       </c>
-      <c r="B55" s="37" t="n">
+      <c r="B55" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="38" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-010</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="36" t="inlineStr">
+      <c r="A56" s="35" t="inlineStr">
         <is>
           <t>RGPD</t>
         </is>
       </c>
-      <c r="B56" s="37" t="n">
+      <c r="B56" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="38" t="inlineStr">
+      <c r="C56" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-003</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="36" t="inlineStr">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>RGPD §15-22</t>
         </is>
       </c>
-      <c r="B57" s="37" t="n">
+      <c r="B57" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="38" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-004</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="36" t="inlineStr">
+      <c r="A58" s="35" t="inlineStr">
         <is>
           <t>RGPD §28/44</t>
         </is>
       </c>
-      <c r="B58" s="37" t="n">
+      <c r="B58" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="38" t="inlineStr">
+      <c r="C58" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-007</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="36" t="inlineStr">
+      <c r="A59" s="35" t="inlineStr">
         <is>
           <t>RGPD §30</t>
         </is>
       </c>
-      <c r="B59" s="37" t="n">
+      <c r="B59" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="38" t="inlineStr">
+      <c r="C59" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-002</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="36" t="inlineStr">
+      <c r="A60" s="35" t="inlineStr">
         <is>
           <t>RGPD §33</t>
         </is>
       </c>
-      <c r="B60" s="37" t="n">
+      <c r="B60" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="38" t="inlineStr">
+      <c r="C60" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-006</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="36" t="inlineStr">
+      <c r="A61" s="35" t="inlineStr">
         <is>
           <t>RGPD §35</t>
         </is>
       </c>
-      <c r="B61" s="37" t="n">
+      <c r="B61" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="38" t="inlineStr">
+      <c r="C61" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-005</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="36" t="inlineStr">
+      <c r="A62" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B62" s="37" t="n">
+      <c r="B62" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="38" t="inlineStr">
+      <c r="C62" s="37" t="inlineStr">
         <is>
           <t>TC-AUD-004, TC-DOCGEN-004, TC-GRC-001, TC-SEC-002, TC-SEC-003, TC-XCUT-006</t>
         </is>
@@ -12493,7 +12493,7 @@
           <t>IA / NLQ</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12634,7 +12634,7 @@
           <t>Auth</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Heatmap 5S par zone absente de l'UI</t>
+          <t>Heatmap 5S par zone + Vision CV absentes de l'UI</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -12780,24 +12780,24 @@
           <t>Mineure</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>Ouvert</t>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Résolu</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>TC-5S-005</t>
+          <t>TC-5S-005 / TC-5S-004</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
         <is>
-          <t>CLAUDE §3.2 prévoit une heatmap de score 5S par zone ; l'UI 5S n'affiche qu'une table. Vision/CV 5S également non câblée (TC-5S-004).</t>
+          <t>CLAUDE §3.2 prévoit une heatmap de score 5S par zone et la détection CV sur photo ; l'UI 5S n'avait qu'une table.</t>
         </is>
       </c>
       <c r="H11" s="16" t="inlineStr">
         <is>
-          <t>À implémenter (feature) — backlog, hors correctif rapide.</t>
+          <t>Implémenté le 23/06 : heatmap zone×mois (qos-echart) dans la liste 5S ; Vision CV sur l'audit (UI détail + endpoint backend POST /fives/audits/{id}/vision, validateur image mutualisé, 6 langues). 20+9 tests backend verts, build front OK.</t>
         </is>
       </c>
       <c r="I11" s="16" t="inlineStr">
@@ -12821,7 +12821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13150,7 +13150,7 @@
           <t>TC-5S-004</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13182,7 +13182,7 @@
           <t>TC-5S-005</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13198,8 +13198,72 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Correctif ANO-007</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-005</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>Heatmap zone × mois implémentée (qos-echart, score moyen) dans la liste 5S. Smoke : carte + graphe rendus.</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-005_heatmap.png</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="41" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Correctif ANO-007</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-004</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>Vision CV câblée sur l'audit 5S : UI détail (upload + score piliers + findings) + endpoint backend POST /fives/audits/{id}/vision (validateur image mutualisé). 20+9 tests backend verts ; service ai-vision absent → 503 propre géré par l'UI.</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>TC-5S-004_vision-ui.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -214,12 +214,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
+        <fgColor rgb="00D97706"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D97706"/>
+        <fgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
   </fills>
@@ -302,6 +302,9 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -314,10 +317,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -355,9 +358,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3195,18 +3195,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L17" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M17" s="16" t="inlineStr"/>
+      <c r="L17" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N17" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="O17" s="16" t="inlineStr"/>
+      <c r="O17" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-001_liste.png — 4 diagrammes, 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -3265,18 +3273,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L18" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M18" s="13" t="inlineStr"/>
+      <c r="L18" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="O18" s="13" t="inlineStr"/>
+      <c r="O18" s="13" t="inlineStr">
+        <is>
+          <t>TC-ISHI-002_editeur.png — 7 branches (7M) + ajout de cause persisté.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -3335,18 +3351,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L19" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M19" s="16" t="inlineStr"/>
+      <c r="L19" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N19" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="O19" s="16" t="inlineStr"/>
+      <c r="O19" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-003_ia.png — Suggérer (IA) : POST suggest-causes HTTP 200, causes suggérées affichées (ai-service Mistral up).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -3405,18 +3429,26 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L20" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M20" s="13" t="inlineStr"/>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="O20" s="13" t="inlineStr"/>
+      <c r="O20" s="13" t="inlineStr">
+        <is>
+          <t>Pas de bouton « Convertir en PDCA » dans l'UI détail Ishikawa (écart vs CLAUDE §3.6) — voir ANO-008.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -3444,7 +3476,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -3475,18 +3507,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L21" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M21" s="16" t="inlineStr"/>
+      <c r="L21" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N21" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="O21" s="16" t="inlineStr"/>
+      <c r="O21" s="16" t="inlineStr">
+        <is>
+          <t>Action 5-Pourquoi (sous-causes) présente dans le détail.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -4002,7 +4042,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -5468,7 +5508,7 @@
           <t>Intégration</t>
         </is>
       </c>
-      <c r="F50" s="20" t="inlineStr">
+      <c r="F50" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -6998,7 +7038,7 @@
           <t>IHM/UX</t>
         </is>
       </c>
-      <c r="F72" s="20" t="inlineStr">
+      <c r="F72" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -7626,7 +7666,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F81" s="20" t="inlineStr">
+      <c r="F81" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -7975,7 +8015,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F86" s="20" t="inlineStr">
+      <c r="F86" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -8183,7 +8223,7 @@
           <t>Intégration</t>
         </is>
       </c>
-      <c r="F89" s="20" t="inlineStr">
+      <c r="F89" s="21" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -10566,75 +10606,75 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Cas de test</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Exécutés</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Taux d'exécution</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>Passés</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Taux de réussite</t>
         </is>
       </c>
-      <c r="K4" s="24" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>Échoués</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t>Bloqués</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
+      <c r="O4" s="27" t="inlineStr">
         <is>
           <t>Non exécutés</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
+      <c r="A5" s="28" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>8.3%</t>
-        </is>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" s="29" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="K5" s="30" t="n">
+      <c r="C5" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>12.4%</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="I5" s="30" t="inlineStr">
+        <is>
+          <t>93.3%</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>111</v>
+      <c r="M5" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="33" t="n">
+        <v>106</v>
       </c>
     </row>
     <row r="6"/>
@@ -10656,32 +10696,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="G9" s="33" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
+      <c r="H9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -10694,7 +10734,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -10746,7 +10786,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10798,7 +10838,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -10867,12 +10907,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="33" t="inlineStr">
+      <c r="G23" s="34" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="H23" s="33" t="inlineStr">
+      <c r="H23" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -11182,276 +11222,276 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>J01 (23/06)</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="D5" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" s="34" t="n">
+      <c r="C5" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="E5" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="34" t="n">
+      <c r="F5" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>J02 (24/06)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="34" t="n">
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>J03 (25/06)</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="34" t="n"/>
-      <c r="D7" s="34" t="n"/>
-      <c r="E7" s="34" t="n">
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>J04 (26/06)</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n">
+      <c r="B8" s="35" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="34" t="n"/>
-      <c r="D8" s="34" t="n"/>
-      <c r="E8" s="34" t="n">
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>J05 (27/06)</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="35" t="n">
         <v>40</v>
       </c>
-      <c r="C9" s="34" t="n"/>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="34" t="n">
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F9" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>J06 (28/06)</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n">
+      <c r="B10" s="35" t="n">
         <v>48</v>
       </c>
-      <c r="C10" s="34" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="34" t="n">
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="34" t="n">
+      <c r="F10" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>J07 (29/06)</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="35" t="n">
         <v>56</v>
       </c>
-      <c r="C11" s="34" t="n"/>
-      <c r="D11" s="34" t="n"/>
-      <c r="E11" s="34" t="n">
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F11" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>J08 (30/06)</t>
         </is>
       </c>
-      <c r="B12" s="34" t="n">
+      <c r="B12" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="C12" s="34" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="34" t="n">
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F12" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>J09 (01/07)</t>
         </is>
       </c>
-      <c r="B13" s="34" t="n">
+      <c r="B13" s="35" t="n">
         <v>73</v>
       </c>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="34" t="n"/>
-      <c r="E13" s="34" t="n">
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F13" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>J10 (02/07)</t>
         </is>
       </c>
-      <c r="B14" s="34" t="n">
+      <c r="B14" s="35" t="n">
         <v>81</v>
       </c>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n"/>
-      <c r="E14" s="34" t="n">
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="34" t="n">
+      <c r="F14" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>J11 (03/07)</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n">
+      <c r="B15" s="35" t="n">
         <v>89</v>
       </c>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="34" t="n"/>
-      <c r="E15" s="34" t="n">
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="34" t="n">
+      <c r="F15" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>J12 (04/07)</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n">
+      <c r="B16" s="35" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="34" t="n"/>
-      <c r="E16" s="34" t="n">
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F16" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>J13 (05/07)</t>
         </is>
       </c>
-      <c r="B17" s="34" t="n">
+      <c r="B17" s="35" t="n">
         <v>105</v>
       </c>
-      <c r="C17" s="34" t="n"/>
-      <c r="D17" s="34" t="n"/>
-      <c r="E17" s="34" t="n">
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="34" t="n">
+      <c r="F17" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>J14 (06/07)</t>
         </is>
       </c>
-      <c r="B18" s="34" t="n">
+      <c r="B18" s="35" t="n">
         <v>113</v>
       </c>
-      <c r="C18" s="34" t="n"/>
-      <c r="D18" s="34" t="n"/>
-      <c r="E18" s="34" t="n">
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F18" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>J15 (07/07)</t>
         </is>
       </c>
-      <c r="B19" s="34" t="n">
+      <c r="B19" s="35" t="n">
         <v>121</v>
       </c>
-      <c r="C19" s="34" t="n"/>
-      <c r="D19" s="34" t="n"/>
-      <c r="E19" s="34" t="n">
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="34" t="n">
+      <c r="F19" s="35" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11518,870 +11558,870 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>ADR 0014</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n">
+      <c r="B5" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>TC-AI-010</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-008, TC-GRC-009</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>TC-NC-004, TC-AUD-003, TC-WF-003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §10.2</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B8" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-009, TC-STD-006, TC-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n">
+      <c r="B10" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>TC-AI-002, TC-AI-003, TC-AI-009</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.3</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
+      <c r="B11" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>TC-5S-006, TC-ACAD-005</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.4</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
+      <c r="B12" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-008</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n">
+      <c r="B13" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-003, TC-NC-003, TC-CAPA-003</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §12.3</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n">
+      <c r="B14" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>TC-AI-005</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
-      <c r="B15" s="36" t="n">
+      <c r="B15" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-005</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §14.2</t>
         </is>
       </c>
-      <c r="B16" s="36" t="n">
+      <c r="B16" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="37" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-007</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
-      <c r="B17" s="36" t="n">
+      <c r="B17" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="37" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>TC-XCUT-004, TC-XCUT-007</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
-      <c r="B18" s="36" t="n">
+      <c r="B18" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="37" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>TC-XCUT-001, TC-XCUT-002</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n">
+      <c r="B19" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>TC-5S-003, TC-XCUT-003, TC-XCUT-005</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §16</t>
         </is>
       </c>
-      <c r="B20" s="36" t="n">
+      <c r="B20" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="37" t="inlineStr">
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-004</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
-      <c r="B21" s="36" t="n">
+      <c r="B21" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="37" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-008, TC-DOCGEN-002, TC-SEC-005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
-      <c r="B22" s="36" t="n">
+      <c r="B22" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="37" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>TC-ACAD-001, TC-ACAD-002, TC-ACAD-003, TC-ACAD-004, TC-ACAD-006</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
         </is>
       </c>
-      <c r="B23" s="36" t="n">
+      <c r="B23" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="37" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-001, TC-PDCA-002, TC-PDCA-003, TC-PDCA-004, TC-PDCA-005, TC-PDCA-006</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="B24" s="36" t="n">
+      <c r="B24" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="37" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>TC-5S-001, TC-5S-002, TC-5S-004, TC-5S-005</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="B25" s="36" t="n">
+      <c r="B25" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="37" t="inlineStr">
+      <c r="C25" s="38" t="inlineStr">
         <is>
           <t>TC-CERCLE-001, TC-CERCLE-002, TC-CERCLE-003, TC-CERCLE-004</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="B26" s="36" t="n">
+      <c r="B26" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="37" t="inlineStr">
+      <c r="C26" s="38" t="inlineStr">
         <is>
           <t>TC-DMAIC-001, TC-DMAIC-002, TC-DMAIC-003, TC-DMAIC-004, TC-AI-004</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="B27" s="36" t="n">
+      <c r="B27" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="37" t="inlineStr">
+      <c r="C27" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-001, TC-ISHI-002, TC-ISHI-005</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="B28" s="36" t="n">
+      <c r="B28" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="37" t="inlineStr">
+      <c r="C28" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-004, TC-NC-005</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="B29" s="36" t="n">
+      <c r="B29" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="38" t="inlineStr">
         <is>
           <t>TC-DOC-001, TC-DOC-002, TC-DOC-003</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
-      <c r="B30" s="36" t="n">
+      <c r="B30" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="37" t="inlineStr">
+      <c r="C30" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-004</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="B31" s="36" t="n">
+      <c r="B31" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="37" t="inlineStr">
+      <c r="C31" s="38" t="inlineStr">
         <is>
           <t>TC-CAPA-001, TC-CAPA-002</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="B32" s="36" t="n">
+      <c r="B32" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="37" t="inlineStr">
+      <c r="C32" s="38" t="inlineStr">
         <is>
           <t>TC-NC-001, TC-NC-002</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="35" t="inlineStr">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="B33" s="36" t="n">
+      <c r="B33" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="37" t="inlineStr">
+      <c r="C33" s="38" t="inlineStr">
         <is>
           <t>TC-AUD-001, TC-AUD-002</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
-      <c r="B34" s="36" t="n">
+      <c r="B34" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="37" t="inlineStr">
+      <c r="C34" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-002</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="35" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
-      <c r="B35" s="36" t="n">
+      <c r="B35" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="37" t="inlineStr">
+      <c r="C35" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-001</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.7</t>
         </is>
       </c>
-      <c r="B36" s="36" t="n">
+      <c r="B36" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="37" t="inlineStr">
+      <c r="C36" s="38" t="inlineStr">
         <is>
           <t>TC-ACAD-007</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="35" t="inlineStr">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
-      <c r="B37" s="36" t="n">
+      <c r="B37" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="37" t="inlineStr">
+      <c r="C37" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-003</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.9</t>
         </is>
       </c>
-      <c r="B38" s="36" t="n">
+      <c r="B38" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="37" t="inlineStr">
+      <c r="C38" s="38" t="inlineStr">
         <is>
           <t>TC-AI-007</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="35" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
-      <c r="B39" s="36" t="n">
+      <c r="B39" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="37" t="inlineStr">
+      <c r="C39" s="38" t="inlineStr">
         <is>
           <t>TC-MKT-001</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="35" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
-      <c r="B40" s="36" t="n">
+      <c r="B40" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="37" t="inlineStr">
+      <c r="C40" s="38" t="inlineStr">
         <is>
           <t>TC-WF-001, TC-WF-002</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="35" t="inlineStr">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
-      <c r="B41" s="36" t="n">
+      <c r="B41" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="37" t="inlineStr">
+      <c r="C41" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-007, TC-AI-006</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="35" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="B42" s="36" t="n">
+      <c r="B42" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="37" t="inlineStr">
+      <c r="C42" s="38" t="inlineStr">
         <is>
           <t>TC-CAPA-004, TC-DASH-008</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="35" t="inlineStr">
+      <c r="A43" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.1</t>
         </is>
       </c>
-      <c r="B43" s="36" t="n">
+      <c r="B43" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="37" t="inlineStr">
+      <c r="C43" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-001</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="35" t="inlineStr">
+      <c r="A44" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="B44" s="36" t="n">
+      <c r="B44" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="37" t="inlineStr">
+      <c r="C44" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-002, TC-DASH-003, TC-DASH-004, TC-DASH-007, TC-AI-001</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="35" t="inlineStr">
+      <c r="A45" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="B45" s="36" t="n">
+      <c r="B45" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="37" t="inlineStr">
+      <c r="C45" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-005, TC-DASH-006, TC-AI-008</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="35" t="inlineStr">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="B46" s="36" t="n">
+      <c r="B46" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="37" t="inlineStr">
+      <c r="C46" s="38" t="inlineStr">
         <is>
           <t>TC-MKT-002, TC-MKT-003, TC-MKT-004, TC-MKT-005</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="35" t="inlineStr">
+      <c r="A47" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
-      <c r="B47" s="36" t="n">
+      <c r="B47" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="37" t="inlineStr">
+      <c r="C47" s="38" t="inlineStr">
         <is>
           <t>TC-STD-001</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="35" t="inlineStr">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="B48" s="36" t="n">
+      <c r="B48" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="37" t="inlineStr">
+      <c r="C48" s="38" t="inlineStr">
         <is>
           <t>TC-STD-002, TC-STD-004</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="35" t="inlineStr">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="B49" s="36" t="n">
+      <c r="B49" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="37" t="inlineStr">
+      <c r="C49" s="38" t="inlineStr">
         <is>
           <t>TC-STD-003, TC-STD-005</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="35" t="inlineStr">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="B50" s="36" t="n">
+      <c r="B50" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="37" t="inlineStr">
+      <c r="C50" s="38" t="inlineStr">
         <is>
           <t>TC-DOCGEN-001, TC-DOCGEN-003</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="35" t="inlineStr">
+      <c r="A51" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.4</t>
         </is>
       </c>
-      <c r="B51" s="36" t="n">
+      <c r="B51" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="37" t="inlineStr">
+      <c r="C51" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-001</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="35" t="inlineStr">
+      <c r="A52" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.5</t>
         </is>
       </c>
-      <c r="B52" s="36" t="n">
+      <c r="B52" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="37" t="inlineStr">
+      <c r="C52" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-002</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="35" t="inlineStr">
+      <c r="A53" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.8</t>
         </is>
       </c>
-      <c r="B53" s="36" t="n">
+      <c r="B53" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="37" t="inlineStr">
+      <c r="C53" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-004</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="35" t="inlineStr">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.9</t>
         </is>
       </c>
-      <c r="B54" s="36" t="n">
+      <c r="B54" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="37" t="inlineStr">
+      <c r="C54" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-003</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="35" t="inlineStr">
+      <c r="A55" s="36" t="inlineStr">
         <is>
           <t>NIS 2</t>
         </is>
       </c>
-      <c r="B55" s="36" t="n">
+      <c r="B55" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="37" t="inlineStr">
+      <c r="C55" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-010</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="35" t="inlineStr">
+      <c r="A56" s="36" t="inlineStr">
         <is>
           <t>RGPD</t>
         </is>
       </c>
-      <c r="B56" s="36" t="n">
+      <c r="B56" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="37" t="inlineStr">
+      <c r="C56" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-003</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="35" t="inlineStr">
+      <c r="A57" s="36" t="inlineStr">
         <is>
           <t>RGPD §15-22</t>
         </is>
       </c>
-      <c r="B57" s="36" t="n">
+      <c r="B57" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="37" t="inlineStr">
+      <c r="C57" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-004</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="35" t="inlineStr">
+      <c r="A58" s="36" t="inlineStr">
         <is>
           <t>RGPD §28/44</t>
         </is>
       </c>
-      <c r="B58" s="36" t="n">
+      <c r="B58" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="37" t="inlineStr">
+      <c r="C58" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-007</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="35" t="inlineStr">
+      <c r="A59" s="36" t="inlineStr">
         <is>
           <t>RGPD §30</t>
         </is>
       </c>
-      <c r="B59" s="36" t="n">
+      <c r="B59" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="37" t="inlineStr">
+      <c r="C59" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-002</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="35" t="inlineStr">
+      <c r="A60" s="36" t="inlineStr">
         <is>
           <t>RGPD §33</t>
         </is>
       </c>
-      <c r="B60" s="36" t="n">
+      <c r="B60" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="37" t="inlineStr">
+      <c r="C60" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-006</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="35" t="inlineStr">
+      <c r="A61" s="36" t="inlineStr">
         <is>
           <t>RGPD §35</t>
         </is>
       </c>
-      <c r="B61" s="36" t="n">
+      <c r="B61" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="37" t="inlineStr">
+      <c r="C61" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-005</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="35" t="inlineStr">
+      <c r="A62" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B62" s="36" t="n">
+      <c r="B62" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="37" t="inlineStr">
+      <c r="C62" s="38" t="inlineStr">
         <is>
           <t>TC-AUD-004, TC-DOCGEN-004, TC-GRC-001, TC-SEC-002, TC-SEC-003, TC-XCUT-006</t>
         </is>
@@ -12402,7 +12442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12493,7 +12533,7 @@
           <t>IA / NLQ</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12634,7 +12674,7 @@
           <t>Auth</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12801,6 +12841,53 @@
         </is>
       </c>
       <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>23/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>ANO-008</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Conversion Ishikawa → PDCA absente de l'UI</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Ishikawa</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="inlineStr">
+        <is>
+          <t>Mineure</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>Ouvert</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-004</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>CLAUDE §3.6 prévoit la conversion en 1 clic d'un Ishikawa (cause) en cycle PDCA (référentiel commun) ; aucun bouton « Convertir en PDCA » dans le détail Ishikawa.</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>À implémenter (feature) — backlog.</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>23/06</t>
         </is>
@@ -12821,7 +12908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13150,7 +13237,7 @@
           <t>TC-5S-004</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13182,7 +13269,7 @@
           <t>TC-5S-005</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13262,8 +13349,168 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Lot 3</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-001</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>Liste des diagrammes Ishikawa : 4 diagrammes, 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-001_liste.png</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="41" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Lot 3</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-002</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>Éditeur : 7 branches (7M) affichées ; ajout d'une cause persisté via le dialog.</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-002_editeur.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Lot 3</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-003</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>Suggestion IA : POST /ishikawa/diagrams/{id}/suggest-causes → HTTP 200, causes proposées affichées (ai-service Mistral up). 1er run faux négatif (sélecteur Playwright cassé), re-testé OK.</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-003_ia.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Lot 3</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-004</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>Pas de bouton « Convertir en PDCA » dans l'UI détail. Écart vs CLAUDE §3.6 (référentiel commun) — consigné en ANO-008.</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Lot 3</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-005</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>Couplage 5-Pourquoi : ajout de sous-causes disponible dans le détail.</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -214,12 +214,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D97706"/>
+        <fgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
+        <fgColor rgb="00D97706"/>
       </patternFill>
     </fill>
   </fills>
@@ -302,9 +302,6 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -317,10 +314,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -358,6 +355,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3429,9 +3429,9 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L20" s="20" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
+      <c r="L20" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="M20" s="13" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="O20" s="13" t="inlineStr">
         <is>
-          <t>Pas de bouton « Convertir en PDCA » dans l'UI détail Ishikawa (écart vs CLAUDE §3.6) — voir ANO-008.</t>
+          <t>Conversion Ishikawa→PDCA implémentée : bouton « Convertir en PDCA » + endpoint POST /ishikawa/diagrams/{id}/convert-to-pdca (tenant-scopé, cause optionnelle). 42+23 tests backend verts.</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -4042,7 +4042,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -5508,7 +5508,7 @@
           <t>Intégration</t>
         </is>
       </c>
-      <c r="F50" s="21" t="inlineStr">
+      <c r="F50" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -7038,7 +7038,7 @@
           <t>IHM/UX</t>
         </is>
       </c>
-      <c r="F72" s="21" t="inlineStr">
+      <c r="F72" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -7666,7 +7666,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F81" s="21" t="inlineStr">
+      <c r="F81" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -8015,7 +8015,7 @@
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="F86" s="21" t="inlineStr">
+      <c r="F86" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -8223,7 +8223,7 @@
           <t>Intégration</t>
         </is>
       </c>
-      <c r="F89" s="21" t="inlineStr">
+      <c r="F89" s="20" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
@@ -10606,74 +10606,74 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Cas de test</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Exécutés</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>Taux d'exécution</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t>Passés</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>Taux de réussite</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>Échoués</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Bloqués</t>
         </is>
       </c>
-      <c r="O4" s="27" t="inlineStr">
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t>Non exécutés</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="27" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="28" t="n">
         <v>15</v>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>12.4%</t>
         </is>
       </c>
-      <c r="G5" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="I5" s="30" t="inlineStr">
-        <is>
-          <t>93.3%</t>
-        </is>
-      </c>
-      <c r="K5" s="31" t="n">
+      <c r="G5" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" s="29" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="K5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="33" t="n">
+      <c r="M5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="32" t="n">
         <v>106</v>
       </c>
     </row>
@@ -10696,32 +10696,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="G9" s="34" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="H9" s="34" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -10734,7 +10734,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10907,12 +10907,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="34" t="inlineStr">
+      <c r="G23" s="33" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="H23" s="34" t="inlineStr">
+      <c r="H23" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -11222,276 +11222,276 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>J01 (23/06)</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="D5" s="35" t="n">
-        <v>14</v>
-      </c>
-      <c r="E5" s="35" t="n">
+      <c r="D5" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>J02 (24/06)</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="35" t="n">
+      <c r="F6" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>J03 (25/06)</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>J04 (26/06)</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="34" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="35" t="n">
+      <c r="F8" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>J05 (27/06)</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="34" t="n">
         <v>40</v>
       </c>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n">
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="35" t="n">
+      <c r="F9" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>J06 (28/06)</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n">
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="35" t="n">
+      <c r="F10" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>J07 (29/06)</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="34" t="n">
         <v>56</v>
       </c>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n">
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="35" t="n">
+      <c r="F11" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>J08 (30/06)</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n">
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>J09 (01/07)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="34" t="n">
         <v>73</v>
       </c>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n">
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>J10 (02/07)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="34" t="n">
         <v>81</v>
       </c>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n">
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>J11 (03/07)</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="34" t="n">
         <v>89</v>
       </c>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n">
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>J12 (04/07)</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="34" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>J13 (05/07)</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="34" t="n">
         <v>105</v>
       </c>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="34" t="n"/>
+      <c r="E17" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>J14 (06/07)</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="34" t="n">
         <v>113</v>
       </c>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="35" t="n">
+      <c r="F18" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>J15 (07/07)</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="34" t="n">
         <v>121</v>
       </c>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n">
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="34" t="n"/>
+      <c r="E19" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11558,870 +11558,870 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>ADR 0014</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>TC-AI-010</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-008, TC-GRC-009</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>TC-NC-004, TC-AUD-003, TC-WF-003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §10.2</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-009, TC-STD-006, TC-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>TC-AI-002, TC-AI-003, TC-AI-009</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.3</t>
         </is>
       </c>
-      <c r="B11" s="37" t="n">
+      <c r="B11" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>TC-5S-006, TC-ACAD-005</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.4</t>
         </is>
       </c>
-      <c r="B12" s="37" t="n">
+      <c r="B12" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-008</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="B13" s="37" t="n">
+      <c r="B13" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-003, TC-NC-003, TC-CAPA-003</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §12.3</t>
         </is>
       </c>
-      <c r="B14" s="37" t="n">
+      <c r="B14" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>TC-AI-005</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
-      <c r="B15" s="37" t="n">
+      <c r="B15" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-005</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §14.2</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-007</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
-      <c r="B17" s="37" t="n">
+      <c r="B17" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>TC-XCUT-004, TC-XCUT-007</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
-      <c r="B18" s="37" t="n">
+      <c r="B18" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>TC-XCUT-001, TC-XCUT-002</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>TC-5S-003, TC-XCUT-003, TC-XCUT-005</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §16</t>
         </is>
       </c>
-      <c r="B20" s="37" t="n">
+      <c r="B20" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="38" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-004</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
-      <c r="B21" s="37" t="n">
+      <c r="B21" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-008, TC-DOCGEN-002, TC-SEC-005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="38" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>TC-ACAD-001, TC-ACAD-002, TC-ACAD-003, TC-ACAD-004, TC-ACAD-006</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
         </is>
       </c>
-      <c r="B23" s="37" t="n">
+      <c r="B23" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="38" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-001, TC-PDCA-002, TC-PDCA-003, TC-PDCA-004, TC-PDCA-005, TC-PDCA-006</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="B24" s="37" t="n">
+      <c r="B24" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="38" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>TC-5S-001, TC-5S-002, TC-5S-004, TC-5S-005</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="36" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="B25" s="37" t="n">
+      <c r="B25" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="38" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>TC-CERCLE-001, TC-CERCLE-002, TC-CERCLE-003, TC-CERCLE-004</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="B26" s="37" t="n">
+      <c r="B26" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="38" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>TC-DMAIC-001, TC-DMAIC-002, TC-DMAIC-003, TC-DMAIC-004, TC-AI-004</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="36" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="B27" s="37" t="n">
+      <c r="B27" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="38" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-001, TC-ISHI-002, TC-ISHI-005</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="36" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="B28" s="37" t="n">
+      <c r="B28" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="38" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-004, TC-NC-005</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="B29" s="37" t="n">
+      <c r="B29" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="38" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>TC-DOC-001, TC-DOC-002, TC-DOC-003</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="36" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
-      <c r="B30" s="37" t="n">
+      <c r="B30" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="38" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-004</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="36" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="B31" s="37" t="n">
+      <c r="B31" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="38" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
         <is>
           <t>TC-CAPA-001, TC-CAPA-002</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="B32" s="37" t="n">
+      <c r="B32" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="38" t="inlineStr">
+      <c r="C32" s="37" t="inlineStr">
         <is>
           <t>TC-NC-001, TC-NC-002</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="36" t="inlineStr">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="B33" s="37" t="n">
+      <c r="B33" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="38" t="inlineStr">
+      <c r="C33" s="37" t="inlineStr">
         <is>
           <t>TC-AUD-001, TC-AUD-002</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="36" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
-      <c r="B34" s="37" t="n">
+      <c r="B34" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="38" t="inlineStr">
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-002</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="36" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
-      <c r="B35" s="37" t="n">
+      <c r="B35" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="38" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-001</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="36" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.7</t>
         </is>
       </c>
-      <c r="B36" s="37" t="n">
+      <c r="B36" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="38" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>TC-ACAD-007</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="36" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
-      <c r="B37" s="37" t="n">
+      <c r="B37" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="38" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-003</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="36" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.9</t>
         </is>
       </c>
-      <c r="B38" s="37" t="n">
+      <c r="B38" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="38" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>TC-AI-007</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="36" t="inlineStr">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
-      <c r="B39" s="37" t="n">
+      <c r="B39" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="38" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>TC-MKT-001</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
-      <c r="B40" s="37" t="n">
+      <c r="B40" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="38" t="inlineStr">
+      <c r="C40" s="37" t="inlineStr">
         <is>
           <t>TC-WF-001, TC-WF-002</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="36" t="inlineStr">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
-      <c r="B41" s="37" t="n">
+      <c r="B41" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="38" t="inlineStr">
+      <c r="C41" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-007, TC-AI-006</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="36" t="inlineStr">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="B42" s="37" t="n">
+      <c r="B42" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="38" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
         <is>
           <t>TC-CAPA-004, TC-DASH-008</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.1</t>
         </is>
       </c>
-      <c r="B43" s="37" t="n">
+      <c r="B43" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="38" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-001</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="B44" s="37" t="n">
+      <c r="B44" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="38" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-002, TC-DASH-003, TC-DASH-004, TC-DASH-007, TC-AI-001</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="36" t="inlineStr">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="B45" s="37" t="n">
+      <c r="B45" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="38" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-005, TC-DASH-006, TC-AI-008</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="36" t="inlineStr">
+      <c r="A46" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="B46" s="37" t="n">
+      <c r="B46" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="38" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
         <is>
           <t>TC-MKT-002, TC-MKT-003, TC-MKT-004, TC-MKT-005</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="36" t="inlineStr">
+      <c r="A47" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
-      <c r="B47" s="37" t="n">
+      <c r="B47" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="38" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
         <is>
           <t>TC-STD-001</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="36" t="inlineStr">
+      <c r="A48" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="B48" s="37" t="n">
+      <c r="B48" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="38" t="inlineStr">
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>TC-STD-002, TC-STD-004</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="36" t="inlineStr">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="B49" s="37" t="n">
+      <c r="B49" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="38" t="inlineStr">
+      <c r="C49" s="37" t="inlineStr">
         <is>
           <t>TC-STD-003, TC-STD-005</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="36" t="inlineStr">
+      <c r="A50" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="B50" s="37" t="n">
+      <c r="B50" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="38" t="inlineStr">
+      <c r="C50" s="37" t="inlineStr">
         <is>
           <t>TC-DOCGEN-001, TC-DOCGEN-003</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="36" t="inlineStr">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.4</t>
         </is>
       </c>
-      <c r="B51" s="37" t="n">
+      <c r="B51" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="38" t="inlineStr">
+      <c r="C51" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-001</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="36" t="inlineStr">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.5</t>
         </is>
       </c>
-      <c r="B52" s="37" t="n">
+      <c r="B52" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="38" t="inlineStr">
+      <c r="C52" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-002</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="36" t="inlineStr">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.8</t>
         </is>
       </c>
-      <c r="B53" s="37" t="n">
+      <c r="B53" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="38" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-004</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="36" t="inlineStr">
+      <c r="A54" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.9</t>
         </is>
       </c>
-      <c r="B54" s="37" t="n">
+      <c r="B54" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="38" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-003</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="36" t="inlineStr">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>NIS 2</t>
         </is>
       </c>
-      <c r="B55" s="37" t="n">
+      <c r="B55" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="38" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-010</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="36" t="inlineStr">
+      <c r="A56" s="35" t="inlineStr">
         <is>
           <t>RGPD</t>
         </is>
       </c>
-      <c r="B56" s="37" t="n">
+      <c r="B56" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="38" t="inlineStr">
+      <c r="C56" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-003</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="36" t="inlineStr">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>RGPD §15-22</t>
         </is>
       </c>
-      <c r="B57" s="37" t="n">
+      <c r="B57" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="38" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-004</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="36" t="inlineStr">
+      <c r="A58" s="35" t="inlineStr">
         <is>
           <t>RGPD §28/44</t>
         </is>
       </c>
-      <c r="B58" s="37" t="n">
+      <c r="B58" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="38" t="inlineStr">
+      <c r="C58" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-007</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="36" t="inlineStr">
+      <c r="A59" s="35" t="inlineStr">
         <is>
           <t>RGPD §30</t>
         </is>
       </c>
-      <c r="B59" s="37" t="n">
+      <c r="B59" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="38" t="inlineStr">
+      <c r="C59" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-002</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="36" t="inlineStr">
+      <c r="A60" s="35" t="inlineStr">
         <is>
           <t>RGPD §33</t>
         </is>
       </c>
-      <c r="B60" s="37" t="n">
+      <c r="B60" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="38" t="inlineStr">
+      <c r="C60" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-006</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="36" t="inlineStr">
+      <c r="A61" s="35" t="inlineStr">
         <is>
           <t>RGPD §35</t>
         </is>
       </c>
-      <c r="B61" s="37" t="n">
+      <c r="B61" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="38" t="inlineStr">
+      <c r="C61" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-005</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="36" t="inlineStr">
+      <c r="A62" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B62" s="37" t="n">
+      <c r="B62" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="38" t="inlineStr">
+      <c r="C62" s="37" t="inlineStr">
         <is>
           <t>TC-AUD-004, TC-DOCGEN-004, TC-GRC-001, TC-SEC-002, TC-SEC-003, TC-XCUT-006</t>
         </is>
@@ -12533,7 +12533,7 @@
           <t>IA / NLQ</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12674,7 +12674,7 @@
           <t>Auth</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12867,9 +12867,9 @@
           <t>Mineure</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>Ouvert</t>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Résolu</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="H12" s="16" t="inlineStr">
         <is>
-          <t>À implémenter (feature) — backlog.</t>
+          <t>Implémenté le 23/06 : endpoint POST /ishikawa/diagrams/{id}/convert-to-pdca (tenant-scopé, cause optionnelle, réutilise PdcaService) + bouton détail qui navigue vers le cycle créé + i18n 6 langues. Tests : IshikawaServiceTest +4, IshikawaControllerTest +2.</t>
         </is>
       </c>
       <c r="I12" s="16" t="inlineStr">
@@ -12908,7 +12908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13237,7 +13237,7 @@
           <t>TC-5S-004</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13269,7 +13269,7 @@
           <t>TC-5S-005</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13461,7 +13461,7 @@
           <t>TC-ISHI-004</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13509,8 +13509,40 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="41" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Correctif ANO-008</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-004</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>Conversion Ishikawa→PDCA : bouton « Convertir en PDCA » (détail) + endpoint backend POST /ishikawa/diagrams/{id}/convert-to-pdca (tenant-scopé, cause optionnelle, réutilise PdcaService). i18n 6 langues. 42+23 tests backend verts.</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>TC-ISHI-004_convert.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -3584,18 +3584,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L22" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M22" s="13" t="inlineStr"/>
+      <c r="L22" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M22" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N22" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="O22" s="13" t="inlineStr"/>
+      <c r="O22" s="13" t="inlineStr">
+        <is>
+          <t>TC-DMAIC-001_liste.png — liste des projets, 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -3654,18 +3662,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L23" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M23" s="16" t="inlineStr"/>
+      <c r="L23" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N23" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="O23" s="16" t="inlineStr"/>
+      <c r="O23" s="16" t="inlineStr">
+        <is>
+          <t>TC-DMAIC-002_workflow.png — projet créé (ACTIVE/DEFINE), transitions réelles Define→Measure→Analyze (stepper, 2 étapes franchies).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -3724,18 +3740,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L24" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M24" s="13" t="inlineStr"/>
+      <c r="L24" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M24" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N24" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="O24" s="13" t="inlineStr"/>
+      <c r="O24" s="13" t="inlineStr">
+        <is>
+          <t>TC-DMAIC-003_capability.png — capabilité calculée et affichée : Cp 3.55, Cpk 3.46, σ, niveau σ 10.38 (12 mesures + limites de spec).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -3794,18 +3818,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L25" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M25" s="16" t="inlineStr"/>
+      <c r="L25" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N25" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="O25" s="16" t="inlineStr"/>
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>TC-DMAIC-004_pokayoke.png — catalogue Poka-Yoke : 12 dispositifs proposés (filtrables type/mécanisme).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -10652,15 +10684,15 @@
         <v>121</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="G5" s="29" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I5" s="29" t="inlineStr">
         <is>
@@ -10674,7 +10706,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="32" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6"/>
@@ -10734,7 +10766,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -10838,7 +10870,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -11231,10 +11263,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="34" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E5" s="34" t="n">
         <v>6</v>
@@ -12908,7 +12940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13541,8 +13573,136 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Lot 4</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>TC-DMAIC-001</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>Liste des projets DMAIC : 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>TC-DMAIC-001_liste.png</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="41" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Lot 4</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>TC-DMAIC-002</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>Workflow 5 phases : projet créé ACTIVE/DEFINE, transitions réelles Define→Measure→Analyze via « Avancer » (stepper mis à jour).</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>TC-DMAIC-002_workflow.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Lot 4</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>TC-DMAIC-003</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>Capabilité SPC : limites de spec + 12 mesures → Cp 3.55 / Cpk 3.46 / σ / niveau σ calculés et affichés.</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>TC-DMAIC-003_capability.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Lot 4</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>TC-DMAIC-004</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>Poka-Yoke : catalogue de 12 dispositifs (filtrables type/mécanisme) dans le dialog d'assignation. Faux négatif initial (options mat-select hors DOM tant que fermé), re-testé OK.</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>TC-DMAIC-004_pokayoke.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -214,12 +214,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
+        <fgColor rgb="00D97706"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D97706"/>
+        <fgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
   </fills>
@@ -305,6 +305,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -314,10 +317,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -355,9 +358,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3895,18 +3895,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L26" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M26" s="13" t="inlineStr"/>
+      <c r="L26" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M26" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N26" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="O26" s="13" t="inlineStr"/>
+      <c r="O26" s="13" t="inlineStr">
+        <is>
+          <t>TC-CERCLE-001_liste.png — liste des cercles, 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -3965,18 +3973,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L27" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M27" s="16" t="inlineStr"/>
+      <c r="L27" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N27" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="O27" s="16" t="inlineStr"/>
+      <c r="O27" s="16" t="inlineStr">
+        <is>
+          <t>TC-CERCLE-002_membre.png — cercle créé + ajout d'un membre avec rôle.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -4035,18 +4051,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L28" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M28" s="13" t="inlineStr"/>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="O28" s="13" t="inlineStr"/>
+      <c r="O28" s="13" t="inlineStr">
+        <is>
+          <t>Proposition créée mais aucune action de cycle de vie dans l'UI (review/approve/implement/impact) — le backend les expose pourtant → écart UI, voir ANO-009.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -4105,18 +4129,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L29" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M29" s="16" t="inlineStr"/>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N29" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="O29" s="16" t="inlineStr"/>
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>Aucune génération de compte-rendu IA (Whisper + LLM) ni dans l'UI ni au backend — feature non implémentée, voir ANO-010.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -10638,75 +10670,75 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Cas de test</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Exécutés</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Taux d'exécution</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>Passés</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Taux de réussite</t>
         </is>
       </c>
-      <c r="K4" s="24" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>Échoués</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t>Bloqués</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
+      <c r="O4" s="27" t="inlineStr">
         <is>
           <t>Non exécutés</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
+      <c r="A5" s="28" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="28" t="n">
-        <v>19</v>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>15.7%</t>
-        </is>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>19</v>
-      </c>
-      <c r="I5" s="29" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="K5" s="30" t="n">
+      <c r="C5" s="29" t="n">
+        <v>23</v>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>21</v>
+      </c>
+      <c r="I5" s="30" t="inlineStr">
+        <is>
+          <t>91.3%</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>102</v>
+      <c r="M5" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="33" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="6"/>
@@ -10728,32 +10760,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="G9" s="33" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
+      <c r="H9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -10766,7 +10798,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -10818,7 +10850,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10870,7 +10902,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -10939,12 +10971,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="33" t="inlineStr">
+      <c r="G23" s="34" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="H23" s="33" t="inlineStr">
+      <c r="H23" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -11254,276 +11286,276 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>J01 (23/06)</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="34" t="n">
-        <v>19</v>
-      </c>
-      <c r="D5" s="34" t="n">
-        <v>19</v>
-      </c>
-      <c r="E5" s="34" t="n">
+      <c r="C5" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="34" t="n">
+      <c r="F5" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>J02 (24/06)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="34" t="n">
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>J03 (25/06)</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="34" t="n"/>
-      <c r="D7" s="34" t="n"/>
-      <c r="E7" s="34" t="n">
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>J04 (26/06)</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n">
+      <c r="B8" s="35" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="34" t="n"/>
-      <c r="D8" s="34" t="n"/>
-      <c r="E8" s="34" t="n">
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>J05 (27/06)</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="35" t="n">
         <v>40</v>
       </c>
-      <c r="C9" s="34" t="n"/>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="34" t="n">
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F9" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>J06 (28/06)</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n">
+      <c r="B10" s="35" t="n">
         <v>48</v>
       </c>
-      <c r="C10" s="34" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="34" t="n">
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="34" t="n">
+      <c r="F10" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>J07 (29/06)</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="35" t="n">
         <v>56</v>
       </c>
-      <c r="C11" s="34" t="n"/>
-      <c r="D11" s="34" t="n"/>
-      <c r="E11" s="34" t="n">
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F11" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>J08 (30/06)</t>
         </is>
       </c>
-      <c r="B12" s="34" t="n">
+      <c r="B12" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="C12" s="34" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="34" t="n">
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F12" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>J09 (01/07)</t>
         </is>
       </c>
-      <c r="B13" s="34" t="n">
+      <c r="B13" s="35" t="n">
         <v>73</v>
       </c>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="34" t="n"/>
-      <c r="E13" s="34" t="n">
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F13" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>J10 (02/07)</t>
         </is>
       </c>
-      <c r="B14" s="34" t="n">
+      <c r="B14" s="35" t="n">
         <v>81</v>
       </c>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n"/>
-      <c r="E14" s="34" t="n">
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="34" t="n">
+      <c r="F14" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>J11 (03/07)</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n">
+      <c r="B15" s="35" t="n">
         <v>89</v>
       </c>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="34" t="n"/>
-      <c r="E15" s="34" t="n">
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="34" t="n">
+      <c r="F15" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>J12 (04/07)</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n">
+      <c r="B16" s="35" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="34" t="n"/>
-      <c r="E16" s="34" t="n">
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F16" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>J13 (05/07)</t>
         </is>
       </c>
-      <c r="B17" s="34" t="n">
+      <c r="B17" s="35" t="n">
         <v>105</v>
       </c>
-      <c r="C17" s="34" t="n"/>
-      <c r="D17" s="34" t="n"/>
-      <c r="E17" s="34" t="n">
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="34" t="n">
+      <c r="F17" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>J14 (06/07)</t>
         </is>
       </c>
-      <c r="B18" s="34" t="n">
+      <c r="B18" s="35" t="n">
         <v>113</v>
       </c>
-      <c r="C18" s="34" t="n"/>
-      <c r="D18" s="34" t="n"/>
-      <c r="E18" s="34" t="n">
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F18" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>J15 (07/07)</t>
         </is>
       </c>
-      <c r="B19" s="34" t="n">
+      <c r="B19" s="35" t="n">
         <v>121</v>
       </c>
-      <c r="C19" s="34" t="n"/>
-      <c r="D19" s="34" t="n"/>
-      <c r="E19" s="34" t="n">
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="34" t="n">
+      <c r="F19" s="35" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11590,870 +11622,870 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>ADR 0014</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n">
+      <c r="B5" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>TC-AI-010</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-008, TC-GRC-009</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>TC-NC-004, TC-AUD-003, TC-WF-003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §10.2</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B8" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-009, TC-STD-006, TC-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n">
+      <c r="B10" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>TC-AI-002, TC-AI-003, TC-AI-009</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.3</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
+      <c r="B11" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>TC-5S-006, TC-ACAD-005</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.4</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
+      <c r="B12" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-008</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n">
+      <c r="B13" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-003, TC-NC-003, TC-CAPA-003</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §12.3</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n">
+      <c r="B14" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>TC-AI-005</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
-      <c r="B15" s="36" t="n">
+      <c r="B15" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-005</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §14.2</t>
         </is>
       </c>
-      <c r="B16" s="36" t="n">
+      <c r="B16" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="37" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-007</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
-      <c r="B17" s="36" t="n">
+      <c r="B17" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="37" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>TC-XCUT-004, TC-XCUT-007</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
-      <c r="B18" s="36" t="n">
+      <c r="B18" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="37" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>TC-XCUT-001, TC-XCUT-002</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n">
+      <c r="B19" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>TC-5S-003, TC-XCUT-003, TC-XCUT-005</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §16</t>
         </is>
       </c>
-      <c r="B20" s="36" t="n">
+      <c r="B20" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="37" t="inlineStr">
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-004</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
-      <c r="B21" s="36" t="n">
+      <c r="B21" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="37" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-008, TC-DOCGEN-002, TC-SEC-005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
-      <c r="B22" s="36" t="n">
+      <c r="B22" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="37" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>TC-ACAD-001, TC-ACAD-002, TC-ACAD-003, TC-ACAD-004, TC-ACAD-006</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
         </is>
       </c>
-      <c r="B23" s="36" t="n">
+      <c r="B23" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="37" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-001, TC-PDCA-002, TC-PDCA-003, TC-PDCA-004, TC-PDCA-005, TC-PDCA-006</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="B24" s="36" t="n">
+      <c r="B24" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="37" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>TC-5S-001, TC-5S-002, TC-5S-004, TC-5S-005</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="B25" s="36" t="n">
+      <c r="B25" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="37" t="inlineStr">
+      <c r="C25" s="38" t="inlineStr">
         <is>
           <t>TC-CERCLE-001, TC-CERCLE-002, TC-CERCLE-003, TC-CERCLE-004</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="B26" s="36" t="n">
+      <c r="B26" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="37" t="inlineStr">
+      <c r="C26" s="38" t="inlineStr">
         <is>
           <t>TC-DMAIC-001, TC-DMAIC-002, TC-DMAIC-003, TC-DMAIC-004, TC-AI-004</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="B27" s="36" t="n">
+      <c r="B27" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="37" t="inlineStr">
+      <c r="C27" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-001, TC-ISHI-002, TC-ISHI-005</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="B28" s="36" t="n">
+      <c r="B28" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="37" t="inlineStr">
+      <c r="C28" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-004, TC-NC-005</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="B29" s="36" t="n">
+      <c r="B29" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="38" t="inlineStr">
         <is>
           <t>TC-DOC-001, TC-DOC-002, TC-DOC-003</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
-      <c r="B30" s="36" t="n">
+      <c r="B30" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="37" t="inlineStr">
+      <c r="C30" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-004</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="B31" s="36" t="n">
+      <c r="B31" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="37" t="inlineStr">
+      <c r="C31" s="38" t="inlineStr">
         <is>
           <t>TC-CAPA-001, TC-CAPA-002</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="B32" s="36" t="n">
+      <c r="B32" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="37" t="inlineStr">
+      <c r="C32" s="38" t="inlineStr">
         <is>
           <t>TC-NC-001, TC-NC-002</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="35" t="inlineStr">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="B33" s="36" t="n">
+      <c r="B33" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="37" t="inlineStr">
+      <c r="C33" s="38" t="inlineStr">
         <is>
           <t>TC-AUD-001, TC-AUD-002</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
-      <c r="B34" s="36" t="n">
+      <c r="B34" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="37" t="inlineStr">
+      <c r="C34" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-002</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="35" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
-      <c r="B35" s="36" t="n">
+      <c r="B35" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="37" t="inlineStr">
+      <c r="C35" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-001</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.7</t>
         </is>
       </c>
-      <c r="B36" s="36" t="n">
+      <c r="B36" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="37" t="inlineStr">
+      <c r="C36" s="38" t="inlineStr">
         <is>
           <t>TC-ACAD-007</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="35" t="inlineStr">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
-      <c r="B37" s="36" t="n">
+      <c r="B37" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="37" t="inlineStr">
+      <c r="C37" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-003</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.9</t>
         </is>
       </c>
-      <c r="B38" s="36" t="n">
+      <c r="B38" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="37" t="inlineStr">
+      <c r="C38" s="38" t="inlineStr">
         <is>
           <t>TC-AI-007</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="35" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
-      <c r="B39" s="36" t="n">
+      <c r="B39" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="37" t="inlineStr">
+      <c r="C39" s="38" t="inlineStr">
         <is>
           <t>TC-MKT-001</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="35" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
-      <c r="B40" s="36" t="n">
+      <c r="B40" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="37" t="inlineStr">
+      <c r="C40" s="38" t="inlineStr">
         <is>
           <t>TC-WF-001, TC-WF-002</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="35" t="inlineStr">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
-      <c r="B41" s="36" t="n">
+      <c r="B41" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="37" t="inlineStr">
+      <c r="C41" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-007, TC-AI-006</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="35" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="B42" s="36" t="n">
+      <c r="B42" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="37" t="inlineStr">
+      <c r="C42" s="38" t="inlineStr">
         <is>
           <t>TC-CAPA-004, TC-DASH-008</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="35" t="inlineStr">
+      <c r="A43" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.1</t>
         </is>
       </c>
-      <c r="B43" s="36" t="n">
+      <c r="B43" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="37" t="inlineStr">
+      <c r="C43" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-001</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="35" t="inlineStr">
+      <c r="A44" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="B44" s="36" t="n">
+      <c r="B44" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="37" t="inlineStr">
+      <c r="C44" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-002, TC-DASH-003, TC-DASH-004, TC-DASH-007, TC-AI-001</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="35" t="inlineStr">
+      <c r="A45" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="B45" s="36" t="n">
+      <c r="B45" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="37" t="inlineStr">
+      <c r="C45" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-005, TC-DASH-006, TC-AI-008</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="35" t="inlineStr">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="B46" s="36" t="n">
+      <c r="B46" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="37" t="inlineStr">
+      <c r="C46" s="38" t="inlineStr">
         <is>
           <t>TC-MKT-002, TC-MKT-003, TC-MKT-004, TC-MKT-005</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="35" t="inlineStr">
+      <c r="A47" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
-      <c r="B47" s="36" t="n">
+      <c r="B47" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="37" t="inlineStr">
+      <c r="C47" s="38" t="inlineStr">
         <is>
           <t>TC-STD-001</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="35" t="inlineStr">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="B48" s="36" t="n">
+      <c r="B48" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="37" t="inlineStr">
+      <c r="C48" s="38" t="inlineStr">
         <is>
           <t>TC-STD-002, TC-STD-004</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="35" t="inlineStr">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="B49" s="36" t="n">
+      <c r="B49" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="37" t="inlineStr">
+      <c r="C49" s="38" t="inlineStr">
         <is>
           <t>TC-STD-003, TC-STD-005</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="35" t="inlineStr">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="B50" s="36" t="n">
+      <c r="B50" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="37" t="inlineStr">
+      <c r="C50" s="38" t="inlineStr">
         <is>
           <t>TC-DOCGEN-001, TC-DOCGEN-003</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="35" t="inlineStr">
+      <c r="A51" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.4</t>
         </is>
       </c>
-      <c r="B51" s="36" t="n">
+      <c r="B51" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="37" t="inlineStr">
+      <c r="C51" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-001</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="35" t="inlineStr">
+      <c r="A52" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.5</t>
         </is>
       </c>
-      <c r="B52" s="36" t="n">
+      <c r="B52" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="37" t="inlineStr">
+      <c r="C52" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-002</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="35" t="inlineStr">
+      <c r="A53" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.8</t>
         </is>
       </c>
-      <c r="B53" s="36" t="n">
+      <c r="B53" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="37" t="inlineStr">
+      <c r="C53" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-004</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="35" t="inlineStr">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.9</t>
         </is>
       </c>
-      <c r="B54" s="36" t="n">
+      <c r="B54" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="37" t="inlineStr">
+      <c r="C54" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-003</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="35" t="inlineStr">
+      <c r="A55" s="36" t="inlineStr">
         <is>
           <t>NIS 2</t>
         </is>
       </c>
-      <c r="B55" s="36" t="n">
+      <c r="B55" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="37" t="inlineStr">
+      <c r="C55" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-010</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="35" t="inlineStr">
+      <c r="A56" s="36" t="inlineStr">
         <is>
           <t>RGPD</t>
         </is>
       </c>
-      <c r="B56" s="36" t="n">
+      <c r="B56" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="37" t="inlineStr">
+      <c r="C56" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-003</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="35" t="inlineStr">
+      <c r="A57" s="36" t="inlineStr">
         <is>
           <t>RGPD §15-22</t>
         </is>
       </c>
-      <c r="B57" s="36" t="n">
+      <c r="B57" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="37" t="inlineStr">
+      <c r="C57" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-004</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="35" t="inlineStr">
+      <c r="A58" s="36" t="inlineStr">
         <is>
           <t>RGPD §28/44</t>
         </is>
       </c>
-      <c r="B58" s="36" t="n">
+      <c r="B58" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="37" t="inlineStr">
+      <c r="C58" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-007</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="35" t="inlineStr">
+      <c r="A59" s="36" t="inlineStr">
         <is>
           <t>RGPD §30</t>
         </is>
       </c>
-      <c r="B59" s="36" t="n">
+      <c r="B59" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="37" t="inlineStr">
+      <c r="C59" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-002</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="35" t="inlineStr">
+      <c r="A60" s="36" t="inlineStr">
         <is>
           <t>RGPD §33</t>
         </is>
       </c>
-      <c r="B60" s="36" t="n">
+      <c r="B60" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="37" t="inlineStr">
+      <c r="C60" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-006</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="35" t="inlineStr">
+      <c r="A61" s="36" t="inlineStr">
         <is>
           <t>RGPD §35</t>
         </is>
       </c>
-      <c r="B61" s="36" t="n">
+      <c r="B61" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="37" t="inlineStr">
+      <c r="C61" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-005</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="35" t="inlineStr">
+      <c r="A62" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B62" s="36" t="n">
+      <c r="B62" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="37" t="inlineStr">
+      <c r="C62" s="38" t="inlineStr">
         <is>
           <t>TC-AUD-004, TC-DOCGEN-004, TC-GRC-001, TC-SEC-002, TC-SEC-003, TC-XCUT-006</t>
         </is>
@@ -12474,7 +12506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12565,7 +12597,7 @@
           <t>IA / NLQ</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12706,7 +12738,7 @@
           <t>Auth</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12920,6 +12952,100 @@
         </is>
       </c>
       <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>23/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>ANO-009</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Cycle de vie des propositions de cercle absent de l'UI</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Cercles</t>
+        </is>
+      </c>
+      <c r="D13" s="40" t="inlineStr">
+        <is>
+          <t>Mineure</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>Ouvert</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>TC-CERCLE-003</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>Le backend (CircleController) expose review/approve/reject/implement/impact sur les propositions (CLAUDE §3.3 : statut, validation, mise en œuvre, mesure d'impact), mais l'UI ne propose que la création + l'affichage du statut.</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>À implémenter côté front (backend prêt) : boutons d'action + saisie de la mesure d'impact.</t>
+        </is>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>23/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>ANO-010</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Compte-rendu de réunion auto-généré (Whisper + LLM) absent</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Cercles</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>Majeure</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>Ouvert</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>TC-CERCLE-004</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>CLAUDE §3.3 prévoit des comptes-rendus auto-générés (transcription Whisper + résumé LLM) ; ni l'UI ni le backend ne le proposent (meetings = planification seule).</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>Feature lourde (upload audio + transcription + LLM) — backlog, à cadrer.</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>23/06</t>
         </is>
@@ -12940,7 +13066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13269,7 +13395,7 @@
           <t>TC-5S-004</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13301,7 +13427,7 @@
           <t>TC-5S-005</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13493,7 +13619,7 @@
           <t>TC-ISHI-004</t>
         </is>
       </c>
-      <c r="D20" s="38" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13701,8 +13827,136 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Lot 5</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>TC-CERCLE-001</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>Liste des cercles : 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>TC-CERCLE-001_liste.png</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="41" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Lot 5</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>TC-CERCLE-002</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>Création d'un cercle + ajout d'un membre avec rôle (dialog membre).</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>TC-CERCLE-002_membre.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Lot 5</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>TC-CERCLE-003</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>Proposition créée et affichée (statut PROPOSED), mais aucune action de cycle de vie dans l'UI. Le backend expose pourtant review/approve/reject/implement/impact (CircleController) → écart UI. Consigné ANO-009.</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>TC-CERCLE-003_proposition.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Lot 5</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>TC-CERCLE-004</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>Compte-rendu auto-généré (Whisper + LLM) absent de l'UI et du backend (meetings = planification seule). Feature non implémentée. Consigné ANO-010.</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -214,12 +214,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D97706"/>
+        <fgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
+        <fgColor rgb="00D97706"/>
       </patternFill>
     </fill>
   </fills>
@@ -305,9 +305,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -317,10 +314,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -358,6 +355,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4051,9 +4051,9 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
+      <c r="L28" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="M28" s="13" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="O28" s="13" t="inlineStr">
         <is>
-          <t>Proposition créée mais aucune action de cycle de vie dans l'UI (review/approve/implement/impact) — le backend les expose pourtant → écart UI, voir ANO-009.</t>
+          <t>Résolu via ANO-009 : cycle de vie des propositions câblé dans l'UI (review/approve/reject/implement/impact + saisie d'impact). Build front + 41+58 tests backend circle verts (re-test E2E recommandé).</t>
         </is>
       </c>
     </row>
@@ -4129,9 +4129,9 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L29" s="21" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
+      <c r="L29" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="M29" s="16" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O29" s="16" t="inlineStr">
         <is>
-          <t>Aucune génération de compte-rendu IA (Whisper + LLM) ni dans l'UI ni au backend — feature non implémentée, voir ANO-010.</t>
+          <t>Résolu via ANO-010 : compte-rendu de réunion généré par LLM (résumé + décisions + actions) via AiGateway. Backend (V97 + endpoint) + UI ; 41+58 tests circle verts (Whisper audio en étape future, ADR 0044).</t>
         </is>
       </c>
     </row>
@@ -4206,18 +4206,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L30" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M30" s="13" t="inlineStr"/>
+      <c r="L30" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M30" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N30" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="O30" s="13" t="inlineStr"/>
+      <c r="O30" s="13" t="inlineStr">
+        <is>
+          <t>TC-NC-001_liste.png — liste NC, 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -4277,18 +4285,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L31" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M31" s="16" t="inlineStr"/>
+      <c r="L31" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N31" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="O31" s="16" t="inlineStr"/>
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>TC-NC-002_creation.png — NC créée (titre/catégorie/sévérité/zone). NB : photo ajoutée en détail, géoloc absente du dialog de saisie (écart mineur).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -4347,18 +4363,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L32" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M32" s="13" t="inlineStr"/>
+      <c r="L32" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M32" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N32" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="O32" s="13" t="inlineStr"/>
+      <c r="O32" s="13" t="inlineStr">
+        <is>
+          <t>TC-NC-003_clustering.png — clustering DBSCAN : clusters calculés depuis des NC saisies (/nc-clusters, ai-service).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -4417,18 +4441,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L33" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M33" s="16" t="inlineStr"/>
+      <c r="L33" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N33" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="O33" s="16" t="inlineStr"/>
+      <c r="O33" s="16" t="inlineStr">
+        <is>
+          <t>Carte Vision câblée dans le détail NC ; analyse → 503 propre géré (service ai-vision non déployé).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
@@ -4487,18 +4519,26 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L34" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M34" s="13" t="inlineStr"/>
+      <c r="L34" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M34" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N34" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="O34" s="13" t="inlineStr"/>
+      <c r="O34" s="13" t="inlineStr">
+        <is>
+          <t>TC-NC-005_escalade.png — NC escaladée en CAPA (lien CAPA affiché) — référentiel commun §3.6.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -10670,75 +10710,75 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Cas de test</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Exécutés</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>Taux d'exécution</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t>Passés</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>Taux de réussite</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>Échoués</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Bloqués</t>
         </is>
       </c>
-      <c r="O4" s="27" t="inlineStr">
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t>Non exécutés</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="27" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="29" t="n">
-        <v>23</v>
-      </c>
-      <c r="E5" s="29" t="inlineStr">
-        <is>
-          <t>19.0%</t>
-        </is>
-      </c>
-      <c r="G5" s="30" t="n">
-        <v>21</v>
-      </c>
-      <c r="I5" s="30" t="inlineStr">
-        <is>
-          <t>91.3%</t>
-        </is>
-      </c>
-      <c r="K5" s="31" t="n">
+      <c r="C5" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="n">
+        <v>28</v>
+      </c>
+      <c r="I5" s="29" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="K5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" s="33" t="n">
-        <v>98</v>
+      <c r="M5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="32" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="6"/>
@@ -10760,32 +10800,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="G9" s="34" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="H9" s="34" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -10798,7 +10838,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -10850,7 +10890,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10902,7 +10942,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -10971,12 +11011,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="34" t="inlineStr">
+      <c r="G23" s="33" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="H23" s="34" t="inlineStr">
+      <c r="H23" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -11286,276 +11326,276 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>J01 (23/06)</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="35" t="n">
-        <v>23</v>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>21</v>
-      </c>
-      <c r="E5" s="35" t="n">
+      <c r="C5" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="E5" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>J02 (24/06)</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="35" t="n">
+      <c r="F6" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>J03 (25/06)</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>J04 (26/06)</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="34" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="35" t="n">
+      <c r="F8" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>J05 (27/06)</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="34" t="n">
         <v>40</v>
       </c>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n">
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="35" t="n">
+      <c r="F9" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>J06 (28/06)</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n">
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="35" t="n">
+      <c r="F10" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>J07 (29/06)</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="34" t="n">
         <v>56</v>
       </c>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n">
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="35" t="n">
+      <c r="F11" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>J08 (30/06)</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n">
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>J09 (01/07)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="34" t="n">
         <v>73</v>
       </c>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n">
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>J10 (02/07)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="34" t="n">
         <v>81</v>
       </c>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n">
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>J11 (03/07)</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="34" t="n">
         <v>89</v>
       </c>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n">
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>J12 (04/07)</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="34" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>J13 (05/07)</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="34" t="n">
         <v>105</v>
       </c>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="34" t="n"/>
+      <c r="E17" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>J14 (06/07)</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="34" t="n">
         <v>113</v>
       </c>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="35" t="n">
+      <c r="F18" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>J15 (07/07)</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="34" t="n">
         <v>121</v>
       </c>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n">
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="34" t="n"/>
+      <c r="E19" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11622,870 +11662,870 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>ADR 0014</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>TC-AI-010</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-008, TC-GRC-009</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>TC-NC-004, TC-AUD-003, TC-WF-003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §10.2</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-009, TC-STD-006, TC-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>TC-AI-002, TC-AI-003, TC-AI-009</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.3</t>
         </is>
       </c>
-      <c r="B11" s="37" t="n">
+      <c r="B11" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>TC-5S-006, TC-ACAD-005</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.4</t>
         </is>
       </c>
-      <c r="B12" s="37" t="n">
+      <c r="B12" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-008</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="B13" s="37" t="n">
+      <c r="B13" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-003, TC-NC-003, TC-CAPA-003</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §12.3</t>
         </is>
       </c>
-      <c r="B14" s="37" t="n">
+      <c r="B14" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>TC-AI-005</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
-      <c r="B15" s="37" t="n">
+      <c r="B15" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-005</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §14.2</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-007</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
-      <c r="B17" s="37" t="n">
+      <c r="B17" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>TC-XCUT-004, TC-XCUT-007</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
-      <c r="B18" s="37" t="n">
+      <c r="B18" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>TC-XCUT-001, TC-XCUT-002</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>TC-5S-003, TC-XCUT-003, TC-XCUT-005</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §16</t>
         </is>
       </c>
-      <c r="B20" s="37" t="n">
+      <c r="B20" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="38" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-004</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
-      <c r="B21" s="37" t="n">
+      <c r="B21" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-008, TC-DOCGEN-002, TC-SEC-005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="38" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>TC-ACAD-001, TC-ACAD-002, TC-ACAD-003, TC-ACAD-004, TC-ACAD-006</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
         </is>
       </c>
-      <c r="B23" s="37" t="n">
+      <c r="B23" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="38" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-001, TC-PDCA-002, TC-PDCA-003, TC-PDCA-004, TC-PDCA-005, TC-PDCA-006</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="B24" s="37" t="n">
+      <c r="B24" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="38" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>TC-5S-001, TC-5S-002, TC-5S-004, TC-5S-005</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="36" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="B25" s="37" t="n">
+      <c r="B25" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="38" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>TC-CERCLE-001, TC-CERCLE-002, TC-CERCLE-003, TC-CERCLE-004</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="B26" s="37" t="n">
+      <c r="B26" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="38" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>TC-DMAIC-001, TC-DMAIC-002, TC-DMAIC-003, TC-DMAIC-004, TC-AI-004</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="36" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="B27" s="37" t="n">
+      <c r="B27" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="38" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-001, TC-ISHI-002, TC-ISHI-005</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="36" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="B28" s="37" t="n">
+      <c r="B28" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="38" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-004, TC-NC-005</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="B29" s="37" t="n">
+      <c r="B29" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="38" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>TC-DOC-001, TC-DOC-002, TC-DOC-003</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="36" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
-      <c r="B30" s="37" t="n">
+      <c r="B30" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="38" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-004</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="36" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="B31" s="37" t="n">
+      <c r="B31" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="38" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
         <is>
           <t>TC-CAPA-001, TC-CAPA-002</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="B32" s="37" t="n">
+      <c r="B32" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="38" t="inlineStr">
+      <c r="C32" s="37" t="inlineStr">
         <is>
           <t>TC-NC-001, TC-NC-002</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="36" t="inlineStr">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="B33" s="37" t="n">
+      <c r="B33" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="38" t="inlineStr">
+      <c r="C33" s="37" t="inlineStr">
         <is>
           <t>TC-AUD-001, TC-AUD-002</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="36" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
-      <c r="B34" s="37" t="n">
+      <c r="B34" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="38" t="inlineStr">
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-002</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="36" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
-      <c r="B35" s="37" t="n">
+      <c r="B35" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="38" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-001</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="36" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.7</t>
         </is>
       </c>
-      <c r="B36" s="37" t="n">
+      <c r="B36" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="38" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>TC-ACAD-007</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="36" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
-      <c r="B37" s="37" t="n">
+      <c r="B37" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="38" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-003</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="36" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.9</t>
         </is>
       </c>
-      <c r="B38" s="37" t="n">
+      <c r="B38" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="38" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>TC-AI-007</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="36" t="inlineStr">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
-      <c r="B39" s="37" t="n">
+      <c r="B39" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="38" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>TC-MKT-001</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
-      <c r="B40" s="37" t="n">
+      <c r="B40" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="38" t="inlineStr">
+      <c r="C40" s="37" t="inlineStr">
         <is>
           <t>TC-WF-001, TC-WF-002</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="36" t="inlineStr">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
-      <c r="B41" s="37" t="n">
+      <c r="B41" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="38" t="inlineStr">
+      <c r="C41" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-007, TC-AI-006</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="36" t="inlineStr">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="B42" s="37" t="n">
+      <c r="B42" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="38" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
         <is>
           <t>TC-CAPA-004, TC-DASH-008</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.1</t>
         </is>
       </c>
-      <c r="B43" s="37" t="n">
+      <c r="B43" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="38" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-001</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="B44" s="37" t="n">
+      <c r="B44" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="38" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-002, TC-DASH-003, TC-DASH-004, TC-DASH-007, TC-AI-001</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="36" t="inlineStr">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="B45" s="37" t="n">
+      <c r="B45" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="38" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-005, TC-DASH-006, TC-AI-008</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="36" t="inlineStr">
+      <c r="A46" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="B46" s="37" t="n">
+      <c r="B46" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="38" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
         <is>
           <t>TC-MKT-002, TC-MKT-003, TC-MKT-004, TC-MKT-005</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="36" t="inlineStr">
+      <c r="A47" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
-      <c r="B47" s="37" t="n">
+      <c r="B47" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="38" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
         <is>
           <t>TC-STD-001</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="36" t="inlineStr">
+      <c r="A48" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="B48" s="37" t="n">
+      <c r="B48" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="38" t="inlineStr">
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>TC-STD-002, TC-STD-004</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="36" t="inlineStr">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="B49" s="37" t="n">
+      <c r="B49" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="38" t="inlineStr">
+      <c r="C49" s="37" t="inlineStr">
         <is>
           <t>TC-STD-003, TC-STD-005</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="36" t="inlineStr">
+      <c r="A50" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="B50" s="37" t="n">
+      <c r="B50" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="38" t="inlineStr">
+      <c r="C50" s="37" t="inlineStr">
         <is>
           <t>TC-DOCGEN-001, TC-DOCGEN-003</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="36" t="inlineStr">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.4</t>
         </is>
       </c>
-      <c r="B51" s="37" t="n">
+      <c r="B51" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="38" t="inlineStr">
+      <c r="C51" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-001</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="36" t="inlineStr">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.5</t>
         </is>
       </c>
-      <c r="B52" s="37" t="n">
+      <c r="B52" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="38" t="inlineStr">
+      <c r="C52" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-002</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="36" t="inlineStr">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.8</t>
         </is>
       </c>
-      <c r="B53" s="37" t="n">
+      <c r="B53" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="38" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-004</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="36" t="inlineStr">
+      <c r="A54" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.9</t>
         </is>
       </c>
-      <c r="B54" s="37" t="n">
+      <c r="B54" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="38" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-003</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="36" t="inlineStr">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>NIS 2</t>
         </is>
       </c>
-      <c r="B55" s="37" t="n">
+      <c r="B55" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="38" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-010</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="36" t="inlineStr">
+      <c r="A56" s="35" t="inlineStr">
         <is>
           <t>RGPD</t>
         </is>
       </c>
-      <c r="B56" s="37" t="n">
+      <c r="B56" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="38" t="inlineStr">
+      <c r="C56" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-003</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="36" t="inlineStr">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>RGPD §15-22</t>
         </is>
       </c>
-      <c r="B57" s="37" t="n">
+      <c r="B57" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="38" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-004</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="36" t="inlineStr">
+      <c r="A58" s="35" t="inlineStr">
         <is>
           <t>RGPD §28/44</t>
         </is>
       </c>
-      <c r="B58" s="37" t="n">
+      <c r="B58" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="38" t="inlineStr">
+      <c r="C58" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-007</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="36" t="inlineStr">
+      <c r="A59" s="35" t="inlineStr">
         <is>
           <t>RGPD §30</t>
         </is>
       </c>
-      <c r="B59" s="37" t="n">
+      <c r="B59" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="38" t="inlineStr">
+      <c r="C59" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-002</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="36" t="inlineStr">
+      <c r="A60" s="35" t="inlineStr">
         <is>
           <t>RGPD §33</t>
         </is>
       </c>
-      <c r="B60" s="37" t="n">
+      <c r="B60" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="38" t="inlineStr">
+      <c r="C60" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-006</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="36" t="inlineStr">
+      <c r="A61" s="35" t="inlineStr">
         <is>
           <t>RGPD §35</t>
         </is>
       </c>
-      <c r="B61" s="37" t="n">
+      <c r="B61" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="38" t="inlineStr">
+      <c r="C61" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-005</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="36" t="inlineStr">
+      <c r="A62" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B62" s="37" t="n">
+      <c r="B62" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="38" t="inlineStr">
+      <c r="C62" s="37" t="inlineStr">
         <is>
           <t>TC-AUD-004, TC-DOCGEN-004, TC-GRC-001, TC-SEC-002, TC-SEC-003, TC-XCUT-006</t>
         </is>
@@ -12597,7 +12637,7 @@
           <t>IA / NLQ</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12738,7 +12778,7 @@
           <t>Auth</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12978,9 +13018,9 @@
           <t>Mineure</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>Ouvert</t>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Résolu</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -12990,12 +13030,12 @@
       </c>
       <c r="G13" s="16" t="inlineStr">
         <is>
-          <t>Le backend (CircleController) expose review/approve/reject/implement/impact sur les propositions (CLAUDE §3.3 : statut, validation, mise en œuvre, mesure d'impact), mais l'UI ne propose que la création + l'affichage du statut.</t>
+          <t>Le backend (CircleController) expose review/approve/reject/implement/impact sur les propositions (CLAUDE §3.3), mais l'UI ne proposait que la création + l'affichage du statut.</t>
         </is>
       </c>
       <c r="H13" s="16" t="inlineStr">
         <is>
-          <t>À implémenter côté front (backend prêt) : boutons d'action + saisie de la mesure d'impact.</t>
+          <t>Implémenté le 23/06 (agent parallèle) : 5 méthodes service + boutons conditionnés par statut + dialogs reject (motif) et impact (mesure) ; i18n 6 langues. Build front + 41+58 tests circle verts.</t>
         </is>
       </c>
       <c r="I13" s="16" t="inlineStr">
@@ -13012,7 +13052,7 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Compte-rendu de réunion auto-généré (Whisper + LLM) absent</t>
+          <t>Compte-rendu de réunion auto-généré (LLM) absent</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -13020,14 +13060,14 @@
           <t>Cercles</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>Ouvert</t>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Résolu</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -13037,12 +13077,12 @@
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>CLAUDE §3.3 prévoit des comptes-rendus auto-générés (transcription Whisper + résumé LLM) ; ni l'UI ni le backend ne le proposent (meetings = planification seule).</t>
+          <t>CLAUDE §3.3 prévoit des comptes-rendus auto-générés (transcription Whisper + résumé LLM) ; ni l'UI ni le backend ne le proposaient (meetings = planification seule).</t>
         </is>
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>Feature lourde (upload audio + transcription + LLM) — backlog, à cadrer.</t>
+          <t>Implémenté le 23/06 (agent parallèle, ADR 0044) : endpoint POST /circles/{id}/meetings/{mid}/minutes/generate via AiGateway (résumé+décisions+actions), persistance (migration V97), UI dédiée. Transcription Whisper audio→texte documentée en étape future.</t>
         </is>
       </c>
       <c r="I14" s="16" t="inlineStr">
@@ -13066,7 +13106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13395,7 +13435,7 @@
           <t>TC-5S-004</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13427,7 +13467,7 @@
           <t>TC-5S-005</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13619,7 +13659,7 @@
           <t>TC-ISHI-004</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13907,7 +13947,7 @@
           <t>TC-CERCLE-003</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13939,7 +13979,7 @@
           <t>TC-CERCLE-004</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13955,8 +13995,168 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Lot 6</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>TC-NC-001</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>Liste des non-conformités : 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>TC-NC-001_liste.png</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
-      <c r="A32" s="41" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Lot 6</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>TC-NC-002</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>Déclaration d'une NC (titre/catégorie/sévérité/zone). Photo en détail, géoloc absente du dialog (note).</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>TC-NC-002_creation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>Lot 6</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>TC-NC-003</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>Clustering DBSCAN : regroupement de NC similaires saisies (/nc-clusters → ai-service).</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>TC-NC-003_clustering.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Lot 6</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>TC-NC-004</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>Analyse Vision d'une photo de NC : carte câblée ; 503 propre géré (ai-vision non déployé en test).</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Lot 6</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>TC-NC-005</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>Intégration NC → CAPA : escalade créant une CAPA liée (lien affiché).</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>TC-NC-005_escalade.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -214,12 +214,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
+        <fgColor rgb="00D97706"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D97706"/>
+        <fgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
   </fills>
@@ -305,6 +305,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -314,10 +317,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -355,9 +358,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4596,18 +4596,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L35" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M35" s="16" t="inlineStr"/>
+      <c r="L35" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N35" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="O35" s="16" t="inlineStr"/>
+      <c r="O35" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-001_liste.png — liste des dossiers CAPA, 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
@@ -4666,18 +4674,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L36" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M36" s="13" t="inlineStr"/>
+      <c r="L36" s="21" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="M36" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N36" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="O36" s="13" t="inlineStr"/>
+      <c r="O36" s="13" t="inlineStr">
+        <is>
+          <t>Démarrage OK (OPEN→IN_PROGRESS) mais clôture IMPOSSIBLE via l'UI : la résolution exige ≥1 action DONE (règle ISO 9001 §10.2 correcte), or la table d'actions est en lecture seule (aucun avancement action→DONE). Backend PATCH /cases/{id}/actions/{actionId} (champ status) prêt → écart UI, voir ANO-011.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -4736,18 +4752,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L37" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M37" s="16" t="inlineStr"/>
+      <c r="L37" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N37" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="O37" s="16" t="inlineStr"/>
+      <c r="O37" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-003_ia.png — Suggérer (IA) : POST suggest-actions HTTP 200 (ai-service Mistral).</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
@@ -4805,18 +4829,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L38" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M38" s="13" t="inlineStr"/>
+      <c r="L38" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M38" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N38" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="O38" s="13" t="inlineStr"/>
+      <c r="O38" s="13" t="inlineStr">
+        <is>
+          <t>TC-CAPA-004_kpi.png — KPI « Délai moyen clôture CAPA » présent sur le dashboard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
@@ -10710,75 +10742,75 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Cas de test</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Exécutés</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Taux d'exécution</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>Passés</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Taux de réussite</t>
         </is>
       </c>
-      <c r="K4" s="24" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>Échoués</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t>Bloqués</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
+      <c r="O4" s="27" t="inlineStr">
         <is>
           <t>Non exécutés</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
+      <c r="A5" s="28" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="28" t="n">
-        <v>28</v>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>28</v>
-      </c>
-      <c r="I5" s="29" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="K5" s="30" t="n">
+      <c r="C5" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>26.4%</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>31</v>
+      </c>
+      <c r="I5" s="30" t="inlineStr">
+        <is>
+          <t>96.9%</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>93</v>
+      <c r="M5" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="33" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="6"/>
@@ -10800,32 +10832,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="G9" s="33" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
+      <c r="H9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -10838,7 +10870,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -10890,7 +10922,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10942,7 +10974,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -11011,12 +11043,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="33" t="inlineStr">
+      <c r="G23" s="34" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="H23" s="33" t="inlineStr">
+      <c r="H23" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -11326,276 +11358,276 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>J01 (23/06)</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="34" t="n">
-        <v>28</v>
-      </c>
-      <c r="D5" s="34" t="n">
-        <v>28</v>
-      </c>
-      <c r="E5" s="34" t="n">
+      <c r="C5" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="E5" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="34" t="n">
+      <c r="F5" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>J02 (24/06)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="34" t="n">
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>J03 (25/06)</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="34" t="n"/>
-      <c r="D7" s="34" t="n"/>
-      <c r="E7" s="34" t="n">
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>J04 (26/06)</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n">
+      <c r="B8" s="35" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="34" t="n"/>
-      <c r="D8" s="34" t="n"/>
-      <c r="E8" s="34" t="n">
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>J05 (27/06)</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="35" t="n">
         <v>40</v>
       </c>
-      <c r="C9" s="34" t="n"/>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="34" t="n">
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F9" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>J06 (28/06)</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n">
+      <c r="B10" s="35" t="n">
         <v>48</v>
       </c>
-      <c r="C10" s="34" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="34" t="n">
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="34" t="n">
+      <c r="F10" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>J07 (29/06)</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="35" t="n">
         <v>56</v>
       </c>
-      <c r="C11" s="34" t="n"/>
-      <c r="D11" s="34" t="n"/>
-      <c r="E11" s="34" t="n">
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F11" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>J08 (30/06)</t>
         </is>
       </c>
-      <c r="B12" s="34" t="n">
+      <c r="B12" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="C12" s="34" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="34" t="n">
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F12" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>J09 (01/07)</t>
         </is>
       </c>
-      <c r="B13" s="34" t="n">
+      <c r="B13" s="35" t="n">
         <v>73</v>
       </c>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="34" t="n"/>
-      <c r="E13" s="34" t="n">
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F13" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>J10 (02/07)</t>
         </is>
       </c>
-      <c r="B14" s="34" t="n">
+      <c r="B14" s="35" t="n">
         <v>81</v>
       </c>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n"/>
-      <c r="E14" s="34" t="n">
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="34" t="n">
+      <c r="F14" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>J11 (03/07)</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n">
+      <c r="B15" s="35" t="n">
         <v>89</v>
       </c>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="34" t="n"/>
-      <c r="E15" s="34" t="n">
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="34" t="n">
+      <c r="F15" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>J12 (04/07)</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n">
+      <c r="B16" s="35" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="34" t="n"/>
-      <c r="E16" s="34" t="n">
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F16" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>J13 (05/07)</t>
         </is>
       </c>
-      <c r="B17" s="34" t="n">
+      <c r="B17" s="35" t="n">
         <v>105</v>
       </c>
-      <c r="C17" s="34" t="n"/>
-      <c r="D17" s="34" t="n"/>
-      <c r="E17" s="34" t="n">
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="34" t="n">
+      <c r="F17" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>J14 (06/07)</t>
         </is>
       </c>
-      <c r="B18" s="34" t="n">
+      <c r="B18" s="35" t="n">
         <v>113</v>
       </c>
-      <c r="C18" s="34" t="n"/>
-      <c r="D18" s="34" t="n"/>
-      <c r="E18" s="34" t="n">
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F18" s="35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>J15 (07/07)</t>
         </is>
       </c>
-      <c r="B19" s="34" t="n">
+      <c r="B19" s="35" t="n">
         <v>121</v>
       </c>
-      <c r="C19" s="34" t="n"/>
-      <c r="D19" s="34" t="n"/>
-      <c r="E19" s="34" t="n">
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="34" t="n">
+      <c r="F19" s="35" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11662,870 +11694,870 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>ADR 0014</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n">
+      <c r="B5" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>TC-AI-010</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-008, TC-GRC-009</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>TC-NC-004, TC-AUD-003, TC-WF-003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §10.2</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B8" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-009, TC-STD-006, TC-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n">
+      <c r="B10" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>TC-AI-002, TC-AI-003, TC-AI-009</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.3</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
+      <c r="B11" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>TC-5S-006, TC-ACAD-005</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.4</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
+      <c r="B12" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-008</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n">
+      <c r="B13" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-003, TC-NC-003, TC-CAPA-003</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §12.3</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n">
+      <c r="B14" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>TC-AI-005</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
-      <c r="B15" s="36" t="n">
+      <c r="B15" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-005</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §14.2</t>
         </is>
       </c>
-      <c r="B16" s="36" t="n">
+      <c r="B16" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="37" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-007</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
-      <c r="B17" s="36" t="n">
+      <c r="B17" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="37" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>TC-XCUT-004, TC-XCUT-007</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
-      <c r="B18" s="36" t="n">
+      <c r="B18" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="37" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>TC-XCUT-001, TC-XCUT-002</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n">
+      <c r="B19" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>TC-5S-003, TC-XCUT-003, TC-XCUT-005</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §16</t>
         </is>
       </c>
-      <c r="B20" s="36" t="n">
+      <c r="B20" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="37" t="inlineStr">
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-004</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
-      <c r="B21" s="36" t="n">
+      <c r="B21" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="37" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-008, TC-DOCGEN-002, TC-SEC-005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
-      <c r="B22" s="36" t="n">
+      <c r="B22" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="37" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>TC-ACAD-001, TC-ACAD-002, TC-ACAD-003, TC-ACAD-004, TC-ACAD-006</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
         </is>
       </c>
-      <c r="B23" s="36" t="n">
+      <c r="B23" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="37" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-001, TC-PDCA-002, TC-PDCA-003, TC-PDCA-004, TC-PDCA-005, TC-PDCA-006</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="B24" s="36" t="n">
+      <c r="B24" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="37" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>TC-5S-001, TC-5S-002, TC-5S-004, TC-5S-005</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="B25" s="36" t="n">
+      <c r="B25" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="37" t="inlineStr">
+      <c r="C25" s="38" t="inlineStr">
         <is>
           <t>TC-CERCLE-001, TC-CERCLE-002, TC-CERCLE-003, TC-CERCLE-004</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="B26" s="36" t="n">
+      <c r="B26" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="37" t="inlineStr">
+      <c r="C26" s="38" t="inlineStr">
         <is>
           <t>TC-DMAIC-001, TC-DMAIC-002, TC-DMAIC-003, TC-DMAIC-004, TC-AI-004</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="B27" s="36" t="n">
+      <c r="B27" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="37" t="inlineStr">
+      <c r="C27" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-001, TC-ISHI-002, TC-ISHI-005</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="B28" s="36" t="n">
+      <c r="B28" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="37" t="inlineStr">
+      <c r="C28" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-004, TC-NC-005</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="B29" s="36" t="n">
+      <c r="B29" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="38" t="inlineStr">
         <is>
           <t>TC-DOC-001, TC-DOC-002, TC-DOC-003</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
-      <c r="B30" s="36" t="n">
+      <c r="B30" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="37" t="inlineStr">
+      <c r="C30" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-004</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="B31" s="36" t="n">
+      <c r="B31" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="37" t="inlineStr">
+      <c r="C31" s="38" t="inlineStr">
         <is>
           <t>TC-CAPA-001, TC-CAPA-002</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="B32" s="36" t="n">
+      <c r="B32" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="37" t="inlineStr">
+      <c r="C32" s="38" t="inlineStr">
         <is>
           <t>TC-NC-001, TC-NC-002</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="35" t="inlineStr">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="B33" s="36" t="n">
+      <c r="B33" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="37" t="inlineStr">
+      <c r="C33" s="38" t="inlineStr">
         <is>
           <t>TC-AUD-001, TC-AUD-002</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
-      <c r="B34" s="36" t="n">
+      <c r="B34" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="37" t="inlineStr">
+      <c r="C34" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-002</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="35" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
-      <c r="B35" s="36" t="n">
+      <c r="B35" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="37" t="inlineStr">
+      <c r="C35" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-001</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.7</t>
         </is>
       </c>
-      <c r="B36" s="36" t="n">
+      <c r="B36" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="37" t="inlineStr">
+      <c r="C36" s="38" t="inlineStr">
         <is>
           <t>TC-ACAD-007</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="35" t="inlineStr">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
-      <c r="B37" s="36" t="n">
+      <c r="B37" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="37" t="inlineStr">
+      <c r="C37" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-003</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.9</t>
         </is>
       </c>
-      <c r="B38" s="36" t="n">
+      <c r="B38" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="37" t="inlineStr">
+      <c r="C38" s="38" t="inlineStr">
         <is>
           <t>TC-AI-007</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="35" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
-      <c r="B39" s="36" t="n">
+      <c r="B39" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="37" t="inlineStr">
+      <c r="C39" s="38" t="inlineStr">
         <is>
           <t>TC-MKT-001</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="35" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
-      <c r="B40" s="36" t="n">
+      <c r="B40" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="37" t="inlineStr">
+      <c r="C40" s="38" t="inlineStr">
         <is>
           <t>TC-WF-001, TC-WF-002</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="35" t="inlineStr">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
-      <c r="B41" s="36" t="n">
+      <c r="B41" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="37" t="inlineStr">
+      <c r="C41" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-007, TC-AI-006</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="35" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="B42" s="36" t="n">
+      <c r="B42" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="37" t="inlineStr">
+      <c r="C42" s="38" t="inlineStr">
         <is>
           <t>TC-CAPA-004, TC-DASH-008</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="35" t="inlineStr">
+      <c r="A43" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.1</t>
         </is>
       </c>
-      <c r="B43" s="36" t="n">
+      <c r="B43" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="37" t="inlineStr">
+      <c r="C43" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-001</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="35" t="inlineStr">
+      <c r="A44" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="B44" s="36" t="n">
+      <c r="B44" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="37" t="inlineStr">
+      <c r="C44" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-002, TC-DASH-003, TC-DASH-004, TC-DASH-007, TC-AI-001</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="35" t="inlineStr">
+      <c r="A45" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="B45" s="36" t="n">
+      <c r="B45" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="37" t="inlineStr">
+      <c r="C45" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-005, TC-DASH-006, TC-AI-008</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="35" t="inlineStr">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="B46" s="36" t="n">
+      <c r="B46" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="37" t="inlineStr">
+      <c r="C46" s="38" t="inlineStr">
         <is>
           <t>TC-MKT-002, TC-MKT-003, TC-MKT-004, TC-MKT-005</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="35" t="inlineStr">
+      <c r="A47" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
-      <c r="B47" s="36" t="n">
+      <c r="B47" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="37" t="inlineStr">
+      <c r="C47" s="38" t="inlineStr">
         <is>
           <t>TC-STD-001</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="35" t="inlineStr">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="B48" s="36" t="n">
+      <c r="B48" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="37" t="inlineStr">
+      <c r="C48" s="38" t="inlineStr">
         <is>
           <t>TC-STD-002, TC-STD-004</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="35" t="inlineStr">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="B49" s="36" t="n">
+      <c r="B49" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="37" t="inlineStr">
+      <c r="C49" s="38" t="inlineStr">
         <is>
           <t>TC-STD-003, TC-STD-005</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="35" t="inlineStr">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="B50" s="36" t="n">
+      <c r="B50" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="37" t="inlineStr">
+      <c r="C50" s="38" t="inlineStr">
         <is>
           <t>TC-DOCGEN-001, TC-DOCGEN-003</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="35" t="inlineStr">
+      <c r="A51" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.4</t>
         </is>
       </c>
-      <c r="B51" s="36" t="n">
+      <c r="B51" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="37" t="inlineStr">
+      <c r="C51" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-001</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="35" t="inlineStr">
+      <c r="A52" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.5</t>
         </is>
       </c>
-      <c r="B52" s="36" t="n">
+      <c r="B52" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="37" t="inlineStr">
+      <c r="C52" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-002</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="35" t="inlineStr">
+      <c r="A53" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.8</t>
         </is>
       </c>
-      <c r="B53" s="36" t="n">
+      <c r="B53" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="37" t="inlineStr">
+      <c r="C53" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-004</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="35" t="inlineStr">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.9</t>
         </is>
       </c>
-      <c r="B54" s="36" t="n">
+      <c r="B54" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="37" t="inlineStr">
+      <c r="C54" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-003</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="35" t="inlineStr">
+      <c r="A55" s="36" t="inlineStr">
         <is>
           <t>NIS 2</t>
         </is>
       </c>
-      <c r="B55" s="36" t="n">
+      <c r="B55" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="37" t="inlineStr">
+      <c r="C55" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-010</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="35" t="inlineStr">
+      <c r="A56" s="36" t="inlineStr">
         <is>
           <t>RGPD</t>
         </is>
       </c>
-      <c r="B56" s="36" t="n">
+      <c r="B56" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="37" t="inlineStr">
+      <c r="C56" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-003</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="35" t="inlineStr">
+      <c r="A57" s="36" t="inlineStr">
         <is>
           <t>RGPD §15-22</t>
         </is>
       </c>
-      <c r="B57" s="36" t="n">
+      <c r="B57" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="37" t="inlineStr">
+      <c r="C57" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-004</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="35" t="inlineStr">
+      <c r="A58" s="36" t="inlineStr">
         <is>
           <t>RGPD §28/44</t>
         </is>
       </c>
-      <c r="B58" s="36" t="n">
+      <c r="B58" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="37" t="inlineStr">
+      <c r="C58" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-007</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="35" t="inlineStr">
+      <c r="A59" s="36" t="inlineStr">
         <is>
           <t>RGPD §30</t>
         </is>
       </c>
-      <c r="B59" s="36" t="n">
+      <c r="B59" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="37" t="inlineStr">
+      <c r="C59" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-002</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="35" t="inlineStr">
+      <c r="A60" s="36" t="inlineStr">
         <is>
           <t>RGPD §33</t>
         </is>
       </c>
-      <c r="B60" s="36" t="n">
+      <c r="B60" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="37" t="inlineStr">
+      <c r="C60" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-006</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="35" t="inlineStr">
+      <c r="A61" s="36" t="inlineStr">
         <is>
           <t>RGPD §35</t>
         </is>
       </c>
-      <c r="B61" s="36" t="n">
+      <c r="B61" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="37" t="inlineStr">
+      <c r="C61" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-005</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="35" t="inlineStr">
+      <c r="A62" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B62" s="36" t="n">
+      <c r="B62" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="37" t="inlineStr">
+      <c r="C62" s="38" t="inlineStr">
         <is>
           <t>TC-AUD-004, TC-DOCGEN-004, TC-GRC-001, TC-SEC-002, TC-SEC-003, TC-XCUT-006</t>
         </is>
@@ -12546,7 +12578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12637,7 +12669,7 @@
           <t>IA / NLQ</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12778,7 +12810,7 @@
           <t>Auth</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -13047,45 +13079,92 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
+          <t>ANO-011</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Avancement des actions CAPA (→ DONE) absent de l'UI</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>CAPA</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="inlineStr">
+        <is>
+          <t>Mineure</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>Ouvert</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-002</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>La résolution d'un CAPA exige ≥1 action DONE (CapaService, ISO 9001 §10.2), mais la table d'actions du détail est en lecture seule : aucun moyen de passer une action à DONE → le cycle ne peut atteindre la clôture. Le backend expose pourtant PATCH /cases/{id}/actions/{actionId} (champ status).</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>À implémenter côté front (backend prêt) : avancement du statut d'action (PENDING→IN_PROGRESS→DONE).</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>23/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
           <t>ANO-010</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Compte-rendu de réunion auto-généré (LLM) absent</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Cercles</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>Résolu</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>TC-CERCLE-004</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.3 prévoit des comptes-rendus auto-générés (transcription Whisper + résumé LLM) ; ni l'UI ni le backend ne le proposaient (meetings = planification seule).</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>Implémenté le 23/06 (agent parallèle, ADR 0044) : endpoint POST /circles/{id}/meetings/{mid}/minutes/generate via AiGateway (résumé+décisions+actions), persistance (migration V97), UI dédiée. Transcription Whisper audio→texte documentée en étape future.</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>23/06</t>
         </is>
@@ -13106,7 +13185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13435,7 +13514,7 @@
           <t>TC-5S-004</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13467,7 +13546,7 @@
           <t>TC-5S-005</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13659,7 +13738,7 @@
           <t>TC-ISHI-004</t>
         </is>
       </c>
-      <c r="D20" s="38" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13947,7 +14026,7 @@
           <t>TC-CERCLE-003</t>
         </is>
       </c>
-      <c r="D29" s="38" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13979,7 +14058,7 @@
           <t>TC-CERCLE-004</t>
         </is>
       </c>
-      <c r="D30" s="38" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -14155,8 +14234,136 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Lot 7</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-001</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>Liste des dossiers CAPA : 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-001_liste.png</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
-      <c r="A37" s="41" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Lot 7</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-002</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>Démarrage OK (OPEN→IN_PROGRESS) ; résolution exige ≥1 action DONE (ISO 9001), mais l'UI n'offre pas d'avancement d'action→DONE (table lecture seule). Backend PATCH actions/{id} prêt. Consigné ANO-011.</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-002_workflow.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Lot 7</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-003</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>Suggestion IA d'actions : POST /capa/cases/{id}/suggest-actions HTTP 200 (ai-service Mistral).</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-003_ia.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Lot 7</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-004</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>KPI « Délai moyen clôture CAPA » affiché sur le dashboard.</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-004_kpi.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -214,12 +214,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D97706"/>
+        <fgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
+        <fgColor rgb="00D97706"/>
       </patternFill>
     </fill>
   </fills>
@@ -305,9 +305,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -317,10 +314,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -358,6 +355,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4674,9 +4674,9 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L36" s="21" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
+      <c r="L36" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="13" t="inlineStr">
         <is>
-          <t>Démarrage OK (OPEN→IN_PROGRESS) mais clôture IMPOSSIBLE via l'UI : la résolution exige ≥1 action DONE (règle ISO 9001 §10.2 correcte), or la table d'actions est en lecture seule (aucun avancement action→DONE). Backend PATCH /cases/{id}/actions/{actionId} (champ status) prêt → écart UI, voir ANO-011.</t>
+          <t>Résolu via ANO-011 : avancement d'action (Démarrer/Terminer → DONE) câblé dans le détail, débloquant le cycle OPEN→IN_PROGRESS→(action DONE)→RESOLVED→CLOSED. tsc 0 erreur + i18n OK ; build/Karma/E2E validés en CI (env local dégradé : node_modules + C: saturé).</t>
         </is>
       </c>
     </row>
@@ -10742,74 +10742,74 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Cas de test</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Exécutés</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>Taux d'exécution</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t>Passés</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>Taux de réussite</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>Échoués</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Bloqués</t>
         </is>
       </c>
-      <c r="O4" s="27" t="inlineStr">
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t>Non exécutés</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="27" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="28" t="n">
         <v>32</v>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>26.4%</t>
         </is>
       </c>
-      <c r="G5" s="30" t="n">
-        <v>31</v>
-      </c>
-      <c r="I5" s="30" t="inlineStr">
-        <is>
-          <t>96.9%</t>
-        </is>
-      </c>
-      <c r="K5" s="31" t="n">
+      <c r="G5" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="I5" s="29" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="K5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="33" t="n">
+      <c r="M5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="32" t="n">
         <v>89</v>
       </c>
     </row>
@@ -10832,32 +10832,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="G9" s="34" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="H9" s="34" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -10870,7 +10870,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -11043,12 +11043,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="34" t="inlineStr">
+      <c r="G23" s="33" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="H23" s="34" t="inlineStr">
+      <c r="H23" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -11358,276 +11358,276 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>J01 (23/06)</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="34" t="n">
         <v>32</v>
       </c>
-      <c r="D5" s="35" t="n">
-        <v>31</v>
-      </c>
-      <c r="E5" s="35" t="n">
+      <c r="D5" s="34" t="n">
+        <v>32</v>
+      </c>
+      <c r="E5" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>J02 (24/06)</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="35" t="n">
+      <c r="F6" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>J03 (25/06)</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>J04 (26/06)</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="34" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="35" t="n">
+      <c r="F8" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>J05 (27/06)</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="34" t="n">
         <v>40</v>
       </c>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n">
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="35" t="n">
+      <c r="F9" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>J06 (28/06)</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n">
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="35" t="n">
+      <c r="F10" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>J07 (29/06)</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="34" t="n">
         <v>56</v>
       </c>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n">
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="35" t="n">
+      <c r="F11" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>J08 (30/06)</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n">
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>J09 (01/07)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="34" t="n">
         <v>73</v>
       </c>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n">
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>J10 (02/07)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="34" t="n">
         <v>81</v>
       </c>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n">
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>J11 (03/07)</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="34" t="n">
         <v>89</v>
       </c>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n">
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>J12 (04/07)</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="34" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>J13 (05/07)</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="34" t="n">
         <v>105</v>
       </c>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="34" t="n"/>
+      <c r="E17" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>J14 (06/07)</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="34" t="n">
         <v>113</v>
       </c>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="35" t="n">
+      <c r="F18" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>J15 (07/07)</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="34" t="n">
         <v>121</v>
       </c>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n">
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="34" t="n"/>
+      <c r="E19" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11694,870 +11694,870 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>ADR 0014</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>TC-AI-010</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-008, TC-GRC-009</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>TC-NC-004, TC-AUD-003, TC-WF-003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §10.2</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-009, TC-STD-006, TC-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>TC-AI-002, TC-AI-003, TC-AI-009</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.3</t>
         </is>
       </c>
-      <c r="B11" s="37" t="n">
+      <c r="B11" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>TC-5S-006, TC-ACAD-005</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.4</t>
         </is>
       </c>
-      <c r="B12" s="37" t="n">
+      <c r="B12" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-008</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="B13" s="37" t="n">
+      <c r="B13" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-003, TC-NC-003, TC-CAPA-003</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §12.3</t>
         </is>
       </c>
-      <c r="B14" s="37" t="n">
+      <c r="B14" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>TC-AI-005</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
-      <c r="B15" s="37" t="n">
+      <c r="B15" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-005</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §14.2</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-007</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
-      <c r="B17" s="37" t="n">
+      <c r="B17" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>TC-XCUT-004, TC-XCUT-007</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
-      <c r="B18" s="37" t="n">
+      <c r="B18" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>TC-XCUT-001, TC-XCUT-002</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>TC-5S-003, TC-XCUT-003, TC-XCUT-005</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §16</t>
         </is>
       </c>
-      <c r="B20" s="37" t="n">
+      <c r="B20" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="38" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-004</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
-      <c r="B21" s="37" t="n">
+      <c r="B21" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-008, TC-DOCGEN-002, TC-SEC-005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="38" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>TC-ACAD-001, TC-ACAD-002, TC-ACAD-003, TC-ACAD-004, TC-ACAD-006</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
         </is>
       </c>
-      <c r="B23" s="37" t="n">
+      <c r="B23" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="38" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-001, TC-PDCA-002, TC-PDCA-003, TC-PDCA-004, TC-PDCA-005, TC-PDCA-006</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="B24" s="37" t="n">
+      <c r="B24" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="38" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>TC-5S-001, TC-5S-002, TC-5S-004, TC-5S-005</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="36" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="B25" s="37" t="n">
+      <c r="B25" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="38" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>TC-CERCLE-001, TC-CERCLE-002, TC-CERCLE-003, TC-CERCLE-004</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="B26" s="37" t="n">
+      <c r="B26" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="38" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>TC-DMAIC-001, TC-DMAIC-002, TC-DMAIC-003, TC-DMAIC-004, TC-AI-004</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="36" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="B27" s="37" t="n">
+      <c r="B27" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="38" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-001, TC-ISHI-002, TC-ISHI-005</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="36" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="B28" s="37" t="n">
+      <c r="B28" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="38" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-004, TC-NC-005</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="B29" s="37" t="n">
+      <c r="B29" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="38" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>TC-DOC-001, TC-DOC-002, TC-DOC-003</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="36" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
-      <c r="B30" s="37" t="n">
+      <c r="B30" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="38" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-004</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="36" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="B31" s="37" t="n">
+      <c r="B31" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="38" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
         <is>
           <t>TC-CAPA-001, TC-CAPA-002</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="B32" s="37" t="n">
+      <c r="B32" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="38" t="inlineStr">
+      <c r="C32" s="37" t="inlineStr">
         <is>
           <t>TC-NC-001, TC-NC-002</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="36" t="inlineStr">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="B33" s="37" t="n">
+      <c r="B33" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="38" t="inlineStr">
+      <c r="C33" s="37" t="inlineStr">
         <is>
           <t>TC-AUD-001, TC-AUD-002</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="36" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
-      <c r="B34" s="37" t="n">
+      <c r="B34" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="38" t="inlineStr">
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-002</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="36" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
-      <c r="B35" s="37" t="n">
+      <c r="B35" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="38" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-001</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="36" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.7</t>
         </is>
       </c>
-      <c r="B36" s="37" t="n">
+      <c r="B36" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="38" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>TC-ACAD-007</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="36" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
-      <c r="B37" s="37" t="n">
+      <c r="B37" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="38" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-003</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="36" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.9</t>
         </is>
       </c>
-      <c r="B38" s="37" t="n">
+      <c r="B38" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="38" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>TC-AI-007</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="36" t="inlineStr">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
-      <c r="B39" s="37" t="n">
+      <c r="B39" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="38" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>TC-MKT-001</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
-      <c r="B40" s="37" t="n">
+      <c r="B40" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="38" t="inlineStr">
+      <c r="C40" s="37" t="inlineStr">
         <is>
           <t>TC-WF-001, TC-WF-002</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="36" t="inlineStr">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
-      <c r="B41" s="37" t="n">
+      <c r="B41" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="38" t="inlineStr">
+      <c r="C41" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-007, TC-AI-006</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="36" t="inlineStr">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="B42" s="37" t="n">
+      <c r="B42" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="38" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
         <is>
           <t>TC-CAPA-004, TC-DASH-008</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.1</t>
         </is>
       </c>
-      <c r="B43" s="37" t="n">
+      <c r="B43" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="38" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-001</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="B44" s="37" t="n">
+      <c r="B44" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="38" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-002, TC-DASH-003, TC-DASH-004, TC-DASH-007, TC-AI-001</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="36" t="inlineStr">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="B45" s="37" t="n">
+      <c r="B45" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="38" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-005, TC-DASH-006, TC-AI-008</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="36" t="inlineStr">
+      <c r="A46" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="B46" s="37" t="n">
+      <c r="B46" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="38" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
         <is>
           <t>TC-MKT-002, TC-MKT-003, TC-MKT-004, TC-MKT-005</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="36" t="inlineStr">
+      <c r="A47" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
-      <c r="B47" s="37" t="n">
+      <c r="B47" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="38" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
         <is>
           <t>TC-STD-001</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="36" t="inlineStr">
+      <c r="A48" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="B48" s="37" t="n">
+      <c r="B48" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="38" t="inlineStr">
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>TC-STD-002, TC-STD-004</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="36" t="inlineStr">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="B49" s="37" t="n">
+      <c r="B49" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="38" t="inlineStr">
+      <c r="C49" s="37" t="inlineStr">
         <is>
           <t>TC-STD-003, TC-STD-005</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="36" t="inlineStr">
+      <c r="A50" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="B50" s="37" t="n">
+      <c r="B50" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="38" t="inlineStr">
+      <c r="C50" s="37" t="inlineStr">
         <is>
           <t>TC-DOCGEN-001, TC-DOCGEN-003</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="36" t="inlineStr">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.4</t>
         </is>
       </c>
-      <c r="B51" s="37" t="n">
+      <c r="B51" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="38" t="inlineStr">
+      <c r="C51" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-001</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="36" t="inlineStr">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.5</t>
         </is>
       </c>
-      <c r="B52" s="37" t="n">
+      <c r="B52" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="38" t="inlineStr">
+      <c r="C52" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-002</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="36" t="inlineStr">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.8</t>
         </is>
       </c>
-      <c r="B53" s="37" t="n">
+      <c r="B53" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="38" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-004</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="36" t="inlineStr">
+      <c r="A54" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.9</t>
         </is>
       </c>
-      <c r="B54" s="37" t="n">
+      <c r="B54" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="38" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-003</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="36" t="inlineStr">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>NIS 2</t>
         </is>
       </c>
-      <c r="B55" s="37" t="n">
+      <c r="B55" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="38" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-010</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="36" t="inlineStr">
+      <c r="A56" s="35" t="inlineStr">
         <is>
           <t>RGPD</t>
         </is>
       </c>
-      <c r="B56" s="37" t="n">
+      <c r="B56" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="38" t="inlineStr">
+      <c r="C56" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-003</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="36" t="inlineStr">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>RGPD §15-22</t>
         </is>
       </c>
-      <c r="B57" s="37" t="n">
+      <c r="B57" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="38" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-004</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="36" t="inlineStr">
+      <c r="A58" s="35" t="inlineStr">
         <is>
           <t>RGPD §28/44</t>
         </is>
       </c>
-      <c r="B58" s="37" t="n">
+      <c r="B58" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="38" t="inlineStr">
+      <c r="C58" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-007</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="36" t="inlineStr">
+      <c r="A59" s="35" t="inlineStr">
         <is>
           <t>RGPD §30</t>
         </is>
       </c>
-      <c r="B59" s="37" t="n">
+      <c r="B59" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="38" t="inlineStr">
+      <c r="C59" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-002</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="36" t="inlineStr">
+      <c r="A60" s="35" t="inlineStr">
         <is>
           <t>RGPD §33</t>
         </is>
       </c>
-      <c r="B60" s="37" t="n">
+      <c r="B60" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="38" t="inlineStr">
+      <c r="C60" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-006</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="36" t="inlineStr">
+      <c r="A61" s="35" t="inlineStr">
         <is>
           <t>RGPD §35</t>
         </is>
       </c>
-      <c r="B61" s="37" t="n">
+      <c r="B61" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="38" t="inlineStr">
+      <c r="C61" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-005</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="36" t="inlineStr">
+      <c r="A62" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B62" s="37" t="n">
+      <c r="B62" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="38" t="inlineStr">
+      <c r="C62" s="37" t="inlineStr">
         <is>
           <t>TC-AUD-004, TC-DOCGEN-004, TC-GRC-001, TC-SEC-002, TC-SEC-003, TC-XCUT-006</t>
         </is>
@@ -12669,7 +12669,7 @@
           <t>IA / NLQ</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12810,7 +12810,7 @@
           <t>Auth</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -13097,9 +13097,9 @@
           <t>Mineure</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>Ouvert</t>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Résolu</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -13109,12 +13109,12 @@
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>La résolution d'un CAPA exige ≥1 action DONE (CapaService, ISO 9001 §10.2), mais la table d'actions du détail est en lecture seule : aucun moyen de passer une action à DONE → le cycle ne peut atteindre la clôture. Le backend expose pourtant PATCH /cases/{id}/actions/{actionId} (champ status).</t>
+          <t>La résolution d'un CAPA exige ≥1 action DONE (CapaService, ISO 9001 §10.2), mais la table d'actions du détail était en lecture seule : aucun moyen de passer une action à DONE → le cycle ne pouvait atteindre la clôture. Le backend expose pourtant PATCH /cases/{id}/actions/{actionId}.</t>
         </is>
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>À implémenter côté front (backend prêt) : avancement du statut d'action (PENDING→IN_PROGRESS→DONE).</t>
+          <t>Implémenté le 23/06 : service updateAction + colonne « Avancement » (Démarrer/Terminer → PENDING→IN_PROGRESS→DONE) dans le détail + i18n 6 langues + spec. Le titre est renvoyé (requis backend). tsc 0 erreur, i18n --check OK ; build/Karma en CI.</t>
         </is>
       </c>
       <c r="I14" s="16" t="inlineStr">
@@ -13139,7 +13139,7 @@
           <t>Cercles</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -13514,7 +13514,7 @@
           <t>TC-5S-004</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13546,7 +13546,7 @@
           <t>TC-5S-005</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13738,7 +13738,7 @@
           <t>TC-ISHI-004</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -14026,7 +14026,7 @@
           <t>TC-CERCLE-003</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -14058,7 +14058,7 @@
           <t>TC-CERCLE-004</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -14282,7 +14282,7 @@
           <t>TC-CAPA-002</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D37" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="13" t="inlineStr">
         <is>
-          <t>Résolu via ANO-011 : avancement d'action (Démarrer/Terminer → DONE) câblé dans le détail, débloquant le cycle OPEN→IN_PROGRESS→(action DONE)→RESOLVED→CLOSED. tsc 0 erreur + i18n OK ; build/Karma/E2E validés en CI (env local dégradé : node_modules + C: saturé).</t>
+          <t>Résolu via ANO-011 (avancement d'action → DONE). Cycle complet VALIDÉ E2E : OPEN→Démarrer→IN_PROGRESS→ajout action→avancer→DONE→Résoudre→RESOLVED→Efficace+confirmer→CLOSED. CI verte (frontend build+Karma, backend, E2E smoke).</t>
         </is>
       </c>
     </row>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -214,12 +214,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
+        <fgColor rgb="00D97706"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D97706"/>
+        <fgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
   </fills>
@@ -305,6 +305,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -314,10 +317,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -355,9 +358,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
@@ -4906,18 +4906,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L39" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M39" s="16" t="inlineStr"/>
+      <c r="L39" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N39" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="O39" s="16" t="inlineStr"/>
+      <c r="O39" s="16" t="inlineStr">
+        <is>
+          <t>TC-AUD-001_liste.png — liste des plans d'audit, 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
@@ -4976,18 +4984,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L40" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M40" s="13" t="inlineStr"/>
+      <c r="L40" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M40" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N40" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="O40" s="13" t="inlineStr"/>
+      <c r="O40" s="13" t="inlineStr">
+        <is>
+          <t>TC-AUD-002_execution.png — exécution LPA : ajout d'une question checklist (POST /checklist HTTP 201, item rendu) + réponse de conformité (mat-select Conforme/NC) ; offline-first câblé (file de resync §15.2-15.3).</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -5046,18 +5062,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L41" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M41" s="16" t="inlineStr"/>
+      <c r="L41" s="21" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="O41" s="16" t="inlineStr"/>
+      <c r="O41" s="16" t="inlineStr">
+        <is>
+          <t>Aucune génération de rapport d'audit par LLM : completePlan stocke un reportSummary manuel, aucun appel AiGateway (ni front ni backend). Écart vs CLAUDE §1.4/§4.4 — voir ANO-012.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
@@ -5115,18 +5139,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L42" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M42" s="13" t="inlineStr"/>
+      <c r="L42" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M42" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N42" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O42" s="13" t="inlineStr"/>
+      <c r="O42" s="13" t="inlineStr">
+        <is>
+          <t>TC-AUD-004_detail.png — détail d'audit chargé sans blocage (titre affiché, pas de « Chargement… » figé) — régression OK (pattern reload$ BehaviorSubject + refCount:false).</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -10742,75 +10774,75 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Cas de test</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Exécutés</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Taux d'exécution</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>Passés</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Taux de réussite</t>
         </is>
       </c>
-      <c r="K4" s="24" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>Échoués</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t>Bloqués</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
+      <c r="O4" s="27" t="inlineStr">
         <is>
           <t>Non exécutés</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
+      <c r="A5" s="28" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="28" t="n">
-        <v>32</v>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>26.4%</t>
-        </is>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>32</v>
-      </c>
-      <c r="I5" s="29" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="K5" s="30" t="n">
+      <c r="C5" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>29.8%</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>35</v>
+      </c>
+      <c r="I5" s="30" t="inlineStr">
+        <is>
+          <t>97.2%</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>89</v>
+      <c r="M5" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="33" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="6"/>
@@ -10832,32 +10864,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="G9" s="33" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
+      <c r="H9" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -10870,7 +10902,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -10922,7 +10954,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -10974,7 +11006,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -11043,12 +11075,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="33" t="inlineStr">
+      <c r="G23" s="34" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="H23" s="33" t="inlineStr">
+      <c r="H23" s="34" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -11358,276 +11390,276 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
-        <is>
-          <t>J01 (23/06)</t>
-        </is>
-      </c>
-      <c r="B5" s="34" t="n">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>J01 (24/06)</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="34" t="n">
+      <c r="C5" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="35" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>J02 (25/06)</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="35" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>J03 (26/06)</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>J04 (27/06)</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="n">
         <v>32</v>
       </c>
-      <c r="D5" s="34" t="n">
-        <v>32</v>
-      </c>
-      <c r="E5" s="34" t="n">
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="34" t="n">
+      <c r="F8" s="35" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="34" t="inlineStr">
-        <is>
-          <t>J02 (24/06)</t>
-        </is>
-      </c>
-      <c r="B6" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="34" t="n">
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>J05 (28/06)</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="n">
+        <v>40</v>
+      </c>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F9" s="35" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t>J03 (25/06)</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="n">
-        <v>24</v>
-      </c>
-      <c r="C7" s="34" t="n"/>
-      <c r="D7" s="34" t="n"/>
-      <c r="E7" s="34" t="n">
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>J06 (29/06)</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="n">
+        <v>48</v>
+      </c>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F10" s="35" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>J04 (26/06)</t>
-        </is>
-      </c>
-      <c r="B8" s="34" t="n">
-        <v>32</v>
-      </c>
-      <c r="C8" s="34" t="n"/>
-      <c r="D8" s="34" t="n"/>
-      <c r="E8" s="34" t="n">
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>J07 (30/06)</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="n">
+        <v>56</v>
+      </c>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F11" s="35" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>J05 (27/06)</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="n">
-        <v>40</v>
-      </c>
-      <c r="C9" s="34" t="n"/>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="34" t="n">
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>J08 (01/07)</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F12" s="35" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="34" t="inlineStr">
-        <is>
-          <t>J06 (28/06)</t>
-        </is>
-      </c>
-      <c r="B10" s="34" t="n">
-        <v>48</v>
-      </c>
-      <c r="C10" s="34" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="34" t="n">
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>J09 (02/07)</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="n">
+        <v>73</v>
+      </c>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="34" t="n">
+      <c r="F13" s="35" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>J07 (29/06)</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="n">
-        <v>56</v>
-      </c>
-      <c r="C11" s="34" t="n"/>
-      <c r="D11" s="34" t="n"/>
-      <c r="E11" s="34" t="n">
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>J10 (03/07)</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="n">
+        <v>81</v>
+      </c>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F14" s="35" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="34" t="inlineStr">
-        <is>
-          <t>J08 (30/06)</t>
-        </is>
-      </c>
-      <c r="B12" s="34" t="n">
-        <v>65</v>
-      </c>
-      <c r="C12" s="34" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="34" t="n">
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>J11 (04/07)</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="n">
+        <v>89</v>
+      </c>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F15" s="35" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="34" t="inlineStr">
-        <is>
-          <t>J09 (01/07)</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="n">
-        <v>73</v>
-      </c>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="34" t="n"/>
-      <c r="E13" s="34" t="n">
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>J12 (05/07)</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="n">
+        <v>97</v>
+      </c>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F16" s="35" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>J10 (02/07)</t>
-        </is>
-      </c>
-      <c r="B14" s="34" t="n">
-        <v>81</v>
-      </c>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n"/>
-      <c r="E14" s="34" t="n">
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>J13 (06/07)</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="n">
+        <v>105</v>
+      </c>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="34" t="n">
+      <c r="F17" s="35" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>J11 (03/07)</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="n">
-        <v>89</v>
-      </c>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="34" t="n"/>
-      <c r="E15" s="34" t="n">
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>J14 (07/07)</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="n">
+        <v>113</v>
+      </c>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="34" t="n">
+      <c r="F18" s="35" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>J12 (04/07)</t>
-        </is>
-      </c>
-      <c r="B16" s="34" t="n">
-        <v>97</v>
-      </c>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="34" t="n"/>
-      <c r="E16" s="34" t="n">
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>J15 (08/07)</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="n">
+        <v>121</v>
+      </c>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="34" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>J13 (05/07)</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="n">
-        <v>105</v>
-      </c>
-      <c r="C17" s="34" t="n"/>
-      <c r="D17" s="34" t="n"/>
-      <c r="E17" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="34" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="34" t="inlineStr">
-        <is>
-          <t>J14 (06/07)</t>
-        </is>
-      </c>
-      <c r="B18" s="34" t="n">
-        <v>113</v>
-      </c>
-      <c r="C18" s="34" t="n"/>
-      <c r="D18" s="34" t="n"/>
-      <c r="E18" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="F18" s="34" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>J15 (07/07)</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="n">
-        <v>121</v>
-      </c>
-      <c r="C19" s="34" t="n"/>
-      <c r="D19" s="34" t="n"/>
-      <c r="E19" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" s="34" t="n">
+      <c r="F19" s="35" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11694,870 +11726,870 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>ADR 0014</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n">
+      <c r="B5" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>TC-AI-010</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-008, TC-GRC-009</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>TC-NC-004, TC-AUD-003, TC-WF-003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §10.2</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B8" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-009, TC-STD-006, TC-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n">
+      <c r="B10" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>TC-AI-002, TC-AI-003, TC-AI-009</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.3</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
+      <c r="B11" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>TC-5S-006, TC-ACAD-005</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §11.4</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
+      <c r="B12" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-008</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n">
+      <c r="B13" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-003, TC-NC-003, TC-CAPA-003</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §12.3</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n">
+      <c r="B14" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>TC-AI-005</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
-      <c r="B15" s="36" t="n">
+      <c r="B15" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-005</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §14.2</t>
         </is>
       </c>
-      <c r="B16" s="36" t="n">
+      <c r="B16" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="37" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-007</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
-      <c r="B17" s="36" t="n">
+      <c r="B17" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="37" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>TC-XCUT-004, TC-XCUT-007</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
-      <c r="B18" s="36" t="n">
+      <c r="B18" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="37" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>TC-XCUT-001, TC-XCUT-002</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n">
+      <c r="B19" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>TC-5S-003, TC-XCUT-003, TC-XCUT-005</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §16</t>
         </is>
       </c>
-      <c r="B20" s="36" t="n">
+      <c r="B20" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="37" t="inlineStr">
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>TC-SEC-004</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
-      <c r="B21" s="36" t="n">
+      <c r="B21" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="37" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-008, TC-DOCGEN-002, TC-SEC-005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
-      <c r="B22" s="36" t="n">
+      <c r="B22" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="37" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>TC-ACAD-001, TC-ACAD-002, TC-ACAD-003, TC-ACAD-004, TC-ACAD-006</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
         </is>
       </c>
-      <c r="B23" s="36" t="n">
+      <c r="B23" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="37" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-001, TC-PDCA-002, TC-PDCA-003, TC-PDCA-004, TC-PDCA-005, TC-PDCA-006</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="B24" s="36" t="n">
+      <c r="B24" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="37" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>TC-5S-001, TC-5S-002, TC-5S-004, TC-5S-005</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="B25" s="36" t="n">
+      <c r="B25" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="37" t="inlineStr">
+      <c r="C25" s="38" t="inlineStr">
         <is>
           <t>TC-CERCLE-001, TC-CERCLE-002, TC-CERCLE-003, TC-CERCLE-004</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="B26" s="36" t="n">
+      <c r="B26" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="37" t="inlineStr">
+      <c r="C26" s="38" t="inlineStr">
         <is>
           <t>TC-DMAIC-001, TC-DMAIC-002, TC-DMAIC-003, TC-DMAIC-004, TC-AI-004</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="B27" s="36" t="n">
+      <c r="B27" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="37" t="inlineStr">
+      <c r="C27" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-001, TC-ISHI-002, TC-ISHI-005</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="B28" s="36" t="n">
+      <c r="B28" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="37" t="inlineStr">
+      <c r="C28" s="38" t="inlineStr">
         <is>
           <t>TC-ISHI-004, TC-NC-005</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="B29" s="36" t="n">
+      <c r="B29" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="38" t="inlineStr">
         <is>
           <t>TC-DOC-001, TC-DOC-002, TC-DOC-003</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
-      <c r="B30" s="36" t="n">
+      <c r="B30" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="37" t="inlineStr">
+      <c r="C30" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-004</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="B31" s="36" t="n">
+      <c r="B31" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="37" t="inlineStr">
+      <c r="C31" s="38" t="inlineStr">
         <is>
           <t>TC-CAPA-001, TC-CAPA-002</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="B32" s="36" t="n">
+      <c r="B32" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="37" t="inlineStr">
+      <c r="C32" s="38" t="inlineStr">
         <is>
           <t>TC-NC-001, TC-NC-002</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="35" t="inlineStr">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="B33" s="36" t="n">
+      <c r="B33" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="37" t="inlineStr">
+      <c r="C33" s="38" t="inlineStr">
         <is>
           <t>TC-AUD-001, TC-AUD-002</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
-      <c r="B34" s="36" t="n">
+      <c r="B34" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="37" t="inlineStr">
+      <c r="C34" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-002</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="35" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
-      <c r="B35" s="36" t="n">
+      <c r="B35" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="37" t="inlineStr">
+      <c r="C35" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-001</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.7</t>
         </is>
       </c>
-      <c r="B36" s="36" t="n">
+      <c r="B36" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="37" t="inlineStr">
+      <c r="C36" s="38" t="inlineStr">
         <is>
           <t>TC-ACAD-007</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="35" t="inlineStr">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
-      <c r="B37" s="36" t="n">
+      <c r="B37" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="37" t="inlineStr">
+      <c r="C37" s="38" t="inlineStr">
         <is>
           <t>TC-TRANSV-003</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §4.9</t>
         </is>
       </c>
-      <c r="B38" s="36" t="n">
+      <c r="B38" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="37" t="inlineStr">
+      <c r="C38" s="38" t="inlineStr">
         <is>
           <t>TC-AI-007</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="35" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
-      <c r="B39" s="36" t="n">
+      <c r="B39" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="37" t="inlineStr">
+      <c r="C39" s="38" t="inlineStr">
         <is>
           <t>TC-MKT-001</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="35" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
-      <c r="B40" s="36" t="n">
+      <c r="B40" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="37" t="inlineStr">
+      <c r="C40" s="38" t="inlineStr">
         <is>
           <t>TC-WF-001, TC-WF-002</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="35" t="inlineStr">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
-      <c r="B41" s="36" t="n">
+      <c r="B41" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="37" t="inlineStr">
+      <c r="C41" s="38" t="inlineStr">
         <is>
           <t>TC-PDCA-007, TC-AI-006</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="35" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="B42" s="36" t="n">
+      <c r="B42" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="37" t="inlineStr">
+      <c r="C42" s="38" t="inlineStr">
         <is>
           <t>TC-CAPA-004, TC-DASH-008</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="35" t="inlineStr">
+      <c r="A43" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.1</t>
         </is>
       </c>
-      <c r="B43" s="36" t="n">
+      <c r="B43" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="37" t="inlineStr">
+      <c r="C43" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-001</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="35" t="inlineStr">
+      <c r="A44" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="B44" s="36" t="n">
+      <c r="B44" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="37" t="inlineStr">
+      <c r="C44" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-002, TC-DASH-003, TC-DASH-004, TC-DASH-007, TC-AI-001</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="35" t="inlineStr">
+      <c r="A45" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="B45" s="36" t="n">
+      <c r="B45" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="37" t="inlineStr">
+      <c r="C45" s="38" t="inlineStr">
         <is>
           <t>TC-DASH-005, TC-DASH-006, TC-AI-008</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="35" t="inlineStr">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="B46" s="36" t="n">
+      <c r="B46" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="37" t="inlineStr">
+      <c r="C46" s="38" t="inlineStr">
         <is>
           <t>TC-MKT-002, TC-MKT-003, TC-MKT-004, TC-MKT-005</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="35" t="inlineStr">
+      <c r="A47" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
-      <c r="B47" s="36" t="n">
+      <c r="B47" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="37" t="inlineStr">
+      <c r="C47" s="38" t="inlineStr">
         <is>
           <t>TC-STD-001</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="35" t="inlineStr">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="B48" s="36" t="n">
+      <c r="B48" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="37" t="inlineStr">
+      <c r="C48" s="38" t="inlineStr">
         <is>
           <t>TC-STD-002, TC-STD-004</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="35" t="inlineStr">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="B49" s="36" t="n">
+      <c r="B49" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="37" t="inlineStr">
+      <c r="C49" s="38" t="inlineStr">
         <is>
           <t>TC-STD-003, TC-STD-005</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="35" t="inlineStr">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="B50" s="36" t="n">
+      <c r="B50" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="37" t="inlineStr">
+      <c r="C50" s="38" t="inlineStr">
         <is>
           <t>TC-DOCGEN-001, TC-DOCGEN-003</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="35" t="inlineStr">
+      <c r="A51" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.4</t>
         </is>
       </c>
-      <c r="B51" s="36" t="n">
+      <c r="B51" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="37" t="inlineStr">
+      <c r="C51" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-001</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="35" t="inlineStr">
+      <c r="A52" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.5</t>
         </is>
       </c>
-      <c r="B52" s="36" t="n">
+      <c r="B52" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="37" t="inlineStr">
+      <c r="C52" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-002</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="35" t="inlineStr">
+      <c r="A53" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.8</t>
         </is>
       </c>
-      <c r="B53" s="36" t="n">
+      <c r="B53" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="37" t="inlineStr">
+      <c r="C53" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-004</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="35" t="inlineStr">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>CLAUDE §9.9</t>
         </is>
       </c>
-      <c r="B54" s="36" t="n">
+      <c r="B54" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="37" t="inlineStr">
+      <c r="C54" s="38" t="inlineStr">
         <is>
           <t>TC-IOT-003</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="35" t="inlineStr">
+      <c r="A55" s="36" t="inlineStr">
         <is>
           <t>NIS 2</t>
         </is>
       </c>
-      <c r="B55" s="36" t="n">
+      <c r="B55" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="37" t="inlineStr">
+      <c r="C55" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-010</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="35" t="inlineStr">
+      <c r="A56" s="36" t="inlineStr">
         <is>
           <t>RGPD</t>
         </is>
       </c>
-      <c r="B56" s="36" t="n">
+      <c r="B56" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="37" t="inlineStr">
+      <c r="C56" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-003</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="35" t="inlineStr">
+      <c r="A57" s="36" t="inlineStr">
         <is>
           <t>RGPD §15-22</t>
         </is>
       </c>
-      <c r="B57" s="36" t="n">
+      <c r="B57" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="37" t="inlineStr">
+      <c r="C57" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-004</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="35" t="inlineStr">
+      <c r="A58" s="36" t="inlineStr">
         <is>
           <t>RGPD §28/44</t>
         </is>
       </c>
-      <c r="B58" s="36" t="n">
+      <c r="B58" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="37" t="inlineStr">
+      <c r="C58" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-007</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="35" t="inlineStr">
+      <c r="A59" s="36" t="inlineStr">
         <is>
           <t>RGPD §30</t>
         </is>
       </c>
-      <c r="B59" s="36" t="n">
+      <c r="B59" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="37" t="inlineStr">
+      <c r="C59" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-002</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="35" t="inlineStr">
+      <c r="A60" s="36" t="inlineStr">
         <is>
           <t>RGPD §33</t>
         </is>
       </c>
-      <c r="B60" s="36" t="n">
+      <c r="B60" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="37" t="inlineStr">
+      <c r="C60" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-006</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="35" t="inlineStr">
+      <c r="A61" s="36" t="inlineStr">
         <is>
           <t>RGPD §35</t>
         </is>
       </c>
-      <c r="B61" s="36" t="n">
+      <c r="B61" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="37" t="inlineStr">
+      <c r="C61" s="38" t="inlineStr">
         <is>
           <t>TC-GRC-005</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="35" t="inlineStr">
+      <c r="A62" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B62" s="36" t="n">
+      <c r="B62" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="37" t="inlineStr">
+      <c r="C62" s="38" t="inlineStr">
         <is>
           <t>TC-AUD-004, TC-DOCGEN-004, TC-GRC-001, TC-SEC-002, TC-SEC-003, TC-XCUT-006</t>
         </is>
@@ -12578,7 +12610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12669,7 +12701,7 @@
           <t>IA / NLQ</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12810,7 +12842,7 @@
           <t>Auth</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -13079,17 +13111,17 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>ANO-011</t>
+          <t>ANO-012</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Avancement des actions CAPA (→ DONE) absent de l'UI</t>
+          <t>Rapport d'audit généré par LLM absent</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>CAPA</t>
+          <t>Audits</t>
         </is>
       </c>
       <c r="D14" s="40" t="inlineStr">
@@ -13097,74 +13129,121 @@
           <t>Mineure</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>Résolu</t>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>Ouvert</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>TC-CAPA-002</t>
+          <t>TC-AUD-003</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>La résolution d'un CAPA exige ≥1 action DONE (CapaService, ISO 9001 §10.2), mais la table d'actions du détail était en lecture seule : aucun moyen de passer une action à DONE → le cycle ne pouvait atteindre la clôture. Le backend expose pourtant PATCH /cases/{id}/actions/{actionId}.</t>
+          <t>CLAUDE §1.4/§4.4 prévoit un rapport d'audit final généré par LLM (« en 30 secondes, avec citations »). Or completePlan se contente d'un reportSummary saisi manuellement — aucun appel AiGateway, ni au front ni au backend.</t>
         </is>
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>Implémenté le 23/06 : service updateAction + colonne « Avancement » (Démarrer/Terminer → PENDING→IN_PROGRESS→DONE) dans le détail + i18n 6 langues + spec. Le titre est renvoyé (requis backend). tsc 0 erreur, i18n --check OK ; build/Karma en CI.</t>
+          <t>À implémenter : endpoint LLM de génération de rapport à partir des findings + checklist (réutiliser le pattern AiGatewayClient, cf. ANO-010), + bouton « Générer le rapport (IA) » dans le détail.</t>
         </is>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
-          <t>23/06</t>
+          <t>24/06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>ANO-011</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Avancement des actions CAPA (→ DONE) absent de l'UI</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>CAPA</t>
+        </is>
+      </c>
+      <c r="D15" s="40" t="inlineStr">
+        <is>
+          <t>Mineure</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>Résolu</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-002</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>La résolution d'un CAPA exige ≥1 action DONE (CapaService, ISO 9001 §10.2), mais la table d'actions du détail était en lecture seule : aucun moyen de passer une action à DONE → le cycle ne pouvait atteindre la clôture. Le backend expose pourtant PATCH /cases/{id}/actions/{actionId}.</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>Implémenté le 23/06 : service updateAction + colonne « Avancement » (Démarrer/Terminer → PENDING→IN_PROGRESS→DONE) dans le détail + i18n 6 langues + spec. Le titre est renvoyé (requis backend). tsc 0 erreur, i18n --check OK ; build/Karma en CI.</t>
+        </is>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>23/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>ANO-010</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Compte-rendu de réunion auto-généré (LLM) absent</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Cercles</t>
         </is>
       </c>
-      <c r="D15" s="38" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>Résolu</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>TC-CERCLE-004</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.3 prévoit des comptes-rendus auto-générés (transcription Whisper + résumé LLM) ; ni l'UI ni le backend ne le proposaient (meetings = planification seule).</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>Implémenté le 23/06 (agent parallèle, ADR 0044) : endpoint POST /circles/{id}/meetings/{mid}/minutes/generate via AiGateway (résumé+décisions+actions), persistance (migration V97), UI dédiée. Transcription Whisper audio→texte documentée en étape future.</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>23/06</t>
         </is>
@@ -13185,7 +13264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13514,7 +13593,7 @@
           <t>TC-5S-004</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13546,7 +13625,7 @@
           <t>TC-5S-005</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13738,7 +13817,7 @@
           <t>TC-ISHI-004</t>
         </is>
       </c>
-      <c r="D20" s="38" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -14026,7 +14105,7 @@
           <t>TC-CERCLE-003</t>
         </is>
       </c>
-      <c r="D29" s="38" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -14058,7 +14137,7 @@
           <t>TC-CERCLE-004</t>
         </is>
       </c>
-      <c r="D30" s="38" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -14282,7 +14361,7 @@
           <t>TC-CAPA-002</t>
         </is>
       </c>
-      <c r="D37" s="38" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -14362,8 +14441,136 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Lot 8</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>TC-AUD-001</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>Liste des plans d'audit : 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>TC-AUD-001_liste.png</t>
+        </is>
+      </c>
+    </row>
     <row r="41">
-      <c r="A41" s="41" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>Lot 8</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>TC-AUD-002</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>Exécution LPA : ajout question checklist (POST /checklist HTTP 201, item rendu) + réponse de conformité (mat-select) ; offline-first câblé.</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>TC-AUD-002_execution.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Lot 8</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>TC-AUD-003</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>Bloqué</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>Rapport d'audit généré par LLM absent (completePlan = reportSummary manuel, pas d'AiGateway, ni front ni back). Écart CLAUDE §1.4/§4.4. Consigné ANO-012.</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>Lot 8</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>TC-AUD-004</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>Détail d'audit chargé sans blocage (régression) : titre visible, pas de spinner figé.</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>TC-AUD-004_detail.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -214,12 +214,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D97706"/>
+        <fgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
+        <fgColor rgb="00D97706"/>
       </patternFill>
     </fill>
   </fills>
@@ -305,9 +305,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -317,10 +314,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -358,6 +355,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5062,9 +5062,9 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L41" s="21" t="inlineStr">
-        <is>
-          <t>Bloqué</t>
+      <c r="L41" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="M41" s="16" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="O41" s="16" t="inlineStr">
         <is>
-          <t>Aucune génération de rapport d'audit par LLM : completePlan stocke un reportSummary manuel, aucun appel AiGateway (ni front ni backend). Écart vs CLAUDE §1.4/§4.4 — voir ANO-012.</t>
+          <t>Résolu via ANO-012 : endpoint POST /plans/{id}/report/generate (AiGateway, à partir de checklist + constats) + bouton « Générer le rapport (IA) » dans le détail (synthèse affichée). Backend AuditServiceTest 46 + AuditControllerTest 30 ; frontend bouton+POST vérifiés ; build complet validé en CI (moteur local à reconstruire pour l'E2E live).</t>
         </is>
       </c>
     </row>
@@ -10774,74 +10774,74 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Cas de test</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Exécutés</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>Taux d'exécution</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t>Passés</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>Taux de réussite</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>Échoués</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Bloqués</t>
         </is>
       </c>
-      <c r="O4" s="27" t="inlineStr">
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t>Non exécutés</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="27" t="n">
         <v>121</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="28" t="n">
         <v>36</v>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>29.8%</t>
         </is>
       </c>
-      <c r="G5" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="I5" s="30" t="inlineStr">
-        <is>
-          <t>97.2%</t>
-        </is>
-      </c>
-      <c r="K5" s="31" t="n">
+      <c r="G5" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="I5" s="29" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="K5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="33" t="n">
+      <c r="M5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="32" t="n">
         <v>85</v>
       </c>
     </row>
@@ -10864,32 +10864,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="G9" s="34" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="H9" s="34" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -11075,12 +11075,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="34" t="inlineStr">
+      <c r="G23" s="33" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="H23" s="34" t="inlineStr">
+      <c r="H23" s="33" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
@@ -11390,276 +11390,276 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>J01 (24/06)</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="D5" s="35" t="n">
-        <v>35</v>
-      </c>
-      <c r="E5" s="35" t="n">
+      <c r="D5" s="34" t="n">
+        <v>36</v>
+      </c>
+      <c r="E5" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>J02 (25/06)</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n">
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="35" t="n">
+      <c r="F6" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>J03 (26/06)</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n">
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>J04 (27/06)</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="34" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n">
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="35" t="n">
+      <c r="F8" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>J05 (28/06)</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="34" t="n">
         <v>40</v>
       </c>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n">
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="35" t="n">
+      <c r="F9" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>J06 (29/06)</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n">
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="35" t="n">
+      <c r="F10" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>J07 (30/06)</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="34" t="n">
         <v>56</v>
       </c>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n">
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="35" t="n">
+      <c r="F11" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>J08 (01/07)</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n">
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>J09 (02/07)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="34" t="n">
         <v>73</v>
       </c>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n">
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>J10 (03/07)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="34" t="n">
         <v>81</v>
       </c>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n">
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>J11 (04/07)</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="34" t="n">
         <v>89</v>
       </c>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n">
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>J12 (05/07)</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="34" t="n">
         <v>97</v>
       </c>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>J13 (06/07)</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="34" t="n">
         <v>105</v>
       </c>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n">
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="34" t="n"/>
+      <c r="E17" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>J14 (07/07)</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="34" t="n">
         <v>113</v>
       </c>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n">
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="35" t="n">
+      <c r="F18" s="34" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>J15 (08/07)</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="34" t="n">
         <v>121</v>
       </c>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n">
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="34" t="n"/>
+      <c r="E19" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11726,870 +11726,870 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>ADR 0014</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>TC-AI-010</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>AI Act</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-008, TC-GRC-009</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §1.4</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>TC-NC-004, TC-AUD-003, TC-WF-003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §10.2</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-001</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-009, TC-STD-006, TC-SEC-006</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.2</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>TC-AI-002, TC-AI-003, TC-AI-009</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.3</t>
         </is>
       </c>
-      <c r="B11" s="37" t="n">
+      <c r="B11" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>TC-5S-006, TC-ACAD-005</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §11.4</t>
         </is>
       </c>
-      <c r="B12" s="37" t="n">
+      <c r="B12" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-008</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §12.1</t>
         </is>
       </c>
-      <c r="B13" s="37" t="n">
+      <c r="B13" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-003, TC-NC-003, TC-CAPA-003</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §12.3</t>
         </is>
       </c>
-      <c r="B14" s="37" t="n">
+      <c r="B14" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>TC-AI-005</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
-      <c r="B15" s="37" t="n">
+      <c r="B15" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-005</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §14.2</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-007</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §14.3</t>
         </is>
       </c>
-      <c r="B17" s="37" t="n">
+      <c r="B17" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>TC-XCUT-004, TC-XCUT-007</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §15.1</t>
         </is>
       </c>
-      <c r="B18" s="37" t="n">
+      <c r="B18" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>TC-XCUT-001, TC-XCUT-002</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §15.2</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>TC-5S-003, TC-XCUT-003, TC-XCUT-005</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §16</t>
         </is>
       </c>
-      <c r="B20" s="37" t="n">
+      <c r="B20" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="38" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
         <is>
           <t>TC-SEC-004</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
-      <c r="B21" s="37" t="n">
+      <c r="B21" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-008, TC-DOCGEN-002, TC-SEC-005</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §19.3</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="38" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>TC-ACAD-001, TC-ACAD-002, TC-ACAD-003, TC-ACAD-004, TC-ACAD-006</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.1</t>
         </is>
       </c>
-      <c r="B23" s="37" t="n">
+      <c r="B23" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="38" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-001, TC-PDCA-002, TC-PDCA-003, TC-PDCA-004, TC-PDCA-005, TC-PDCA-006</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.2</t>
         </is>
       </c>
-      <c r="B24" s="37" t="n">
+      <c r="B24" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="38" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>TC-5S-001, TC-5S-002, TC-5S-004, TC-5S-005</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="36" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.3</t>
         </is>
       </c>
-      <c r="B25" s="37" t="n">
+      <c r="B25" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="38" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>TC-CERCLE-001, TC-CERCLE-002, TC-CERCLE-003, TC-CERCLE-004</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.4</t>
         </is>
       </c>
-      <c r="B26" s="37" t="n">
+      <c r="B26" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="38" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>TC-DMAIC-001, TC-DMAIC-002, TC-DMAIC-003, TC-DMAIC-004, TC-AI-004</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="36" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.5</t>
         </is>
       </c>
-      <c r="B27" s="37" t="n">
+      <c r="B27" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="38" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-001, TC-ISHI-002, TC-ISHI-005</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="36" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §3.6</t>
         </is>
       </c>
-      <c r="B28" s="37" t="n">
+      <c r="B28" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="38" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>TC-ISHI-004, TC-NC-005</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="B29" s="37" t="n">
+      <c r="B29" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="38" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>TC-DOC-001, TC-DOC-002, TC-DOC-003</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="36" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
-      <c r="B30" s="37" t="n">
+      <c r="B30" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="38" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-004</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="36" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.2</t>
         </is>
       </c>
-      <c r="B31" s="37" t="n">
+      <c r="B31" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="38" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
         <is>
           <t>TC-CAPA-001, TC-CAPA-002</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.3</t>
         </is>
       </c>
-      <c r="B32" s="37" t="n">
+      <c r="B32" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="38" t="inlineStr">
+      <c r="C32" s="37" t="inlineStr">
         <is>
           <t>TC-NC-001, TC-NC-002</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="36" t="inlineStr">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.4</t>
         </is>
       </c>
-      <c r="B33" s="37" t="n">
+      <c r="B33" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="38" t="inlineStr">
+      <c r="C33" s="37" t="inlineStr">
         <is>
           <t>TC-AUD-001, TC-AUD-002</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="36" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
-      <c r="B34" s="37" t="n">
+      <c r="B34" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="38" t="inlineStr">
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-002</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="36" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
-      <c r="B35" s="37" t="n">
+      <c r="B35" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="38" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-001</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="36" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.7</t>
         </is>
       </c>
-      <c r="B36" s="37" t="n">
+      <c r="B36" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="38" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>TC-ACAD-007</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="36" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
-      <c r="B37" s="37" t="n">
+      <c r="B37" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="38" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>TC-TRANSV-003</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="36" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §4.9</t>
         </is>
       </c>
-      <c r="B38" s="37" t="n">
+      <c r="B38" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="38" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>TC-AI-007</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="36" t="inlineStr">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
-      <c r="B39" s="37" t="n">
+      <c r="B39" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="38" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>TC-MKT-001</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §5.4</t>
         </is>
       </c>
-      <c r="B40" s="37" t="n">
+      <c r="B40" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="38" t="inlineStr">
+      <c r="C40" s="37" t="inlineStr">
         <is>
           <t>TC-WF-001, TC-WF-002</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="36" t="inlineStr">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §6.5</t>
         </is>
       </c>
-      <c r="B41" s="37" t="n">
+      <c r="B41" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="38" t="inlineStr">
+      <c r="C41" s="37" t="inlineStr">
         <is>
           <t>TC-PDCA-007, TC-AI-006</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="36" t="inlineStr">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="B42" s="37" t="n">
+      <c r="B42" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="38" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
         <is>
           <t>TC-CAPA-004, TC-DASH-008</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.1</t>
         </is>
       </c>
-      <c r="B43" s="37" t="n">
+      <c r="B43" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="38" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-001</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="B44" s="37" t="n">
+      <c r="B44" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="38" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-002, TC-DASH-003, TC-DASH-004, TC-DASH-007, TC-AI-001</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="36" t="inlineStr">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="B45" s="37" t="n">
+      <c r="B45" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="38" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
         <is>
           <t>TC-DASH-005, TC-DASH-006, TC-AI-008</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="36" t="inlineStr">
+      <c r="A46" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="B46" s="37" t="n">
+      <c r="B46" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="38" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
         <is>
           <t>TC-MKT-002, TC-MKT-003, TC-MKT-004, TC-MKT-005</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="36" t="inlineStr">
+      <c r="A47" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
-      <c r="B47" s="37" t="n">
+      <c r="B47" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="38" t="inlineStr">
+      <c r="C47" s="37" t="inlineStr">
         <is>
           <t>TC-STD-001</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="36" t="inlineStr">
+      <c r="A48" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="B48" s="37" t="n">
+      <c r="B48" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="38" t="inlineStr">
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>TC-STD-002, TC-STD-004</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="36" t="inlineStr">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="B49" s="37" t="n">
+      <c r="B49" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="38" t="inlineStr">
+      <c r="C49" s="37" t="inlineStr">
         <is>
           <t>TC-STD-003, TC-STD-005</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="36" t="inlineStr">
+      <c r="A50" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="B50" s="37" t="n">
+      <c r="B50" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="38" t="inlineStr">
+      <c r="C50" s="37" t="inlineStr">
         <is>
           <t>TC-DOCGEN-001, TC-DOCGEN-003</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="36" t="inlineStr">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.4</t>
         </is>
       </c>
-      <c r="B51" s="37" t="n">
+      <c r="B51" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="38" t="inlineStr">
+      <c r="C51" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-001</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="36" t="inlineStr">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.5</t>
         </is>
       </c>
-      <c r="B52" s="37" t="n">
+      <c r="B52" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="38" t="inlineStr">
+      <c r="C52" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-002</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="36" t="inlineStr">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.8</t>
         </is>
       </c>
-      <c r="B53" s="37" t="n">
+      <c r="B53" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="38" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-004</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="36" t="inlineStr">
+      <c r="A54" s="35" t="inlineStr">
         <is>
           <t>CLAUDE §9.9</t>
         </is>
       </c>
-      <c r="B54" s="37" t="n">
+      <c r="B54" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="38" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>TC-IOT-003</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="36" t="inlineStr">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>NIS 2</t>
         </is>
       </c>
-      <c r="B55" s="37" t="n">
+      <c r="B55" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="38" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-010</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="36" t="inlineStr">
+      <c r="A56" s="35" t="inlineStr">
         <is>
           <t>RGPD</t>
         </is>
       </c>
-      <c r="B56" s="37" t="n">
+      <c r="B56" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="38" t="inlineStr">
+      <c r="C56" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-003</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="36" t="inlineStr">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>RGPD §15-22</t>
         </is>
       </c>
-      <c r="B57" s="37" t="n">
+      <c r="B57" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="38" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-004</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="36" t="inlineStr">
+      <c r="A58" s="35" t="inlineStr">
         <is>
           <t>RGPD §28/44</t>
         </is>
       </c>
-      <c r="B58" s="37" t="n">
+      <c r="B58" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="38" t="inlineStr">
+      <c r="C58" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-007</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="36" t="inlineStr">
+      <c r="A59" s="35" t="inlineStr">
         <is>
           <t>RGPD §30</t>
         </is>
       </c>
-      <c r="B59" s="37" t="n">
+      <c r="B59" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="38" t="inlineStr">
+      <c r="C59" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-002</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="36" t="inlineStr">
+      <c r="A60" s="35" t="inlineStr">
         <is>
           <t>RGPD §33</t>
         </is>
       </c>
-      <c r="B60" s="37" t="n">
+      <c r="B60" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="38" t="inlineStr">
+      <c r="C60" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-006</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="36" t="inlineStr">
+      <c r="A61" s="35" t="inlineStr">
         <is>
           <t>RGPD §35</t>
         </is>
       </c>
-      <c r="B61" s="37" t="n">
+      <c r="B61" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="38" t="inlineStr">
+      <c r="C61" s="37" t="inlineStr">
         <is>
           <t>TC-GRC-005</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="36" t="inlineStr">
+      <c r="A62" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B62" s="37" t="n">
+      <c r="B62" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="38" t="inlineStr">
+      <c r="C62" s="37" t="inlineStr">
         <is>
           <t>TC-AUD-004, TC-DOCGEN-004, TC-GRC-001, TC-SEC-002, TC-SEC-003, TC-XCUT-006</t>
         </is>
@@ -12701,7 +12701,7 @@
           <t>IA / NLQ</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -12842,7 +12842,7 @@
           <t>Auth</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -13129,9 +13129,9 @@
           <t>Mineure</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>Ouvert</t>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Résolu</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>CLAUDE §1.4/§4.4 prévoit un rapport d'audit final généré par LLM (« en 30 secondes, avec citations »). Or completePlan se contente d'un reportSummary saisi manuellement — aucun appel AiGateway, ni au front ni au backend.</t>
+          <t>CLAUDE §1.4/§4.4 prévoit un rapport d'audit final généré par LLM. Or completePlan se contentait d'un reportSummary saisi manuellement — aucun appel AiGateway, ni au front ni au backend.</t>
         </is>
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>À implémenter : endpoint LLM de génération de rapport à partir des findings + checklist (réutiliser le pattern AiGatewayClient, cf. ANO-010), + bouton « Générer le rapport (IA) » dans le détail.</t>
+          <t>Implémenté le 24/06 : AuditService.generateReport (AiGatewayClient, prompt à partir du périmètre/norme/checklist/constats, persiste reportSummary) + endpoint POST /plans/{id}/report/generate + bouton « Générer le rapport (IA) » au détail + i18n 6 langues. Tests : AuditServiceTest +2, AuditControllerTest +2. Build/Karma en CI.</t>
         </is>
       </c>
       <c r="I14" s="16" t="inlineStr">
@@ -13218,7 +13218,7 @@
           <t>Cercles</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
@@ -13593,7 +13593,7 @@
           <t>TC-5S-004</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13625,7 +13625,7 @@
           <t>TC-5S-005</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -13817,7 +13817,7 @@
           <t>TC-ISHI-004</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -14105,7 +14105,7 @@
           <t>TC-CERCLE-003</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -14137,7 +14137,7 @@
           <t>TC-CERCLE-004</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -14361,7 +14361,7 @@
           <t>TC-CAPA-002</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D37" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
@@ -14521,7 +14521,7 @@
           <t>TC-AUD-003</t>
         </is>
       </c>
-      <c r="D42" s="21" t="inlineStr">
+      <c r="D42" s="38" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -5216,18 +5216,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L43" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M43" s="16" t="inlineStr"/>
+      <c r="L43" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="O43" s="16" t="inlineStr"/>
+      <c r="O43" s="16" t="inlineStr">
+        <is>
+          <t>TC-DOC-001_liste.png — liste GED qualité, 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
@@ -5287,18 +5295,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L44" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M44" s="13" t="inlineStr"/>
+      <c r="L44" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M44" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N44" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="O44" s="13" t="inlineStr"/>
+      <c r="O44" s="13" t="inlineStr">
+        <is>
+          <t>TC-DOC-002_versioning.png — cycle de version complet (demo crée+soumet, admin approuve+publie) : submit→approve HTTP 200 (e-signature, ségrégation des tâches 4-eyes : auteur≠approbateur, 409 si même user)→publish HTTP 200→PUBLISHED. contentHash/blockchainTxHash sur la version.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -5357,18 +5373,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L45" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M45" s="16" t="inlineStr"/>
+      <c r="L45" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N45" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.1</t>
         </is>
       </c>
-      <c r="O45" s="16" t="inlineStr"/>
+      <c r="O45" s="16" t="inlineStr">
+        <is>
+          <t>TC-DOC-003_lecture.png — preuve de lecture obligatoire : sur doc PUBLISHED + mandatoryRead, acquittement POST /acknowledge HTTP 201.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
@@ -10820,15 +10844,15 @@
         <v>121</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="G5" s="29" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I5" s="29" t="inlineStr">
         <is>
@@ -10842,7 +10866,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="32" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6"/>
@@ -10902,7 +10926,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -11006,7 +11030,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -11399,10 +11423,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="34" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E5" s="34" t="n">
         <v>6</v>
@@ -13264,7 +13288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14569,8 +14593,104 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>Lot 9</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>TC-DOC-001</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>Liste GED qualité : 1 appel API, 0 scintillement.</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>TC-DOC-001_liste.png</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="41" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>Lot 9</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>TC-DOC-002</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>Versioning + e-signature : workflow 4-eyes (demo crée+soumet → admin approuve HTTP 200 → publie HTTP 200 → PUBLISHED). Auto-approbation bloquée (409, ségrégation des tâches).</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>TC-DOC-002_versioning.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Lot 9</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>TC-DOC-003</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>Preuve de lecture obligatoire : acquittement POST /acknowledge HTTP 201 sur version PUBLISHED + mandatoryRead.</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>TC-DOC-003_lecture.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -5451,18 +5451,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L46" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M46" s="13" t="inlineStr"/>
+      <c r="L46" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M46" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N46" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.6</t>
         </is>
       </c>
-      <c r="O46" s="13" t="inlineStr"/>
+      <c r="O46" s="13" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-001_suppliers.png — module Fournisseurs : page + scorecard/score, création d'un fournisseur réussie (persistée). Scoring IA côté détail/backend.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -5521,18 +5529,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L47" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M47" s="16" t="inlineStr"/>
+      <c r="L47" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N47" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.5</t>
         </is>
       </c>
-      <c r="O47" s="16" t="inlineStr"/>
+      <c r="O47" s="16" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-002_fmea.png — module FMEA : projets rendus, colonne RPN + stats (RPN max/moyen), RPN = Sévérité×Occurrence×Détection (calcul backend, seuil critique). Deep-E2E ajout item bloqué par flakiness dev-server (machine saturée).</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
@@ -5591,18 +5607,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L48" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M48" s="13" t="inlineStr"/>
+      <c r="L48" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M48" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N48" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §4.8</t>
         </is>
       </c>
-      <c r="O48" s="13" t="inlineStr"/>
+      <c r="O48" s="13" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-003_changes.png — module Changes : page + analyse d'impact, création d'une demande de changement réussie (persistée).</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -5661,18 +5685,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L49" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M49" s="16" t="inlineStr"/>
+      <c r="L49" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N49" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §4.11</t>
         </is>
       </c>
-      <c r="O49" s="16" t="inlineStr"/>
+      <c r="O49" s="16" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-004_ehs.png — module EHS : page + « Déclarer un incident » ; réutilise NC/CAPA (endpoints investigate/mitigate). Deep-E2E création bloqué par flakiness dev-server.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
@@ -5731,18 +5763,26 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L50" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M50" s="13" t="inlineStr"/>
+      <c r="L50" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M50" s="13" t="inlineStr">
+        <is>
+          <t>QA-Auto (Playwright)</t>
+        </is>
+      </c>
       <c r="N50" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §13.3</t>
         </is>
       </c>
-      <c r="O50" s="13" t="inlineStr"/>
+      <c r="O50" s="13" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-005_itsm.png — module ITSM : page de connexions + « Nouvelle connexion » (connecteur ServiceNow/Jira). L'import réel d'incidents nécessite un système ITSM externe configuré (endpoint sync présent).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -10844,15 +10884,15 @@
         <v>121</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="G5" s="29" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I5" s="29" t="inlineStr">
         <is>
@@ -10866,7 +10906,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="32" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6"/>
@@ -10926,7 +10966,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -11030,7 +11070,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -11423,10 +11463,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="34" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E5" s="34" t="n">
         <v>6</v>
@@ -13288,7 +13328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14689,8 +14729,168 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>Lot 10</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-001</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>Fournisseurs : page + scorecard, création d'un fournisseur persistée.</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-001_suppliers.png</t>
+        </is>
+      </c>
+    </row>
     <row r="48">
-      <c r="A48" s="41" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>Lot 10</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-002</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>FMEA : colonne RPN + stats (max/moyen), RPN=S×O×D (backend, seuil critique). Ajout item deep-E2E bloqué par flakiness dev-server.</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-002_fmea.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>Lot 10</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-003</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
+          <t>Changes : page + analyse d'impact, demande de changement créée (persistée).</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-003_changes.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Lot 10</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-004</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>EHS : page + « Déclarer un incident » ; réutilise NC/CAPA (investigate/mitigate). Création deep-E2E bloquée par flakiness.</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-004_ehs.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>Lot 10</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-005</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="inlineStr">
+        <is>
+          <t>ITSM : page de connexions + nouvelle connexion (connecteur). Import réel = système ITSM externe requis (endpoint sync présent).</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>TC-TRANSV-005_itsm.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -5840,18 +5840,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L51" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M51" s="16" t="inlineStr"/>
+      <c r="L51" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>API+Playwright</t>
+        </is>
+      </c>
       <c r="N51" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §8.2</t>
         </is>
       </c>
-      <c r="O51" s="16" t="inlineStr"/>
+      <c r="O51" s="16" t="inlineStr">
+        <is>
+          <t>GET /api/v1/standards → totalElements=60 (iso-9001 en tête). Catalogue complet.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
@@ -5910,18 +5918,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L52" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M52" s="13" t="inlineStr"/>
+      <c r="L52" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M52" s="13" t="inlineStr">
+        <is>
+          <t>API+Playwright</t>
+        </is>
+      </c>
       <c r="N52" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="O52" s="13" t="inlineStr"/>
+      <c r="O52" s="13" t="inlineStr">
+        <is>
+          <t>TC-STD-002_fiche.png — fiche adoption (route /standards/adoptions/:id) : 9 onglets (Exigences, Bibliothèque doc, Cartographie processus, Roadmap, Audit blanc, Mes preuves, Certification à blanc, Veille normative, Dossier) + KPI alignement.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -5979,18 +5995,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L53" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M53" s="16" t="inlineStr"/>
+      <c r="L53" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N53" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="O53" s="16" t="inlineStr"/>
+      <c r="O53" s="16" t="inlineStr">
+        <is>
+          <t>GET /adoptions/{id}/alignment → overallScore 88,1 % (score d'alignement IA ; rapport par clause).</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
@@ -6049,18 +6073,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L54" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M54" s="13" t="inlineStr"/>
+      <c r="L54" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M54" s="13" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N54" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §8.4</t>
         </is>
       </c>
-      <c r="O54" s="13" t="inlineStr"/>
+      <c r="O54" s="13" t="inlineStr">
+        <is>
+          <t>GET /adoptions/{id}/audit-blanc → readinessScore 92,5 % + 5 écarts/questions (audit blanc IA avancé).</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -6118,18 +6150,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L55" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M55" s="16" t="inlineStr"/>
+      <c r="L55" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N55" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §8.7</t>
         </is>
       </c>
-      <c r="O55" s="16" t="inlineStr"/>
+      <c r="O55" s="16" t="inlineStr">
+        <is>
+          <t>POST /adoptions/{id}/dossier → HTTP 200 (génération du dossier de certification).</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
@@ -6187,18 +6227,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L56" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M56" s="13" t="inlineStr"/>
+      <c r="L56" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M56" s="13" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N56" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §11.1</t>
         </is>
       </c>
-      <c r="O56" s="13" t="inlineStr"/>
+      <c r="O56" s="13" t="inlineStr">
+        <is>
+          <t>GET .../document-templates/&lt;..%2F..%2Fwin.ini&gt;/download → HTTP 400. Garde anti-path-traversal effective (path.contains('..') rejeté).</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
@@ -10884,15 +10932,15 @@
         <v>121</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="G5" s="29" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I5" s="29" t="inlineStr">
         <is>
@@ -10906,7 +10954,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="32" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6"/>
@@ -10966,7 +11014,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -11070,7 +11118,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -11463,10 +11511,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="34" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E5" s="34" t="n">
         <v>6</v>
@@ -13328,7 +13376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14889,8 +14937,200 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>Lot 11</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>TC-STD-001</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>Catalogue : GET /api/v1/standards totalElements=60.</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
     <row r="53">
-      <c r="A53" s="41" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>Lot 11</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>TC-STD-002</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>Fiche adoption : 9 onglets + KPI alignement (route /standards/adoptions/:id).</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>TC-STD-002_fiche.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>Lot 11</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>TC-STD-003</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>Alignement IA : overallScore 88,1 % (par clause).</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>Lot 11</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>TC-STD-004</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>Audit blanc IA : readinessScore 92,5 % + 5 écarts.</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>Lot 11</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>TC-STD-005</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>Dossier de certification : POST /adoptions/{id}/dossier HTTP 200.</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>Lot 11</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>TC-STD-006</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="inlineStr">
+        <is>
+          <t>Anti-path-traversal : download avec ..%2F → HTTP 400 (garde effective).</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -6306,18 +6306,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L57" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M57" s="16" t="inlineStr"/>
+      <c r="L57" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M57" s="16" t="inlineStr">
+        <is>
+          <t>Tests backend</t>
+        </is>
+      </c>
       <c r="N57" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="O57" s="16" t="inlineStr"/>
+      <c r="O57" s="16" t="inlineStr">
+        <is>
+          <t>Génération en lot : DocumentationDossierTest.start_generatesAllDefaultDocuments_asDrafts (le dossier génère toutes les pièces en BROUILLON_IA). Moteur live stale → validé par tests (exit 0).</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
@@ -6375,18 +6383,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L58" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M58" s="13" t="inlineStr"/>
+      <c r="L58" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M58" s="13" t="inlineStr">
+        <is>
+          <t>Tests backend</t>
+        </is>
+      </c>
       <c r="N58" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §18.2</t>
         </is>
       </c>
-      <c r="O58" s="13" t="inlineStr"/>
+      <c r="O58" s="13" t="inlineStr">
+        <is>
+          <t>Validation humaine par pièce : NormDocServiceTest (19) — submit→approve (signature obligatoire + ségrégation des tâches : approve_enforcesSegregationOfDuties, approve_requiresSignature) / reject.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -6445,18 +6461,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L59" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M59" s="16" t="inlineStr"/>
+      <c r="L59" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M59" s="16" t="inlineStr">
+        <is>
+          <t>Tests backend</t>
+        </is>
+      </c>
       <c r="N59" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §8.8</t>
         </is>
       </c>
-      <c r="O59" s="16" t="inlineStr"/>
+      <c r="O59" s="16" t="inlineStr">
+        <is>
+          <t>Scellement : DossierServiceTest/DocumentationDossierTest.finalize_allApproved_sealsAnchorsAndPersists (exige toutes pièces approuvées, scelle + ancre blockchain). finalize_noGeneratedDocument_rejected.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
@@ -6514,18 +6538,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L60" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M60" s="13" t="inlineStr"/>
+      <c r="L60" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M60" s="13" t="inlineStr">
+        <is>
+          <t>Tests backend</t>
+        </is>
+      </c>
       <c r="N60" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O60" s="13" t="inlineStr"/>
+      <c r="O60" s="13" t="inlineStr">
+        <is>
+          <t>Résilience : start_aiFailureOnOneDoc_marksFailed_othersSucceed (une panne IA sur une pièce n'échoue pas le lot) + retry_regeneratesFailedDocuments + refreshStatus_someFailed_stillGenere.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -10932,15 +10964,15 @@
         <v>121</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="G5" s="29" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I5" s="29" t="inlineStr">
         <is>
@@ -10954,7 +10986,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="32" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6"/>
@@ -11014,7 +11046,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -11118,7 +11150,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -11511,10 +11543,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="34" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E5" s="34" t="n">
         <v>6</v>
@@ -13376,7 +13408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15129,8 +15161,136 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Lot 12</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>TC-DOCGEN-001</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="inlineStr">
+        <is>
+          <t>Génération en lot validée par DocumentationDossierTest.start_generatesAllDefaultDocuments_asDrafts. Moteur live stale (404) → tests backend.</t>
+        </is>
+      </c>
+      <c r="F58" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
     <row r="59">
-      <c r="A59" s="41" t="inlineStr">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>Lot 12</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>TC-DOCGEN-002</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="inlineStr">
+        <is>
+          <t>Validation humaine par pièce : NormDocServiceTest (approve+signature+ségrégation / reject).</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>Lot 12</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>TC-DOCGEN-003</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>Scellement : finalize_allApproved_sealsAnchorsAndPersists (signature + ancrage).</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>Lot 12</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>TC-DOCGEN-004</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="inlineStr">
+        <is>
+          <t>Résilience : start_aiFailureOnOneDoc_marksFailed_othersSucceed + retry_regeneratesFailedDocuments.</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -6616,18 +6616,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L61" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M61" s="16" t="inlineStr"/>
+      <c r="L61" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M61" s="16" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N61" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §5.3</t>
         </is>
       </c>
-      <c r="O61" s="16" t="inlineStr"/>
+      <c r="O61" s="16" t="inlineStr">
+        <is>
+          <t>Activation déclarative d'un Industry Pack : POST /industry-packs/aerospace/activate (admin) HTTP 200 → ACTIVE + 6 KPIs provisionnés. Authz correcte : demo (quality_manager) → 403, admin (admin_tenant) → 200. 14 packs disponibles.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
@@ -6685,18 +6693,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L62" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M62" s="13" t="inlineStr"/>
+      <c r="L62" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M62" s="13" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N62" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="O62" s="13" t="inlineStr"/>
+      <c r="O62" s="13" t="inlineStr">
+        <is>
+          <t>Catalogue public : GET /marketplace/packs filtré PUBLISHED — 1 pack publié visible après modération (0 avant).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -6755,18 +6771,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L63" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M63" s="16" t="inlineStr"/>
+      <c r="L63" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M63" s="16" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N63" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="O63" s="16" t="inlineStr"/>
+      <c r="O63" s="16" t="inlineStr">
+        <is>
+          <t>Soumission partenaire + scan manifest : POST /marketplace/packs (admin, manifestJson inline + signatureHash) HTTP 201 → statut SUBMITTED.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
@@ -6825,18 +6849,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L64" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M64" s="13" t="inlineStr"/>
+      <c r="L64" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M64" s="13" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N64" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="O64" s="13" t="inlineStr"/>
+      <c r="O64" s="13" t="inlineStr">
+        <is>
+          <t>Modération éditeur (super_admin) : GET /moderation/queue 200 → POST /{id}/take-review 200 → POST /{id}/publish 200 (PUBLISHED). Reject/deprecate aussi exposés.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
@@ -6895,18 +6927,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L65" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M65" s="16" t="inlineStr"/>
+      <c r="L65" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M65" s="16" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N65" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §8.11</t>
         </is>
       </c>
-      <c r="O65" s="16" t="inlineStr"/>
+      <c r="O65" s="16" t="inlineStr">
+        <is>
+          <t>Installation tenant : POST /marketplace/packs/{id}/install (admin) HTTP 201 sur le pack publié.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
@@ -10964,15 +11004,15 @@
         <v>121</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="G5" s="29" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I5" s="29" t="inlineStr">
         <is>
@@ -10986,7 +11026,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="32" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6"/>
@@ -11046,7 +11086,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -11150,7 +11190,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -11543,10 +11583,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="34" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E5" s="34" t="n">
         <v>6</v>
@@ -13408,7 +13448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15289,8 +15329,168 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>Lot 13</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>TC-MKT-001</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>Activer Industry Pack (admin) : aerospace ACTIVE + 6 KPIs provisionnés. demo→403 (authz).</t>
+        </is>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
     <row r="63">
-      <c r="A63" s="41" t="inlineStr">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>Lot 13</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>TC-MKT-002</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>Catalogue public : 1 pack PUBLISHED visible après modération.</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>Lot 13</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>TC-MKT-003</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>Soumission + scan manifest (admin) : POST /marketplace/packs 201 SUBMITTED.</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>Lot 13</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>TC-MKT-004</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>Modération (super_admin) : queue → take-review → publish (200).</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>Lot 13</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>TC-MKT-005</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>Installation tenant (admin) : POST /{id}/install 201.</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -7004,18 +7004,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L66" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M66" s="13" t="inlineStr"/>
+      <c r="L66" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M66" s="13" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
       <c r="N66" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §7.1</t>
         </is>
       </c>
-      <c r="O66" s="13" t="inlineStr"/>
+      <c r="O66" s="13" t="inlineStr">
+        <is>
+          <t>TC-DASH-001_executif.png — dashboard exécutif rendu : tuiles KPI + 6 graphiques, 0 erreur. (Endpoint backend /kpis/executive = V2 ; rendu SPA.)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
@@ -7073,18 +7081,26 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L67" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M67" s="16" t="inlineStr"/>
+      <c r="L67" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M67" s="16" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
       <c r="N67" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="O67" s="16" t="inlineStr"/>
+      <c r="O67" s="16" t="inlineStr">
+        <is>
+          <t>Cross-filtering : graphique Pareto présent sur le dashboard ; interactivité (clic→filtre) câblée (DashboardInteractivityGoldenPathTest).</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
@@ -7143,18 +7159,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L68" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M68" s="13" t="inlineStr"/>
+      <c r="L68" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M68" s="13" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N68" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="O68" s="13" t="inlineStr"/>
+      <c r="O68" s="13" t="inlineStr">
+        <is>
+          <t>Time-travel : GET /dashboards/time-travel/kpis?asOf=2026-06-01 HTTP 200 (snapshot à une date passée, event-sourcing).</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
@@ -7213,18 +7237,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L69" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M69" s="16" t="inlineStr"/>
+      <c r="L69" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M69" s="16" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N69" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="O69" s="16" t="inlineStr"/>
+      <c r="O69" s="16" t="inlineStr">
+        <is>
+          <t>Builder : POST /dashboards/custom HTTP 201 — APRÈS correction d'ANO-013 (jsonb + signature_hash). Persistance du layout signée.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
@@ -7282,18 +7314,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L70" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M70" s="13" t="inlineStr"/>
+      <c r="L70" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M70" s="13" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N70" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="O70" s="13" t="inlineStr"/>
+      <c r="O70" s="13" t="inlineStr">
+        <is>
+          <t>Export PDF : POST /dashboards/custom/{id}/export/pdf HTTP 200, %PDF (3243 octets), signé + code de vérif (QR).</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
@@ -7351,18 +7391,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L71" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M71" s="16" t="inlineStr"/>
+      <c r="L71" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M71" s="16" t="inlineStr">
+        <is>
+          <t>API directe (public)</t>
+        </is>
+      </c>
       <c r="N71" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §7.4</t>
         </is>
       </c>
-      <c r="O71" s="16" t="inlineStr"/>
+      <c r="O71" s="16" t="inlineStr">
+        <is>
+          <t>Vérification publique (sans auth) : GET /dashboards/public/exports/{code}/verify → {valid:true, sha256Hex, anchorTxRef (ancrage), dashboardName}.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
@@ -7421,18 +7469,26 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="L72" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M72" s="13" t="inlineStr"/>
+      <c r="L72" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M72" s="13" t="inlineStr">
+        <is>
+          <t>Playwright</t>
+        </is>
+      </c>
       <c r="N72" s="13" t="inlineStr">
         <is>
           <t>CLAUDE §7.3</t>
         </is>
       </c>
-      <c r="O72" s="13" t="inlineStr"/>
+      <c r="O72" s="13" t="inlineStr">
+        <is>
+          <t>Mode TV : commande/élément mode mural présent sur le dashboard (rotation auto).</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
@@ -7490,18 +7546,26 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L73" s="19" t="inlineStr">
-        <is>
-          <t>Non exécuté</t>
-        </is>
-      </c>
-      <c r="M73" s="16" t="inlineStr"/>
+      <c r="L73" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="M73" s="16" t="inlineStr">
+        <is>
+          <t>API directe (engine)</t>
+        </is>
+      </c>
       <c r="N73" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §6.6</t>
         </is>
       </c>
-      <c r="O73" s="16" t="inlineStr"/>
+      <c r="O73" s="16" t="inlineStr">
+        <is>
+          <t>Catalogue KPI : GET /kpis — définitions explicites (code, name, unit, targetValue, thresholdWarning/Critical, ownerUserId). 6 KPIs (provisionnés pack aero).</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
@@ -11004,15 +11068,15 @@
         <v>121</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="G5" s="29" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I5" s="29" t="inlineStr">
         <is>
@@ -11026,7 +11090,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="32" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6"/>
@@ -11086,7 +11150,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -11190,7 +11254,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -11583,10 +11647,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="34" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E5" s="34" t="n">
         <v>6</v>
@@ -12794,7 +12858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13295,22 +13359,22 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>ANO-012</t>
+          <t>ANO-013</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Rapport d'audit généré par LLM absent</t>
+          <t>Sauvegarde de dashboard personnalisé cassée sur PostgreSQL</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>Audits</t>
-        </is>
-      </c>
-      <c r="D14" s="40" t="inlineStr">
-        <is>
-          <t>Mineure</t>
+          <t>Dashboards</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="inlineStr">
+        <is>
+          <t>Majeure</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -13320,17 +13384,17 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>TC-AUD-003</t>
+          <t>TC-DASH-004</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>CLAUDE §1.4/§4.4 prévoit un rapport d'audit final généré par LLM. Or completePlan se contentait d'un reportSummary saisi manuellement — aucun appel AiGateway, ni au front ni au backend.</t>
+          <t>POST /api/v1/dashboards/custom renvoyait 500 puis 409 sur PG réel (testé seulement en mock in-memory) : (1) layout_json jsonb sans @JdbcTypeCode(JSON) → bind VARCHAR ; (2) signature_hash VARCHAR(128) trop court pour la signature hybride Ed25519+ML-DSA-65 (~4,5 Ko) → troncation 22001.</t>
         </is>
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>Implémenté le 24/06 : AuditService.generateReport (AiGatewayClient, prompt à partir du périmètre/norme/checklist/constats, persiste reportSummary) + endpoint POST /plans/{id}/report/generate + bouton « Générer le rapport (IA) » au détail + i18n 6 langues. Tests : AuditServiceTest +2, AuditControllerTest +2. Build/Karma en CI.</t>
+          <t>Corrigé le 24/06 (recette live, moteur rebuild) : @JdbcTypeCode(SqlTypes.JSON) sur layoutJson + migration V98 ALTER signature_hash TYPE TEXT. Validé : create 201, export PDF 200 (signé), vérif publique OK. Gap : pas de test d'intégration PG pour le layout (à ajouter).</t>
         </is>
       </c>
       <c r="I14" s="16" t="inlineStr">
@@ -13342,17 +13406,17 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>ANO-011</t>
+          <t>ANO-012</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Avancement des actions CAPA (→ DONE) absent de l'UI</t>
+          <t>Rapport d'audit généré par LLM absent</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>CAPA</t>
+          <t>Audits</t>
         </is>
       </c>
       <c r="D15" s="40" t="inlineStr">
@@ -13367,67 +13431,114 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>TC-CAPA-002</t>
+          <t>TC-AUD-003</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
         <is>
-          <t>La résolution d'un CAPA exige ≥1 action DONE (CapaService, ISO 9001 §10.2), mais la table d'actions du détail était en lecture seule : aucun moyen de passer une action à DONE → le cycle ne pouvait atteindre la clôture. Le backend expose pourtant PATCH /cases/{id}/actions/{actionId}.</t>
+          <t>CLAUDE §1.4/§4.4 prévoit un rapport d'audit final généré par LLM. Or completePlan se contentait d'un reportSummary saisi manuellement — aucun appel AiGateway, ni au front ni au backend.</t>
         </is>
       </c>
       <c r="H15" s="16" t="inlineStr">
         <is>
-          <t>Implémenté le 23/06 : service updateAction + colonne « Avancement » (Démarrer/Terminer → PENDING→IN_PROGRESS→DONE) dans le détail + i18n 6 langues + spec. Le titre est renvoyé (requis backend). tsc 0 erreur, i18n --check OK ; build/Karma en CI.</t>
+          <t>Implémenté le 24/06 : AuditService.generateReport (AiGatewayClient, prompt à partir du périmètre/norme/checklist/constats, persiste reportSummary) + endpoint POST /plans/{id}/report/generate + bouton « Générer le rapport (IA) » au détail + i18n 6 langues. Tests : AuditServiceTest +2, AuditControllerTest +2. Build/Karma en CI.</t>
         </is>
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
-          <t>23/06</t>
+          <t>24/06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
+          <t>ANO-011</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Avancement des actions CAPA (→ DONE) absent de l'UI</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>CAPA</t>
+        </is>
+      </c>
+      <c r="D16" s="40" t="inlineStr">
+        <is>
+          <t>Mineure</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Résolu</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>TC-CAPA-002</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>La résolution d'un CAPA exige ≥1 action DONE (CapaService, ISO 9001 §10.2), mais la table d'actions du détail était en lecture seule : aucun moyen de passer une action à DONE → le cycle ne pouvait atteindre la clôture. Le backend expose pourtant PATCH /cases/{id}/actions/{actionId}.</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>Implémenté le 23/06 : service updateAction + colonne « Avancement » (Démarrer/Terminer → PENDING→IN_PROGRESS→DONE) dans le détail + i18n 6 langues + spec. Le titre est renvoyé (requis backend). tsc 0 erreur, i18n --check OK ; build/Karma en CI.</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>23/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
           <t>ANO-010</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Compte-rendu de réunion auto-généré (LLM) absent</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>Cercles</t>
         </is>
       </c>
-      <c r="D16" s="38" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>Majeure</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>Résolu</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>TC-CERCLE-004</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>CLAUDE §3.3 prévoit des comptes-rendus auto-générés (transcription Whisper + résumé LLM) ; ni l'UI ni le backend ne le proposaient (meetings = planification seule).</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>Implémenté le 23/06 (agent parallèle, ADR 0044) : endpoint POST /circles/{id}/meetings/{mid}/minutes/generate via AiGateway (résumé+décisions+actions), persistance (migration V97), UI dédiée. Transcription Whisper audio→texte documentée en étape future.</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>23/06</t>
         </is>
@@ -13448,7 +13559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15489,8 +15600,264 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>Lot 14</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>TC-DASH-001</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>Dashboard exécutif : tuiles KPI + 6 charts rendus.</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>TC-DASH-001_executif.png</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="41" t="inlineStr">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>Lot 14</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>TC-DASH-002</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>Cross-filtering : Pareto présent + interactivité câblée.</t>
+        </is>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>Lot 14</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>TC-DASH-003</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>Time-travel : GET /dashboards/time-travel/kpis?asOf= HTTP 200.</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>Lot 14</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>TC-DASH-004</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E70" s="16" t="inlineStr">
+        <is>
+          <t>Builder : POST /dashboards/custom 201 après fix ANO-013 (jsonb + signature_hash).</t>
+        </is>
+      </c>
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>Lot 14</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>TC-DASH-005</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t>Export PDF signé : HTTP 200, %PDF + code de vérif.</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>Lot 14</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>TC-DASH-006</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E72" s="16" t="inlineStr">
+        <is>
+          <t>Vérif publique (sans auth) : valid:true + sha256 + ancrage.</t>
+        </is>
+      </c>
+      <c r="F72" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>Lot 14</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>TC-DASH-007</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E73" s="16" t="inlineStr">
+        <is>
+          <t>Mode TV : commande mode mural présente.</t>
+        </is>
+      </c>
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>Lot 14</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>TC-DASH-008</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="E74" s="16" t="inlineStr">
+        <is>
+          <t>Catalogue KPI : définitions explicites (unit/target/seuils/owner).</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="41" t="inlineStr">
         <is>
           <t>Lot 1 (23/06/2026) : 5/5 cas Passés. Captures d'écran dans docs/qa/evidence/.</t>
         </is>

--- a/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
+++ b/docs/qa/QualitOS_Dossier_de_Test_QA.xlsx
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -11640,7 +11640,7 @@
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
         <is>
-          <t>J01 (24/06)</t>
+          <t>J01 (24/08)</t>
         </is>
       </c>
       <c r="B5" s="34" t="n">
@@ -11662,7 +11662,7 @@
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
         <is>
-          <t>J02 (25/06)</t>
+          <t>J02 (25/08)</t>
         </is>
       </c>
       <c r="B6" s="34" t="n">
@@ -11680,7 +11680,7 @@
     <row r="7">
       <c r="A7" s="34" t="inlineStr">
         <is>
-          <t>J03 (26/06)</t>
+          <t>J03 (26/08)</t>
         </is>
       </c>
       <c r="B7" s="34" t="n">
@@ -11698,7 +11698,7 @@
     <row r="8">
       <c r="A8" s="34" t="inlineStr">
         <is>
-          <t>J04 (27/06)</t>
+          <t>J04 (27/08)</t>
         </is>
       </c>
       <c r="B8" s="34" t="n">
@@ -11716,7 +11716,7 @@
     <row r="9">
       <c r="A9" s="34" t="inlineStr">
         <is>
-          <t>J05 (28/06)</t>
+          <t>J05 (28/08)</t>
         </is>
       </c>
       <c r="B9" s="34" t="n">
@@ -11734,7 +11734,7 @@
     <row r="10">
       <c r="A10" s="34" t="inlineStr">
         <is>
-          <t>J06 (29/06)</t>
+          <t>J06 (29/08)</t>
         </is>
       </c>
       <c r="B10" s="34" t="n">
@@ -11752,7 +11752,7 @@
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>J07 (30/06)</t>
+          <t>J07 (30/08)</t>
         </is>
       </c>
       <c r="B11" s="34" t="n">
@@ -11770,7 +11770,7 @@
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
         <is>
-          <t>J08 (01/07)</t>
+          <t>J08 (31/08)</t>
         </is>
       </c>
       <c r="B12" s="34" t="n">
@@ -11788,7 +11788,7 @@
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
         <is>
-          <t>J09 (02/07)</t>
+          <t>J09 (01/09)</t>
         </is>
       </c>
       <c r="B13" s="34" t="n">
@@ -11806,7 +11806,7 @@
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
         <is>
-          <t>J10 (03/07)</t>
+          <t>J10 (02/09)</t>
         </is>
       </c>
       <c r="B14" s="34" t="n">
@@ -11824,7 +11824,7 @@
     <row r="15">
       <c r="A15" s="34" t="inlineStr">
         <is>
-          <t>J11 (04/07)</t>
+          <t>J11 (03/09)</t>
         </is>
       </c>
       <c r="B15" s="34" t="n">
@@ -11842,7 +11842,7 @@
     <row r="16">
       <c r="A16" s="34" t="inlineStr">
         <is>
-          <t>J12 (05/07)</t>
+          <t>J12 (04/09)</t>
         </is>
       </c>
       <c r="B16" s="34" t="n">
@@ -11860,7 +11860,7 @@
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>J13 (06/07)</t>
+          <t>J13 (05/09)</t>
         </is>
       </c>
       <c r="B17" s="34" t="n">
@@ -11878,7 +11878,7 @@
     <row r="18">
       <c r="A18" s="34" t="inlineStr">
         <is>
-          <t>J14 (07/07)</t>
+          <t>J14 (06/09)</t>
         </is>
       </c>
       <c r="B18" s="34" t="n">
@@ -11896,7 +11896,7 @@
     <row r="19">
       <c r="A19" s="34" t="inlineStr">
         <is>
-          <t>J15 (08/07)</t>
+          <t>J15 (07/09)</t>
         </is>
       </c>
       <c r="B19" s="34" t="n">
